--- a/kapremont/output/Квитанция_КапРемонт_Омск_шаблон.xlsx
+++ b/kapremont/output/Квитанция_КапРемонт_Омск_шаблон.xlsx
@@ -24,18 +24,17 @@
     <definedName name="КВ_ПЕРИОД">КВИТАНЦИЯ!$G$17</definedName>
     <definedName name="КВ_НАЧИСЛЕНО">КВИТАНЦИЯ!$H$21</definedName>
     <definedName name="КВ_ДОЛГ">КВИТАНЦИЯ!$H$22</definedName>
-    <definedName name="КВ_ПЕНИ">КВИТАНЦИЯ!$H$23</definedName>
-    <definedName name="КВ_ПЕРЕРАСЧЕТ">КВИТАНЦИЯ!$H$24</definedName>
-    <definedName name="КВ_ИТОГО">КВИТАНЦИЯ!$H$25</definedName>
-    <definedName name="КВ_ОПЛАЧЕНО">КВИТАНЦИЯ!$G$28</definedName>
-    <definedName name="КВ_НАКОПЛЕНО">КВИТАНЦИЯ!$G$29</definedName>
-    <definedName name="КВ_ОСТАТОК">КВИТАНЦИЯ!$G$30</definedName>
-    <definedName name="КВ_QR_МЕСТО">КВИТАНЦИЯ!$G$33</definedName>
+    <definedName name="КВ_ПЕРЕРАСЧЕТ">КВИТАНЦИЯ!$H$23</definedName>
+    <definedName name="КВ_ИТОГО">КВИТАНЦИЯ!$H$24</definedName>
+    <definedName name="КВ_ОПЛАЧЕНО">КВИТАНЦИЯ!$G$27</definedName>
+    <definedName name="КВ_НАКОПЛЕНО">КВИТАНЦИЯ!$G$28</definedName>
+    <definedName name="КВ_ОСТАТОК">КВИТАНЦИЯ!$G$29</definedName>
+    <definedName name="КВ_QR_МЕСТО">КВИТАНЦИЯ!$G$32</definedName>
     <definedName name="КВ_QR">НАСТРОЙКИ!$B$20</definedName>
     <definedName name="КВ_СХЕМА">НАСТРОЙКИ!$B$17</definedName>
-    <definedName name="ДАННЫЕ_ТАБЛИЦА">ДАННЫЕ!$A$1:$R$5000</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'КВИТАНЦИЯ'!$A$1:$I$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ДАННЫЕ'!$A$1:$R$1</definedName>
+    <definedName name="ДАННЫЕ_ТАБЛИЦА">ДАННЫЕ!$A$1:$Q$5000</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'КВИТАНЦИЯ'!$A$1:$I$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ДАННЫЕ'!$A$1:$Q$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -388,7 +387,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -525,23 +524,17 @@
     <xf numFmtId="4" fontId="11" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -985,17 +978,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H42"/>
+  <dimension ref="B2:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.8" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20.5" customWidth="1" min="2" max="2"/>
     <col width="12.5" customWidth="1" min="3" max="3"/>
-    <col width="11.5" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12.5" customWidth="1" min="7" max="7"/>
-    <col width="14.5" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="10.5" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="1.8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -1022,7 +1015,7 @@
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="4">
-        <f>"Расчётный период: "&amp;IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$14,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
+        <f>"Расчётный период: "&amp;IF(IFERROR(INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$14,INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
         <v/>
       </c>
       <c r="G3" s="4" t="n"/>
@@ -1252,7 +1245,7 @@
         </is>
       </c>
       <c r="G17" s="31">
-        <f>IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$14,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
+        <f>IF(IFERROR(INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$14,INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
         <v/>
       </c>
       <c r="H17" s="32" t="n"/>
@@ -1302,7 +1295,7 @@
       <c r="D21" s="13" t="n"/>
       <c r="E21" s="13" t="n"/>
       <c r="F21" s="37">
-        <f>IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$14,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
+        <f>IF(IFERROR(INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$14,INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
         <v/>
       </c>
       <c r="G21" s="37" t="n"/>
@@ -1321,7 +1314,7 @@
       <c r="D22" s="13" t="n"/>
       <c r="E22" s="13" t="n"/>
       <c r="F22" s="37">
-        <f>"на "&amp;TEXT(DAY(IF(IFERROR(INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;TEXT(MONTH(IF(IFERROR(INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;YEAR(IF(IFERROR(INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))))</f>
+        <f>"на "&amp;TEXT(DAY(IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;TEXT(MONTH(IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;YEAR(IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))))</f>
         <v/>
       </c>
       <c r="G22" s="37" t="n"/>
@@ -1333,7 +1326,7 @@
     <row r="23" ht="17" customHeight="1">
       <c r="B23" s="36" t="inlineStr">
         <is>
-          <t>Пени за несвоевременную уплату взносов</t>
+          <t>Перерасчёты / переплата (уменьшают сумму к оплате)</t>
         </is>
       </c>
       <c r="C23" s="13" t="n"/>
@@ -1346,273 +1339,244 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="17" customHeight="1">
-      <c r="B24" s="36" t="inlineStr">
-        <is>
-          <t>Перерасчёты / переплата (уменьшают сумму к оплате)</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="37" t="n"/>
-      <c r="G24" s="37" t="n"/>
-      <c r="H24" s="38">
-        <f>IFERROR(INDEX(ДАННЫЕ!$J:$J,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="B25" s="39" t="inlineStr">
+    <row r="24" ht="28" customHeight="1">
+      <c r="B24" s="39" t="inlineStr">
         <is>
           <t>ИТОГО К ОПЛАТЕ</t>
         </is>
       </c>
-      <c r="C25" s="40" t="n"/>
-      <c r="D25" s="40" t="n"/>
-      <c r="E25" s="40" t="n"/>
-      <c r="F25" s="40" t="n"/>
-      <c r="G25" s="40" t="n"/>
-      <c r="H25" s="41">
-        <f>IF(IFERROR(INDEX(ДАННЫЕ!$K:$K,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",ROUND(H21+H22+H23+H24,2),INDEX(ДАННЫЕ!$K:$K,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="5" customHeight="1"/>
-    <row r="27" ht="16" customHeight="1">
-      <c r="B27" s="6" t="inlineStr">
+      <c r="C24" s="40" t="n"/>
+      <c r="D24" s="40" t="n"/>
+      <c r="E24" s="40" t="n"/>
+      <c r="F24" s="40" t="n"/>
+      <c r="G24" s="40" t="n"/>
+      <c r="H24" s="41">
+        <f>IF(IFERROR(INDEX(ДАННЫЕ!$J:$J,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",ROUND(H21+H22+H23,2),INDEX(ДАННЫЕ!$J:$J,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="5" customHeight="1"/>
+    <row r="26" ht="16" customHeight="1">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>4. СПРАВОЧНАЯ ИНФОРМАЦИЯ ПО СПЕЦИАЛЬНОМУ СЧЁТУ (ч. 7 ст. 177 ЖК РФ)</t>
         </is>
       </c>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="8" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="8" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="B27" s="36">
+        <f>"Поступило оплат по лицевому счёту с начала "&amp;YEAR(IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))))&amp;" года, руб."</f>
+        <v/>
+      </c>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="13" t="n"/>
+      <c r="G27" s="42">
+        <f>IFERROR(INDEX(ДАННЫЕ!$K:$K,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="H27" s="38" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="B28" s="36">
-        <f>"Поступило оплат по лицевому счёту с начала "&amp;YEAR(IF(IFERROR(INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))))&amp;" года, руб."</f>
-        <v/>
+      <c r="B28" s="36" t="inlineStr">
+        <is>
+          <t>Размер фонда капитального ремонта, накопленного по лицевому счёту, руб.</t>
+        </is>
       </c>
       <c r="C28" s="13" t="n"/>
       <c r="D28" s="13" t="n"/>
       <c r="E28" s="13" t="n"/>
       <c r="F28" s="13" t="n"/>
       <c r="G28" s="42">
-        <f>IFERROR(INDEX(ДАННЫЕ!$L:$L,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),0)</f>
+        <f>IF(IFERROR(INDEX(ДАННЫЕ!$M:$M,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="","—",INDEX(ДАННЫЕ!$M:$M,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
         <v/>
       </c>
       <c r="H28" s="38" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="B29" s="36" t="inlineStr">
-        <is>
-          <t>Размер фонда капитального ремонта, накопленного по лицевому счёту, руб.</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="42">
-        <f>IF(IFERROR(INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="","—",INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
-        <v/>
-      </c>
-      <c r="H29" s="38" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="B30" s="43" t="inlineStr">
+      <c r="B29" s="43" t="inlineStr">
         <is>
           <t>Остаток средств на специальном счёте многоквартирного дома, руб.</t>
         </is>
       </c>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="19" t="n"/>
-      <c r="F30" s="19" t="n"/>
-      <c r="G30" s="44">
-        <f>IF(IFERROR(INDEX(ДАННЫЕ!$M:$M,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="","—",INDEX(ДАННЫЕ!$M:$M,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
-        <v/>
-      </c>
-      <c r="H30" s="45" t="n"/>
-    </row>
-    <row r="31" ht="5" customHeight="1"/>
-    <row r="32" ht="16" customHeight="1">
-      <c r="B32" s="6" t="inlineStr">
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="19" t="n"/>
+      <c r="F29" s="19" t="n"/>
+      <c r="G29" s="44">
+        <f>IF(IFERROR(INDEX(ДАННЫЕ!$L:$L,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="","—",INDEX(ДАННЫЕ!$L:$L,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="H29" s="45" t="n"/>
+    </row>
+    <row r="30" ht="5" customHeight="1"/>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>5. ПОРЯДОК ОПЛАТЫ</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n"/>
-      <c r="G32" s="46" t="inlineStr">
-        <is>
-          <t>QR-КОД ДЛЯ ОПЛАТЫ</t>
-        </is>
-      </c>
-      <c r="H32" s="47" t="n"/>
-    </row>
-    <row r="33" ht="14" customHeight="1">
-      <c r="B33" s="36" t="inlineStr">
-        <is>
-          <t>1) без комиссии — в отделениях АО «Россельхозбанк» (через операционистов);</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="48" t="inlineStr">
-        <is>
-          <t>QR-код
-формируется
-макросом</t>
-        </is>
-      </c>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="8" t="n"/>
+    </row>
+    <row r="32" ht="14" customHeight="1">
+      <c r="B32" s="46" t="inlineStr">
+        <is>
+          <t>1) без комиссии — в отделениях АО «Россельхозбанк» (банк, в котором открыт специальный счёт дома);</t>
+        </is>
+      </c>
+      <c r="C32" s="47" t="n"/>
+      <c r="D32" s="47" t="n"/>
+      <c r="E32" s="47" t="n"/>
+      <c r="F32" s="47" t="n"/>
+      <c r="G32" s="48" t="n"/>
+      <c r="H32" s="49" t="n"/>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="B33" s="46" t="inlineStr">
+        <is>
+          <t>2) по тарифам банка — переводом по указанным выше реквизитам в отделениях и мобильных приложениях ПАО Сбербанк, АО «АЛЬФА-БАНК», Банка ВТБ (ПАО), АО «ТБанк», а также любого другого банка;</t>
+        </is>
+      </c>
+      <c r="C33" s="47" t="n"/>
+      <c r="D33" s="47" t="n"/>
+      <c r="E33" s="47" t="n"/>
+      <c r="F33" s="47" t="n"/>
+      <c r="G33" s="48" t="n"/>
       <c r="H33" s="49" t="n"/>
     </row>
     <row r="34" ht="14" customHeight="1">
-      <c r="B34" s="36" t="inlineStr">
-        <is>
-          <t>2) по тарифам банка — в отделениях ПАО Сбербанк (банкоматы, терминалы, операционисты);</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
+      <c r="B34" s="46" t="n"/>
+      <c r="C34" s="47" t="n"/>
+      <c r="D34" s="47" t="n"/>
+      <c r="E34" s="47" t="n"/>
+      <c r="F34" s="47" t="n"/>
       <c r="G34" s="48" t="n"/>
       <c r="H34" s="49" t="n"/>
     </row>
     <row r="35" ht="14" customHeight="1">
-      <c r="B35" s="36" t="inlineStr">
-        <is>
-          <t>3) в мобильном приложении любого банка — по QR-коду (ГОСТ Р 56042-2014).</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="n"/>
-      <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>Назначение платежа:</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="n"/>
+      <c r="D35" s="15" t="n"/>
+      <c r="E35" s="15" t="n"/>
+      <c r="F35" s="15" t="n"/>
       <c r="G35" s="48" t="n"/>
       <c r="H35" s="49" t="n"/>
     </row>
-    <row r="36" ht="14" customHeight="1">
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>Назначение платежа:</t>
-        </is>
-      </c>
-      <c r="C36" s="15" t="n"/>
-      <c r="D36" s="15" t="n"/>
-      <c r="E36" s="15" t="n"/>
-      <c r="F36" s="15" t="n"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="B36" s="46">
+        <f>"Взнос на капитальный ремонт, л/с № "&amp;КВ_ЛС&amp;", кв. № "&amp;IFERROR(INDEX(ДАННЫЕ!$B:$B,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")&amp;", за "&amp;IF(IFERROR(INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$14,INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))&amp;"."</f>
+        <v/>
+      </c>
+      <c r="C36" s="47" t="n"/>
+      <c r="D36" s="47" t="n"/>
+      <c r="E36" s="47" t="n"/>
+      <c r="F36" s="47" t="n"/>
       <c r="G36" s="48" t="n"/>
       <c r="H36" s="49" t="n"/>
     </row>
-    <row r="37" ht="30" customHeight="1">
+    <row r="37" ht="17" customHeight="1">
       <c r="B37" s="50">
-        <f>"Взнос на капитальный ремонт, л/с № "&amp;КВ_ЛС&amp;", кв. № "&amp;IFERROR(INDEX(ДАННЫЕ!$B:$B,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")&amp;", за "&amp;IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$14,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))&amp;"."</f>
+        <f>"Срок оплаты: до "&amp;TEXT(DAY(IF(IFERROR(INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;TEXT(MONTH(IF(IFERROR(INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;YEAR(IF(IFERROR(INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))))&amp;" г."</f>
         <v/>
       </c>
       <c r="C37" s="51" t="n"/>
       <c r="D37" s="51" t="n"/>
       <c r="E37" s="51" t="n"/>
       <c r="F37" s="51" t="n"/>
-      <c r="G37" s="48" t="n"/>
-      <c r="H37" s="49" t="n"/>
-    </row>
-    <row r="38" ht="17" customHeight="1">
-      <c r="B38" s="52">
-        <f>"Срок оплаты: до "&amp;TEXT(DAY(IF(IFERROR(INDEX(ДАННЫЕ!$Q:$Q,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$Q:$Q,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;TEXT(MONTH(IF(IFERROR(INDEX(ДАННЫЕ!$Q:$Q,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$Q:$Q,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;YEAR(IF(IFERROR(INDEX(ДАННЫЕ!$Q:$Q,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$Q:$Q,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))))&amp;" г."</f>
-        <v/>
-      </c>
-      <c r="C38" s="53" t="n"/>
-      <c r="D38" s="53" t="n"/>
-      <c r="E38" s="53" t="n"/>
-      <c r="F38" s="53" t="n"/>
-      <c r="G38" s="54" t="n"/>
-      <c r="H38" s="55" t="n"/>
-    </row>
-    <row r="39" ht="5" customHeight="1"/>
-    <row r="40" ht="24" customHeight="1">
-      <c r="B40" s="56" t="inlineStr">
+      <c r="G37" s="52" t="n"/>
+      <c r="H37" s="53" t="n"/>
+    </row>
+    <row r="38" ht="5" customHeight="1"/>
+    <row r="39" ht="24" customHeight="1">
+      <c r="B39" s="54" t="inlineStr">
         <is>
           <t>Подпись плательщика  ______________________</t>
         </is>
       </c>
-      <c r="C40" s="56" t="n"/>
-      <c r="D40" s="56" t="n"/>
-      <c r="E40" s="56" t="inlineStr">
+      <c r="C39" s="54" t="n"/>
+      <c r="D39" s="54" t="n"/>
+      <c r="E39" s="54" t="inlineStr">
         <is>
           <t>Кассир  ______________</t>
         </is>
       </c>
-      <c r="F40" s="56" t="n"/>
-      <c r="G40" s="56" t="inlineStr">
+      <c r="F39" s="54" t="n"/>
+      <c r="G39" s="54" t="inlineStr">
         <is>
           <t>Дата  ____________</t>
         </is>
       </c>
-      <c r="H40" s="56" t="n"/>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="B41" s="57" t="inlineStr">
+      <c r="H39" s="54" t="n"/>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="B40" s="55" t="inlineStr">
         <is>
           <t>ВНИМАНИЕ! При оплате в банке обязательно проверяйте расчётный счёт и назначение платежа — во избежание ошибочного зачисления средств на счёт другого дома.</t>
         </is>
       </c>
-      <c r="C41" s="57" t="n"/>
-      <c r="D41" s="57" t="n"/>
-      <c r="E41" s="57" t="n"/>
-      <c r="F41" s="57" t="n"/>
-      <c r="G41" s="57" t="n"/>
-      <c r="H41" s="57" t="n"/>
-    </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="B42" s="58">
-        <f>"По вопросам начислений обращайтесь к председателю совета дома, тел. "&amp;НАСТРОЙКИ!$B$13&amp;".    Документ № "&amp;IF(IFERROR(INDEX(ДАННЫЕ!$R:$R,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="","—",INDEX(ДАННЫЕ!$R:$R,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
-        <v/>
-      </c>
-      <c r="C42" s="58" t="n"/>
-      <c r="D42" s="58" t="n"/>
-      <c r="E42" s="58" t="n"/>
-      <c r="F42" s="58" t="n"/>
-      <c r="G42" s="58" t="n"/>
-      <c r="H42" s="58" t="n"/>
+      <c r="C40" s="55" t="n"/>
+      <c r="D40" s="55" t="n"/>
+      <c r="E40" s="55" t="n"/>
+      <c r="F40" s="55" t="n"/>
+      <c r="G40" s="55" t="n"/>
+      <c r="H40" s="55" t="n"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="B41" s="56">
+        <f>"По вопросам начислений обращайтесь к председателю совета дома, тел. "&amp;НАСТРОЙКИ!$B$13&amp;".    Документ № "&amp;IF(IFERROR(INDEX(ДАННЫЕ!$Q:$Q,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="","—",INDEX(ДАННЫЕ!$Q:$Q,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="C41" s="56" t="n"/>
+      <c r="D41" s="56" t="n"/>
+      <c r="E41" s="56" t="n"/>
+      <c r="F41" s="56" t="n"/>
+      <c r="G41" s="56" t="n"/>
+      <c r="H41" s="56" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="50">
+  <mergeCells count="47">
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="C9:H9"/>
+    <mergeCell ref="G27:H27"/>
     <mergeCell ref="F8:H8"/>
-    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B39:D39"/>
     <mergeCell ref="B20:E20"/>
-    <mergeCell ref="G40:H40"/>
     <mergeCell ref="B5:H5"/>
+    <mergeCell ref="E39:F39"/>
     <mergeCell ref="G17:H17"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="G39:H39"/>
     <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="B26:H26"/>
     <mergeCell ref="B41:H41"/>
-    <mergeCell ref="G33:H38"/>
     <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B40:D40"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="E40:F40"/>
     <mergeCell ref="C7:H7"/>
     <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="B24:G24"/>
     <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B27:H27"/>
-    <mergeCell ref="G30:H30"/>
     <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="G32:H37"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B21:E21"/>
@@ -1621,17 +1585,13 @@
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B42:H42"/>
     <mergeCell ref="F11:H11"/>
     <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B25:G25"/>
     <mergeCell ref="C15:H15"/>
     <mergeCell ref="G29:H29"/>
-    <mergeCell ref="B30:F30"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B13:H13"/>
-    <mergeCell ref="G32:H32"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B32:F32"/>
@@ -1645,7 +1605,7 @@
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.5" right="0.5" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageMargins left="0.24" right="0.24" top="0.2" bottom="0.2" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
@@ -1665,301 +1625,301 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="59" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>Параметр</t>
         </is>
       </c>
-      <c r="B1" s="59" t="inlineStr">
+      <c r="B1" s="57" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C1" s="59" t="inlineStr">
+      <c r="C1" s="57" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="60" t="inlineStr">
+      <c r="A2" s="58" t="inlineStr">
         <is>
           <t>Получатель платежа</t>
         </is>
       </c>
-      <c r="B2" s="61" t="inlineStr">
+      <c r="B2" s="59" t="inlineStr">
         <is>
           <t>РЕГИОНАЛЬНЫЙ ФОНД КАПИТАЛЬНОГО РЕМОНТА МНОГОКВАРТИРНЫХ ДОМОВ ОМСКОЙ ОБЛАСТИ (СПЕЦ. СЧЕТ)</t>
         </is>
       </c>
-      <c r="C2" s="62" t="inlineStr">
+      <c r="C2" s="60" t="inlineStr">
         <is>
           <t>Владелец специального счёта МКД</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="60" t="inlineStr">
+      <c r="A3" s="58" t="inlineStr">
         <is>
           <t>Юридический адрес</t>
         </is>
       </c>
-      <c r="B3" s="61" t="inlineStr">
+      <c r="B3" s="59" t="inlineStr">
         <is>
           <t>644099, г. Омск, ул. Краснофлотская, 24</t>
         </is>
       </c>
-      <c r="C3" s="62" t="inlineStr">
+      <c r="C3" s="60" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="60" t="inlineStr">
+      <c r="A4" s="58" t="inlineStr">
         <is>
           <t>ИНН</t>
         </is>
       </c>
-      <c r="B4" s="61" t="inlineStr">
+      <c r="B4" s="59" t="inlineStr">
         <is>
           <t>5503239348</t>
         </is>
       </c>
-      <c r="C4" s="62" t="inlineStr">
+      <c r="C4" s="60" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="60" t="inlineStr">
+      <c r="A5" s="58" t="inlineStr">
         <is>
           <t>КПП</t>
         </is>
       </c>
-      <c r="B5" s="61" t="inlineStr">
+      <c r="B5" s="59" t="inlineStr">
         <is>
           <t>550301001</t>
         </is>
       </c>
-      <c r="C5" s="62" t="inlineStr">
+      <c r="C5" s="60" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="60" t="inlineStr">
+      <c r="A6" s="58" t="inlineStr">
         <is>
           <t>ОГРН</t>
         </is>
       </c>
-      <c r="B6" s="61" t="inlineStr">
+      <c r="B6" s="59" t="inlineStr">
         <is>
           <t>1027700342890</t>
         </is>
       </c>
-      <c r="C6" s="62" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="60" t="inlineStr">
+      <c r="A7" s="58" t="inlineStr">
         <is>
           <t>Расчётный счёт (спец. счёт МКД)</t>
         </is>
       </c>
-      <c r="B7" s="61" t="inlineStr">
+      <c r="B7" s="59" t="inlineStr">
         <is>
           <t>40604810809000000154</t>
         </is>
       </c>
-      <c r="C7" s="62" t="inlineStr">
+      <c r="C7" s="60" t="inlineStr">
         <is>
           <t>Специальный счёт дома по ул. Магистральная, 2</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="60" t="inlineStr">
+      <c r="A8" s="58" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
       </c>
-      <c r="B8" s="61" t="inlineStr">
+      <c r="B8" s="59" t="inlineStr">
         <is>
           <t>Омский РФ АО «Россельхозбанк»</t>
         </is>
       </c>
-      <c r="C8" s="62" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="60" t="inlineStr">
+      <c r="A9" s="58" t="inlineStr">
         <is>
           <t>Корреспондентский счёт</t>
         </is>
       </c>
-      <c r="B9" s="61" t="inlineStr">
+      <c r="B9" s="59" t="inlineStr">
         <is>
           <t>30101810900000000822</t>
         </is>
       </c>
-      <c r="C9" s="62" t="inlineStr">
+      <c r="C9" s="60" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="60" t="inlineStr">
+      <c r="A10" s="58" t="inlineStr">
         <is>
           <t>БИК</t>
         </is>
       </c>
-      <c r="B10" s="61" t="inlineStr">
+      <c r="B10" s="59" t="inlineStr">
         <is>
           <t>045209822</t>
         </is>
       </c>
-      <c r="C10" s="62" t="inlineStr">
+      <c r="C10" s="60" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="60" t="inlineStr">
+      <c r="A11" s="58" t="inlineStr">
         <is>
           <t>ИНН/КПП банка</t>
         </is>
       </c>
-      <c r="B11" s="61" t="inlineStr">
+      <c r="B11" s="59" t="inlineStr">
         <is>
           <t>7725114488 / 550502001</t>
         </is>
       </c>
-      <c r="C11" s="62" t="inlineStr">
+      <c r="C11" s="60" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="60" t="inlineStr">
+      <c r="A12" s="58" t="inlineStr">
         <is>
           <t>Адрес МКД</t>
         </is>
       </c>
-      <c r="B12" s="61" t="inlineStr">
+      <c r="B12" s="59" t="inlineStr">
         <is>
           <t>г. Омск, ул. Магистральная, 2</t>
         </is>
       </c>
-      <c r="C12" s="62" t="inlineStr">
+      <c r="C12" s="60" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="60" t="inlineStr">
+      <c r="A13" s="58" t="inlineStr">
         <is>
           <t>Контактный телефон</t>
         </is>
       </c>
-      <c r="B13" s="61" t="inlineStr">
+      <c r="B13" s="59" t="inlineStr">
         <is>
           <t>8 908 108 02 00</t>
         </is>
       </c>
-      <c r="C13" s="62" t="inlineStr">
+      <c r="C13" s="60" t="inlineStr">
         <is>
           <t>Председатель совета дома</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="60" t="inlineStr">
+      <c r="A14" s="58" t="inlineStr">
         <is>
           <t>Расчётный период (текст)</t>
         </is>
       </c>
-      <c r="B14" s="61" t="inlineStr">
+      <c r="B14" s="59" t="inlineStr">
         <is>
           <t>Июль 2026</t>
         </is>
       </c>
-      <c r="C14" s="62" t="inlineStr">
+      <c r="C14" s="60" t="inlineStr">
         <is>
           <t>Подставляется в заголовок и в назначение платежа</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="60" t="inlineStr">
+      <c r="A15" s="58" t="inlineStr">
         <is>
           <t>Дата начала периода</t>
         </is>
       </c>
-      <c r="B15" s="63" t="n">
+      <c r="B15" s="61" t="n">
         <v>46204</v>
       </c>
-      <c r="C15" s="62" t="inlineStr">
+      <c r="C15" s="60" t="inlineStr">
         <is>
           <t>Первое число расчётного месяца</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="60" t="inlineStr">
+      <c r="A16" s="58" t="inlineStr">
         <is>
           <t>Срок оплаты</t>
         </is>
       </c>
-      <c r="B16" s="63" t="n">
+      <c r="B16" s="61" t="n">
         <v>46244</v>
       </c>
-      <c r="C16" s="62" t="inlineStr">
+      <c r="C16" s="60" t="inlineStr">
         <is>
           <t>До какого числа вносится взнос</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="60" t="inlineStr">
+      <c r="A17" s="58" t="inlineStr">
         <is>
           <t>Текущая цветовая схема</t>
         </is>
       </c>
-      <c r="B17" s="61" t="inlineStr">
+      <c r="B17" s="59" t="inlineStr">
         <is>
           <t>ЧБ</t>
         </is>
       </c>
-      <c r="C17" s="62" t="inlineStr">
+      <c r="C17" s="60" t="inlineStr">
         <is>
           <t>ЧБ — для печати на А4; ЦВЕТ — для выгрузки в PDF. Переключается макросом</t>
         </is>
       </c>
     </row>
     <row r="20" ht="64" customHeight="1">
-      <c r="A20" s="64" t="inlineStr">
+      <c r="A20" s="62" t="inlineStr">
         <is>
           <t>Строка QR (ГОСТ Р 56042-2014)</t>
         </is>
       </c>
-      <c r="B20" s="65">
+      <c r="B20" s="63">
         <f>"ST00012|Name="&amp;НАСТРОЙКИ!$B$2&amp;"|PersonalAcc="&amp;НАСТРОЙКИ!$B$7&amp;"|BankName="&amp;НАСТРОЙКИ!$B$8&amp;"|BIC="&amp;НАСТРОЙКИ!$B$10&amp;"|CorrespAcc="&amp;НАСТРОЙКИ!$B$9&amp;"|PayeeINN="&amp;НАСТРОЙКИ!$B$4&amp;"|KPP="&amp;НАСТРОЙКИ!$B$5&amp;"|Sum="&amp;TEXT(ROUND(КВ_ИТОГО*100,0),"0")&amp;"|Purpose=Взнос на капитальный ремонт за "&amp;НАСТРОЙКИ!$B$14&amp;", л/с "&amp;КВ_ЛС&amp;"|PersAcc="&amp;КВ_ЛС&amp;"|PayerAddress="&amp;КВ_АДРЕС</f>
         <v/>
       </c>
-      <c r="C20" s="66" t="inlineStr">
+      <c r="C20" s="64" t="inlineStr">
         <is>
           <t>Сумма — в копейках, как требует стандарт. Значение читается макросом (функция СтрокаQR) и передаётся в генератор QR-кода.</t>
         </is>
@@ -1976,7 +1936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1987,179 +1947,170 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="67" t="inlineStr">
+      <c r="A1" s="65" t="inlineStr">
         <is>
           <t>Лицевой счёт</t>
         </is>
       </c>
-      <c r="B1" s="67" t="inlineStr">
+      <c r="B1" s="65" t="inlineStr">
         <is>
           <t>Квартира</t>
         </is>
       </c>
-      <c r="C1" s="67" t="inlineStr">
+      <c r="C1" s="65" t="inlineStr">
         <is>
           <t>ФИО собственника</t>
         </is>
       </c>
-      <c r="D1" s="67" t="inlineStr">
+      <c r="D1" s="65" t="inlineStr">
         <is>
           <t>Адрес помещения</t>
         </is>
       </c>
-      <c r="E1" s="67" t="inlineStr">
+      <c r="E1" s="65" t="inlineStr">
         <is>
           <t>Площадь, м²</t>
         </is>
       </c>
-      <c r="F1" s="67" t="inlineStr">
+      <c r="F1" s="65" t="inlineStr">
         <is>
           <t>Размер взноса, руб./м²</t>
         </is>
       </c>
-      <c r="G1" s="67" t="inlineStr">
+      <c r="G1" s="65" t="inlineStr">
         <is>
           <t>Начислено за период, руб.</t>
         </is>
       </c>
-      <c r="H1" s="67" t="inlineStr">
+      <c r="H1" s="65" t="inlineStr">
         <is>
           <t>Задолженность на начало периода, руб.</t>
         </is>
       </c>
-      <c r="I1" s="67" t="inlineStr">
-        <is>
-          <t>Пени, руб.</t>
-        </is>
-      </c>
-      <c r="J1" s="67" t="inlineStr">
+      <c r="I1" s="65" t="inlineStr">
         <is>
           <t>Перерасчёт / переплата, руб.</t>
         </is>
       </c>
-      <c r="K1" s="67" t="inlineStr">
+      <c r="J1" s="65" t="inlineStr">
         <is>
           <t>ИТОГО к оплате, руб.</t>
         </is>
       </c>
-      <c r="L1" s="67" t="inlineStr">
+      <c r="K1" s="65" t="inlineStr">
         <is>
           <t>Оплачено с начала года, руб.</t>
         </is>
       </c>
-      <c r="M1" s="67" t="inlineStr">
+      <c r="L1" s="65" t="inlineStr">
         <is>
           <t>Остаток на спец. счёте МКД, руб.</t>
         </is>
       </c>
-      <c r="N1" s="67" t="inlineStr">
+      <c r="M1" s="65" t="inlineStr">
         <is>
           <t>Накоплено по лицевому счёту, руб.</t>
         </is>
       </c>
-      <c r="O1" s="67" t="inlineStr">
+      <c r="N1" s="65" t="inlineStr">
         <is>
           <t>Расчётный период (текст)</t>
         </is>
       </c>
-      <c r="P1" s="67" t="inlineStr">
+      <c r="O1" s="65" t="inlineStr">
         <is>
           <t>Дата начала периода</t>
         </is>
       </c>
-      <c r="Q1" s="67" t="inlineStr">
+      <c r="P1" s="65" t="inlineStr">
         <is>
           <t>Срок оплаты</t>
         </is>
       </c>
-      <c r="R1" s="67" t="inlineStr">
+      <c r="Q1" s="65" t="inlineStr">
         <is>
           <t>№ квитанции</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="68" t="n">
+      <c r="A2" s="66" t="n">
         <v>31202</v>
       </c>
-      <c r="B2" s="68" t="n">
+      <c r="B2" s="66" t="n">
         <v>49</v>
       </c>
-      <c r="C2" s="68" t="inlineStr">
+      <c r="C2" s="66" t="inlineStr">
         <is>
           <t>Иванов Иван Иванович</t>
         </is>
       </c>
-      <c r="D2" s="68" t="inlineStr">
+      <c r="D2" s="66" t="inlineStr">
         <is>
           <t>г. Омск, ул. Магистральная, 2, кв. 49</t>
         </is>
       </c>
-      <c r="E2" s="69" t="n">
+      <c r="E2" s="67" t="n">
         <v>63.1</v>
       </c>
-      <c r="F2" s="70" t="n"/>
-      <c r="G2" s="70" t="n">
+      <c r="F2" s="68" t="n"/>
+      <c r="G2" s="68" t="n">
         <v>674.99</v>
       </c>
-      <c r="H2" s="70" t="n">
+      <c r="H2" s="68" t="n">
         <v>19501.38</v>
       </c>
-      <c r="I2" s="70" t="n">
+      <c r="I2" s="68" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="70" t="n">
+      <c r="J2" s="68" t="n">
         <v>20176.37</v>
       </c>
-      <c r="L2" s="70" t="n">
+      <c r="K2" s="68" t="n">
         <v>13441.28</v>
       </c>
-      <c r="M2" s="70" t="n"/>
-      <c r="N2" s="70" t="n"/>
-      <c r="O2" s="68" t="inlineStr">
+      <c r="L2" s="68" t="n"/>
+      <c r="M2" s="68" t="n"/>
+      <c r="N2" s="66" t="inlineStr">
         <is>
           <t>Июль 2026</t>
         </is>
       </c>
-      <c r="P2" s="71" t="n">
+      <c r="O2" s="69" t="n">
         <v>46204</v>
       </c>
-      <c r="Q2" s="71" t="n">
+      <c r="P2" s="69" t="n">
         <v>46244</v>
       </c>
-      <c r="R2" s="68" t="inlineStr">
+      <c r="Q2" s="66" t="inlineStr">
         <is>
           <t>КР-2026-07-31202</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="72" t="inlineStr">
-        <is>
-          <t>Строка 2 — пример из образца. Ниже макрос разноски дописывает по одной строке на лицевой счёт за расчётный период. Ключ поиска — столбец A (лицевой счёт): по нему лист КВИТАНЦИЯ подтягивает все значения формулами ИНДЕКС/ПОИСКПОЗ. Столбцы F, K, M, N можно оставить пустыми — бланк рассчитает их сам либо поставит прочерк.</t>
+      <c r="A4" s="70" t="inlineStr">
+        <is>
+          <t>Строка 2 — пример из образца. Ниже макрос разноски дописывает по одной строке на лицевой счёт за расчётный период. Ключ поиска — столбец A (лицевой счёт): по нему лист КВИТАНЦИЯ подтягивает все значения формулами ИНДЕКС/ПОИСКПОЗ. Столбцы F, J, L, M можно оставить пустыми — бланк рассчитает их сам либо поставит прочерк.</t>
         </is>
       </c>
     </row>
     <row r="5"/>
     <row r="6"/>
   </sheetData>
-  <autoFilter ref="A1:R1"/>
+  <autoFilter ref="A1:Q1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H6"/>
   </mergeCells>
@@ -2185,423 +2136,423 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="67" t="inlineStr">
+      <c r="A1" s="65" t="inlineStr">
         <is>
           <t>Роль</t>
         </is>
       </c>
-      <c r="B1" s="67" t="inlineStr">
+      <c r="B1" s="65" t="inlineStr">
         <is>
           <t>Диапазоны (через запятую)</t>
         </is>
       </c>
-      <c r="C1" s="67" t="inlineStr">
+      <c r="C1" s="65" t="inlineStr">
         <is>
           <t>ЧБ: заливка</t>
         </is>
       </c>
-      <c r="D1" s="67" t="inlineStr">
+      <c r="D1" s="65" t="inlineStr">
         <is>
           <t>ЧБ: шрифт</t>
         </is>
       </c>
-      <c r="E1" s="67" t="inlineStr">
+      <c r="E1" s="65" t="inlineStr">
         <is>
           <t>ЦВЕТ: заливка</t>
         </is>
       </c>
-      <c r="F1" s="67" t="inlineStr">
+      <c r="F1" s="65" t="inlineStr">
         <is>
           <t>ЦВЕТ: шрифт</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="73" t="inlineStr">
+      <c r="A2" s="71" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B2" s="74" t="inlineStr">
+      <c r="B2" s="72" t="inlineStr">
         <is>
           <t>B2:H2</t>
         </is>
       </c>
-      <c r="C2" s="73" t="inlineStr">
+      <c r="C2" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="D2" s="73" t="inlineStr">
+      <c r="D2" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="E2" s="73" t="inlineStr">
+      <c r="E2" s="71" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
-      <c r="F2" s="73" t="inlineStr">
+      <c r="F2" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="73" t="inlineStr">
+      <c r="A3" s="71" t="inlineStr">
         <is>
           <t>subtitle</t>
         </is>
       </c>
-      <c r="B3" s="74" t="inlineStr">
+      <c r="B3" s="72" t="inlineStr">
         <is>
           <t>B3:E3,F3:H3</t>
         </is>
       </c>
-      <c r="C3" s="73" t="inlineStr">
+      <c r="C3" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D3" s="73" t="inlineStr">
+      <c r="D3" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E3" s="73" t="inlineStr">
+      <c r="E3" s="71" t="inlineStr">
         <is>
           <t>DDEFF0</t>
         </is>
       </c>
-      <c r="F3" s="73" t="inlineStr">
+      <c r="F3" s="71" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="73" t="inlineStr">
+      <c r="A4" s="71" t="inlineStr">
         <is>
           <t>section</t>
         </is>
       </c>
-      <c r="B4" s="74" t="inlineStr">
-        <is>
-          <t>B5:H5,B13:H13,B19:H19,B27:H27,B32:F32,G32:H32</t>
-        </is>
-      </c>
-      <c r="C4" s="73" t="inlineStr">
+      <c r="B4" s="72" t="inlineStr">
+        <is>
+          <t>B5:H5,B13:H13,B19:H19,B26:H26,B31:H31</t>
+        </is>
+      </c>
+      <c r="C4" s="71" t="inlineStr">
         <is>
           <t>D9D9D9</t>
         </is>
       </c>
-      <c r="D4" s="73" t="inlineStr">
+      <c r="D4" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E4" s="73" t="inlineStr">
+      <c r="E4" s="71" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
-      <c r="F4" s="73" t="inlineStr">
+      <c r="F4" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="73" t="inlineStr">
+      <c r="A5" s="71" t="inlineStr">
         <is>
           <t>thead</t>
         </is>
       </c>
-      <c r="B5" s="74" t="inlineStr">
+      <c r="B5" s="72" t="inlineStr">
         <is>
           <t>B20:E20,F20:G20,H20</t>
         </is>
       </c>
-      <c r="C5" s="73" t="inlineStr">
+      <c r="C5" s="71" t="inlineStr">
         <is>
           <t>BFBFBF</t>
         </is>
       </c>
-      <c r="D5" s="73" t="inlineStr">
+      <c r="D5" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E5" s="73" t="inlineStr">
+      <c r="E5" s="71" t="inlineStr">
         <is>
           <t>263238</t>
         </is>
       </c>
-      <c r="F5" s="73" t="inlineStr">
+      <c r="F5" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="73" t="inlineStr">
+      <c r="A6" s="71" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="B6" s="74" t="inlineStr">
-        <is>
-          <t>B6,B7,B8,E8,B9,B10,B11,E11,B14,D14,F14,B15,B16,B17,D17,F17,B36:F36</t>
-        </is>
-      </c>
-      <c r="C6" s="73" t="inlineStr">
+      <c r="B6" s="72" t="inlineStr">
+        <is>
+          <t>B6,B7,B8,E8,B9,B10,B11,E11,B14,D14,F14,B15,B16,B17,D17,F17,B35:F35</t>
+        </is>
+      </c>
+      <c r="C6" s="71" t="inlineStr">
         <is>
           <t>F2F2F2</t>
         </is>
       </c>
-      <c r="D6" s="73" t="inlineStr">
+      <c r="D6" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E6" s="73" t="inlineStr">
+      <c r="E6" s="71" t="inlineStr">
         <is>
           <t>F3F5F5</t>
         </is>
       </c>
-      <c r="F6" s="73" t="inlineStr">
+      <c r="F6" s="71" t="inlineStr">
         <is>
           <t>263238</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="73" t="inlineStr">
+      <c r="A7" s="71" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="B7" s="74" t="inlineStr">
-        <is>
-          <t>C6:H6,C7:H7,C8:D8,F8:H8,C9:H9,C10:H10,C11:D11,F11:H11,E14,G14:H14,C15:H15,C16:H16,C17,E17,G17:H17,B21:E21,F21:G21,H21,B22:E22,F22:G22,H22,B23:E23,F23:G23,H23,B24:E24,F24:G24,H24,B28:F28,G28:H28,B29:F29,G29:H29,B30:F30,G30:H30,B33:F33,B34:F34,B35:F35,B37:F37,B42:H42</t>
-        </is>
-      </c>
-      <c r="C7" s="73" t="inlineStr">
+      <c r="B7" s="72" t="inlineStr">
+        <is>
+          <t>C6:H6,C7:H7,C8:D8,F8:H8,C9:H9,C10:H10,C11:D11,F11:H11,E14,G14:H14,C15:H15,C16:H16,C17,E17,G17:H17,B21:E21,F21:G21,H21,B22:E22,F22:G22,H22,B23:E23,F23:G23,H23,B27:F27,G27:H27,B28:F28,G28:H28,B29:F29,G29:H29,B32:F32,B33:F33,B34:F34,B36:F36,B41:H41</t>
+        </is>
+      </c>
+      <c r="C7" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D7" s="73" t="inlineStr">
+      <c r="D7" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E7" s="73" t="inlineStr">
+      <c r="E7" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="F7" s="73" t="inlineStr">
+      <c r="F7" s="71" t="inlineStr">
         <is>
           <t>263238</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="73" t="inlineStr">
+      <c r="A8" s="71" t="inlineStr">
         <is>
           <t>input</t>
         </is>
       </c>
-      <c r="B8" s="74" t="inlineStr">
+      <c r="B8" s="72" t="inlineStr">
         <is>
           <t>C14</t>
         </is>
       </c>
-      <c r="C8" s="73" t="inlineStr">
+      <c r="C8" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D8" s="73" t="inlineStr">
+      <c r="D8" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E8" s="73" t="inlineStr">
+      <c r="E8" s="71" t="inlineStr">
         <is>
           <t>E8F3F3</t>
         </is>
       </c>
-      <c r="F8" s="73" t="inlineStr">
+      <c r="F8" s="71" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="73" t="inlineStr">
+      <c r="A9" s="71" t="inlineStr">
         <is>
           <t>total</t>
         </is>
       </c>
-      <c r="B9" s="74" t="inlineStr">
-        <is>
-          <t>B25:G25</t>
-        </is>
-      </c>
-      <c r="C9" s="73" t="inlineStr">
+      <c r="B9" s="72" t="inlineStr">
+        <is>
+          <t>B24:G24</t>
+        </is>
+      </c>
+      <c r="C9" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="D9" s="73" t="inlineStr">
+      <c r="D9" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="E9" s="73" t="inlineStr">
+      <c r="E9" s="71" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
-      <c r="F9" s="73" t="inlineStr">
+      <c r="F9" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="73" t="inlineStr">
+      <c r="A10" s="71" t="inlineStr">
         <is>
           <t>totalsum</t>
         </is>
       </c>
-      <c r="B10" s="74" t="inlineStr">
-        <is>
-          <t>H25</t>
-        </is>
-      </c>
-      <c r="C10" s="73" t="inlineStr">
+      <c r="B10" s="72" t="inlineStr">
+        <is>
+          <t>H24</t>
+        </is>
+      </c>
+      <c r="C10" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D10" s="73" t="inlineStr">
+      <c r="D10" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E10" s="73" t="inlineStr">
+      <c r="E10" s="71" t="inlineStr">
         <is>
           <t>E8F3F3</t>
         </is>
       </c>
-      <c r="F10" s="73" t="inlineStr">
+      <c r="F10" s="71" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="73" t="inlineStr">
+      <c r="A11" s="71" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B11" s="74" t="inlineStr">
-        <is>
-          <t>B38:F38,B41:H41</t>
-        </is>
-      </c>
-      <c r="C11" s="73" t="inlineStr">
+      <c r="B11" s="72" t="inlineStr">
+        <is>
+          <t>B37:F37,B40:H40</t>
+        </is>
+      </c>
+      <c r="C11" s="71" t="inlineStr">
         <is>
           <t>F2F2F2</t>
         </is>
       </c>
-      <c r="D11" s="73" t="inlineStr">
+      <c r="D11" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E11" s="73" t="inlineStr">
+      <c r="E11" s="71" t="inlineStr">
         <is>
           <t>E8F3F3</t>
         </is>
       </c>
-      <c r="F11" s="73" t="inlineStr">
+      <c r="F11" s="71" t="inlineStr">
         <is>
           <t>263238</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="73" t="inlineStr">
+      <c r="A12" s="71" t="inlineStr">
         <is>
           <t>qr</t>
         </is>
       </c>
-      <c r="B12" s="74" t="inlineStr">
-        <is>
-          <t>G33:H38</t>
-        </is>
-      </c>
-      <c r="C12" s="73" t="inlineStr">
+      <c r="B12" s="72" t="inlineStr">
+        <is>
+          <t>G32:H37</t>
+        </is>
+      </c>
+      <c r="C12" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D12" s="73" t="inlineStr">
+      <c r="D12" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E12" s="73" t="inlineStr">
+      <c r="E12" s="71" t="inlineStr">
         <is>
           <t>F3F5F5</t>
         </is>
       </c>
-      <c r="F12" s="73" t="inlineStr">
+      <c r="F12" s="71" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="73" t="inlineStr">
+      <c r="A13" s="71" t="inlineStr">
         <is>
           <t>plain</t>
         </is>
       </c>
-      <c r="B13" s="74" t="inlineStr">
-        <is>
-          <t>B40:D40,E40:F40,G40:H40</t>
-        </is>
-      </c>
-      <c r="C13" s="73" t="inlineStr">
+      <c r="B13" s="72" t="inlineStr">
+        <is>
+          <t>B39:D39,E39:F39,G39:H39</t>
+        </is>
+      </c>
+      <c r="C13" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D13" s="73" t="inlineStr">
+      <c r="D13" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E13" s="73" t="inlineStr">
+      <c r="E13" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="F13" s="73" t="inlineStr">
+      <c r="F13" s="71" t="inlineStr">
         <is>
           <t>263238</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="72" t="inlineStr">
+      <c r="A15" s="70" t="inlineStr">
         <is>
           <t>Служебная таблица. Макрос ПрименитьСхему читает её и перекрашивает лист КВИТАНЦИЯ. Цвета задаются шестью шестнадцатеричными знаками RRGGBB — правьте прямо здесь, код менять не нужно.</t>
         </is>
@@ -2634,186 +2585,186 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="75" t="inlineStr">
+      <c r="A1" s="73" t="inlineStr">
         <is>
           <t>КАК ВСТРОИТЬ ЭТОТ БЛАНК В СУЩЕСТВУЮЩУЮ ТАБЛИЦУ РАЗНОСКИ</t>
         </is>
       </c>
     </row>
     <row r="2" ht="8" customHeight="1">
-      <c r="A2" s="76" t="inlineStr"/>
+      <c r="A2" s="74" t="inlineStr"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="77" t="inlineStr">
+      <c r="A3" s="75" t="inlineStr">
         <is>
           <t>1. Перенос листов</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="78" t="inlineStr">
+      <c r="A4" s="76" t="inlineStr">
         <is>
           <t>Скопируйте в свою книгу (правый клик по ярлыку листа → Переместить/скопировать) листы КВИТАНЦИЯ, ДАННЫЕ, НАСТРОЙКИ и СХЕМА. Лист СХЕМА скрыт: чтобы увидеть его, нажмите правой кнопкой на любом ярлыке → Показать.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="78" t="inlineStr">
+      <c r="A5" s="76" t="inlineStr">
         <is>
           <t>Именованные диапазоны (КВ_ЛС, КВ_НАЧИСЛЕНО, КВ_ДОЛГ, КВ_ИТОГО и др.) переносятся вместе с листами. Проверьте их в Формулы → Диспетчер имён.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="78" t="inlineStr">
+      <c r="A6" s="76" t="inlineStr">
         <is>
           <t>Импортируйте модуль vba/modКвитанция.bas: Alt+F11 → File → Import File. Книгу сохраните как .xlsm.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="8" customHeight="1">
-      <c r="A7" s="76" t="inlineStr"/>
+      <c r="A7" s="74" t="inlineStr"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="77" t="inlineStr">
+      <c r="A8" s="75" t="inlineStr">
         <is>
           <t>2. Подключение разноски</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="78" t="inlineStr">
+      <c r="A9" s="76" t="inlineStr">
         <is>
           <t>Лист ДАННЫЕ — единственная точка стыковки. Ваш макрос разноски кладёт в него по одной строке на лицевой счёт за расчётный период. Ключ поиска — столбец A (лицевой счёт).</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="78" t="inlineStr">
+      <c r="A10" s="76" t="inlineStr">
         <is>
           <t>Если разноска уже лежит на другом листе, не копируйте её: пропишите в столбцах листа ДАННЫЕ обычные формулы-ссылки на этот лист (ВПР или ИНДЕКС+ПОИСКПОЗ). Бланк разницы не заметит.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="8" customHeight="1">
-      <c r="A11" s="76" t="inlineStr"/>
+      <c r="A11" s="74" t="inlineStr"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="77" t="inlineStr">
+      <c r="A12" s="75" t="inlineStr">
         <is>
           <t>3. Автоподстановка сумм</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="78" t="inlineStr">
-        <is>
-          <t>Достаточно записать лицевой счёт в ячейку КВИТАНЦИЯ!C14 (имя КВ_ЛС) — ФИО, адрес, площадь, начислено, долг, пени и итог подтянутся формулами.</t>
+      <c r="A13" s="76" t="inlineStr">
+        <is>
+          <t>Достаточно записать лицевой счёт в ячейку КВИТАНЦИЯ!C14 (имя КВ_ЛС) — ФИО, адрес, площадь, начислено, долг и итог подтянутся формулами.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="78" t="inlineStr">
+      <c r="A14" s="76" t="inlineStr">
         <is>
           <t>Если суммы удобнее подавать напрямую из макроса, вызывайте процедуру ПодставитьСуммы: она пишет значения в лист ДАННЫЕ, а формулы бланка пересчитываются сами.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="78" t="inlineStr">
-        <is>
-          <t>ИТОГО К ОПЛАТЕ берётся из столбца K листа ДАННЫЕ. Если столбец пуст, бланк считает итог сам: начислено + долг + пени + перерасчёт.</t>
+      <c r="A15" s="76" t="inlineStr">
+        <is>
+          <t>ИТОГО К ОПЛАТЕ берётся из столбца J листа ДАННЫЕ. Если столбец пуст, бланк считает итог сам: начислено + долг + перерасчёт. Пени в этом доме не начисляются, поэтому строки под них в бланке нет.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="8" customHeight="1">
-      <c r="A16" s="76" t="inlineStr"/>
+      <c r="A16" s="74" t="inlineStr"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="77" t="inlineStr">
+      <c r="A17" s="75" t="inlineStr">
         <is>
           <t>4. Печать и PDF</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="78" t="inlineStr">
+      <c r="A18" s="76" t="inlineStr">
         <is>
           <t>Книга сохранена в чёрно-белой схеме — можно сразу печатать на А4: одна страница, поля 5 мм, вписано по ширине и высоте.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="78" t="inlineStr">
+      <c r="A19" s="76" t="inlineStr">
         <is>
           <t>Макрос ЭкспортКвитанцииВPDF временно переключает бланк в цветную схему, выгружает PDF и возвращает чёрно-белый вид. Файл для отправки жителю получается цветным, бумажная копия остаётся чёрно-белой.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="78" t="inlineStr">
+      <c r="A20" s="76" t="inlineStr">
         <is>
           <t>Макрос ПакетныйЭкспортPDF делает то же самое по всем лицевым счетам листа ДАННЫЕ и раскладывает файлы по выбранной папке.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="78" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>Макросы СхемаЧБ и СхемаЦвет переключают вид вручную — например, чтобы посмотреть, как квитанция будет выглядеть у жителя на экране.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="8" customHeight="1">
-      <c r="A22" s="76" t="inlineStr"/>
+      <c r="A22" s="74" t="inlineStr"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="77" t="inlineStr">
+      <c r="A23" s="75" t="inlineStr">
         <is>
           <t>5. QR-код</t>
         </is>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="78" t="inlineStr">
+      <c r="A24" s="76" t="inlineStr">
         <is>
           <t>Строка платежа по ГОСТ Р 56042-2014 собирается формулой на листе НАСТРОЙКИ (имя КВ_QR) и готова к передаче в любой генератор QR. Функция СтрокаQR возвращает её из VBA.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="78" t="inlineStr">
-        <is>
-          <t>Сама картинка QR в шаблон не встроена: вставьте изображение в область G33:H38 вручную либо подключите свой генератор в процедуре ВставитьQR (в модуле оставлена заготовка).</t>
+      <c r="A25" s="76" t="inlineStr">
+        <is>
+          <t>Сама картинка QR в шаблон не встроена: вставьте изображение в область G32:H37 вручную либо подключите свой генератор в процедуре ВставитьQR (в модуле оставлена заготовка).</t>
         </is>
       </c>
     </row>
     <row r="26" ht="8" customHeight="1">
-      <c r="A26" s="76" t="inlineStr"/>
+      <c r="A26" s="74" t="inlineStr"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="77" t="inlineStr">
+      <c r="A27" s="75" t="inlineStr">
         <is>
           <t>6. Что проверить перед первой выдачей квитанций</t>
         </is>
       </c>
     </row>
     <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="78" t="inlineStr">
+      <c r="A28" s="76" t="inlineStr">
         <is>
           <t>• Размер взноса (руб./м²). В исходном файле он подтягивался из внешней книги, поэтому столбец F листа ДАННЫЕ оставлен пустым, а бланк восстанавливает тариф как начислено ÷ площадь. Впишите утверждённый тариф, чтобы в квитанции стояла точная величина.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="78" t="inlineStr">
-        <is>
-          <t>• Остаток средств на специальном счёте и накопления по лицевому счёту (столбцы M и N). Пока они пусты, в разделе 4 стоит прочерк.</t>
+      <c r="A29" s="76" t="inlineStr">
+        <is>
+          <t>• Остаток средств на специальном счёте и накопления по лицевому счёту (столбцы L и M). Пока они пусты, в разделе 4 стоит прочерк.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="78" t="inlineStr">
+      <c r="A30" s="76" t="inlineStr">
         <is>
           <t>• Реквизиты специального счёта на листе НАСТРОЙКИ — они перенесены из вашего образца без изменений.</t>
         </is>

--- a/kapremont/output/Квитанция_КапРемонт_Омск_шаблон.xlsx
+++ b/kapremont/output/Квитанция_КапРемонт_Омск_шаблон.xlsx
@@ -33,7 +33,7 @@
     <definedName name="КВ_QR">НАСТРОЙКИ!$B$20</definedName>
     <definedName name="КВ_СХЕМА">НАСТРОЙКИ!$B$17</definedName>
     <definedName name="ДАННЫЕ_ТАБЛИЦА">ДАННЫЕ!$A$1:$Q$5000</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'КВИТАНЦИЯ'!$A$1:$I$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'КВИТАНЦИЯ'!$A$1:$I$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ДАННЫЕ'!$A$1:$Q$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -387,7 +387,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -548,11 +548,14 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -978,7 +981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H41"/>
+  <dimension ref="B2:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.8" customWidth="1" min="1" max="1"/>
@@ -1446,7 +1449,31 @@
     <row r="33" ht="26" customHeight="1">
       <c r="B33" s="46" t="inlineStr">
         <is>
-          <t>2) по тарифам банка — переводом по указанным выше реквизитам в отделениях и мобильных приложениях ПАО Сбербанк, АО «АЛЬФА-БАНК», Банка ВТБ (ПАО), АО «ТБанк», а также любого другого банка;</t>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">2) по тарифам банка — </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00000000"/>
+              <sz val="9"/>
+            </rPr>
+            <t>только по номеру расчётного счёта</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00000000"/>
+              <sz val="9"/>
+            </rPr>
+            <t>, указанного в разделе 1, в отделениях и мобильных приложениях ПАО Сбербанк, АО «АЛЬФА-БАНК», Банка ВТБ (ПАО), АО «ТБанк», а также любого другого банка;</t>
+          </r>
         </is>
       </c>
       <c r="C33" s="47" t="n"/>
@@ -1503,32 +1530,22 @@
       <c r="H37" s="53" t="n"/>
     </row>
     <row r="38" ht="5" customHeight="1"/>
-    <row r="39" ht="24" customHeight="1">
-      <c r="B39" s="54" t="inlineStr">
-        <is>
-          <t>Подпись плательщика  ______________________</t>
-        </is>
+    <row r="39" ht="30" customHeight="1">
+      <c r="B39" s="54">
+        <f>"ВНИМАНИЕ! ПЛАТИТЕ ТОЛЬКО ПО НОМЕРУ РАСЧЁТНОГО СЧЁТА "&amp;НАСТРОЙКИ!$B$7&amp;" — ЭТО СПЕЦИАЛЬНЫЙ СЧЁТ ВАШЕГО ДОМА"</f>
+        <v/>
       </c>
       <c r="C39" s="54" t="n"/>
       <c r="D39" s="54" t="n"/>
-      <c r="E39" s="54" t="inlineStr">
-        <is>
-          <t>Кассир  ______________</t>
-        </is>
-      </c>
+      <c r="E39" s="54" t="n"/>
       <c r="F39" s="54" t="n"/>
-      <c r="G39" s="54" t="inlineStr">
-        <is>
-          <t>Дата  ____________</t>
-        </is>
-      </c>
+      <c r="G39" s="54" t="n"/>
       <c r="H39" s="54" t="n"/>
     </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="B40" s="55" t="inlineStr">
-        <is>
-          <t>ВНИМАНИЕ! При оплате в банке обязательно проверяйте расчётный счёт и назначение платежа — во избежание ошибочного зачисления средств на счёт другого дома.</t>
-        </is>
+    <row r="40" ht="44" customHeight="1">
+      <c r="B40" s="55">
+        <f>"В отделении банка и в мобильном приложении выбирайте оплату по реквизитам — вкладку «Специальный счёт». Не платите через поиск «Капитальный ремонт»: такой платёж уходит на общий счёт Регионального фонда капитального ремонта и на счёт вашего дома не поступает."&amp;CHAR(10)&amp;"Лицевой счёт № "&amp;КВ_ЛС&amp;" при оплате НЕ вводится — он указан справочно, только для учёта начислений."</f>
+        <v/>
       </c>
       <c r="C40" s="55" t="n"/>
       <c r="D40" s="55" t="n"/>
@@ -1537,36 +1554,57 @@
       <c r="G40" s="55" t="n"/>
       <c r="H40" s="55" t="n"/>
     </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="B41" s="56">
+    <row r="41" ht="6" customHeight="1"/>
+    <row r="42" ht="24" customHeight="1">
+      <c r="B42" s="56" t="inlineStr">
+        <is>
+          <t>Подпись плательщика  ______________________</t>
+        </is>
+      </c>
+      <c r="C42" s="56" t="n"/>
+      <c r="D42" s="56" t="n"/>
+      <c r="E42" s="56" t="inlineStr">
+        <is>
+          <t>Кассир  ______________</t>
+        </is>
+      </c>
+      <c r="F42" s="56" t="n"/>
+      <c r="G42" s="56" t="inlineStr">
+        <is>
+          <t>Дата  ____________</t>
+        </is>
+      </c>
+      <c r="H42" s="56" t="n"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="B43" s="57">
         <f>"По вопросам начислений обращайтесь к председателю совета дома, тел. "&amp;НАСТРОЙКИ!$B$13&amp;".    Документ № "&amp;IF(IFERROR(INDEX(ДАННЫЕ!$Q:$Q,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="","—",INDEX(ДАННЫЕ!$Q:$Q,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="C41" s="56" t="n"/>
-      <c r="D41" s="56" t="n"/>
-      <c r="E41" s="56" t="n"/>
-      <c r="F41" s="56" t="n"/>
-      <c r="G41" s="56" t="n"/>
-      <c r="H41" s="56" t="n"/>
+      <c r="C43" s="57" t="n"/>
+      <c r="D43" s="57" t="n"/>
+      <c r="E43" s="57" t="n"/>
+      <c r="F43" s="57" t="n"/>
+      <c r="G43" s="57" t="n"/>
+      <c r="H43" s="57" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="48">
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
     <mergeCell ref="B40:H40"/>
     <mergeCell ref="C9:H9"/>
+    <mergeCell ref="G42:H42"/>
     <mergeCell ref="G27:H27"/>
     <mergeCell ref="F8:H8"/>
-    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="E42:F42"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="B5:H5"/>
-    <mergeCell ref="E39:F39"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="B27:F27"/>
-    <mergeCell ref="G39:H39"/>
     <mergeCell ref="F21:G21"/>
     <mergeCell ref="B26:H26"/>
-    <mergeCell ref="B41:H41"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="B3:E3"/>
@@ -1579,9 +1617,11 @@
     <mergeCell ref="G32:H37"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B39:H39"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="F22:G22"/>
@@ -1625,301 +1665,301 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="57" t="inlineStr">
+      <c r="A1" s="58" t="inlineStr">
         <is>
           <t>Параметр</t>
         </is>
       </c>
-      <c r="B1" s="57" t="inlineStr">
+      <c r="B1" s="58" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C1" s="57" t="inlineStr">
+      <c r="C1" s="58" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="58" t="inlineStr">
+      <c r="A2" s="59" t="inlineStr">
         <is>
           <t>Получатель платежа</t>
         </is>
       </c>
-      <c r="B2" s="59" t="inlineStr">
+      <c r="B2" s="60" t="inlineStr">
         <is>
           <t>РЕГИОНАЛЬНЫЙ ФОНД КАПИТАЛЬНОГО РЕМОНТА МНОГОКВАРТИРНЫХ ДОМОВ ОМСКОЙ ОБЛАСТИ (СПЕЦ. СЧЕТ)</t>
         </is>
       </c>
-      <c r="C2" s="60" t="inlineStr">
+      <c r="C2" s="61" t="inlineStr">
         <is>
           <t>Владелец специального счёта МКД</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="58" t="inlineStr">
+      <c r="A3" s="59" t="inlineStr">
         <is>
           <t>Юридический адрес</t>
         </is>
       </c>
-      <c r="B3" s="59" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>644099, г. Омск, ул. Краснофлотская, 24</t>
         </is>
       </c>
-      <c r="C3" s="60" t="inlineStr">
+      <c r="C3" s="61" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="58" t="inlineStr">
+      <c r="A4" s="59" t="inlineStr">
         <is>
           <t>ИНН</t>
         </is>
       </c>
-      <c r="B4" s="59" t="inlineStr">
+      <c r="B4" s="60" t="inlineStr">
         <is>
           <t>5503239348</t>
         </is>
       </c>
-      <c r="C4" s="60" t="inlineStr">
+      <c r="C4" s="61" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="58" t="inlineStr">
+      <c r="A5" s="59" t="inlineStr">
         <is>
           <t>КПП</t>
         </is>
       </c>
-      <c r="B5" s="59" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>550301001</t>
         </is>
       </c>
-      <c r="C5" s="60" t="inlineStr">
+      <c r="C5" s="61" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="58" t="inlineStr">
+      <c r="A6" s="59" t="inlineStr">
         <is>
           <t>ОГРН</t>
         </is>
       </c>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>1027700342890</t>
         </is>
       </c>
-      <c r="C6" s="60" t="inlineStr">
+      <c r="C6" s="61" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="58" t="inlineStr">
+      <c r="A7" s="59" t="inlineStr">
         <is>
           <t>Расчётный счёт (спец. счёт МКД)</t>
         </is>
       </c>
-      <c r="B7" s="59" t="inlineStr">
+      <c r="B7" s="60" t="inlineStr">
         <is>
           <t>40604810809000000154</t>
         </is>
       </c>
-      <c r="C7" s="60" t="inlineStr">
+      <c r="C7" s="61" t="inlineStr">
         <is>
           <t>Специальный счёт дома по ул. Магистральная, 2</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="58" t="inlineStr">
+      <c r="A8" s="59" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
       </c>
-      <c r="B8" s="59" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>Омский РФ АО «Россельхозбанк»</t>
         </is>
       </c>
-      <c r="C8" s="60" t="inlineStr">
+      <c r="C8" s="61" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="58" t="inlineStr">
+      <c r="A9" s="59" t="inlineStr">
         <is>
           <t>Корреспондентский счёт</t>
         </is>
       </c>
-      <c r="B9" s="59" t="inlineStr">
+      <c r="B9" s="60" t="inlineStr">
         <is>
           <t>30101810900000000822</t>
         </is>
       </c>
-      <c r="C9" s="60" t="inlineStr">
+      <c r="C9" s="61" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="58" t="inlineStr">
+      <c r="A10" s="59" t="inlineStr">
         <is>
           <t>БИК</t>
         </is>
       </c>
-      <c r="B10" s="59" t="inlineStr">
+      <c r="B10" s="60" t="inlineStr">
         <is>
           <t>045209822</t>
         </is>
       </c>
-      <c r="C10" s="60" t="inlineStr">
+      <c r="C10" s="61" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="58" t="inlineStr">
+      <c r="A11" s="59" t="inlineStr">
         <is>
           <t>ИНН/КПП банка</t>
         </is>
       </c>
-      <c r="B11" s="59" t="inlineStr">
+      <c r="B11" s="60" t="inlineStr">
         <is>
           <t>7725114488 / 550502001</t>
         </is>
       </c>
-      <c r="C11" s="60" t="inlineStr">
+      <c r="C11" s="61" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="58" t="inlineStr">
+      <c r="A12" s="59" t="inlineStr">
         <is>
           <t>Адрес МКД</t>
         </is>
       </c>
-      <c r="B12" s="59" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t>г. Омск, ул. Магистральная, 2</t>
         </is>
       </c>
-      <c r="C12" s="60" t="inlineStr">
+      <c r="C12" s="61" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="58" t="inlineStr">
+      <c r="A13" s="59" t="inlineStr">
         <is>
           <t>Контактный телефон</t>
         </is>
       </c>
-      <c r="B13" s="59" t="inlineStr">
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t>8 908 108 02 00</t>
         </is>
       </c>
-      <c r="C13" s="60" t="inlineStr">
+      <c r="C13" s="61" t="inlineStr">
         <is>
           <t>Председатель совета дома</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="58" t="inlineStr">
+      <c r="A14" s="59" t="inlineStr">
         <is>
           <t>Расчётный период (текст)</t>
         </is>
       </c>
-      <c r="B14" s="59" t="inlineStr">
+      <c r="B14" s="60" t="inlineStr">
         <is>
           <t>Июль 2026</t>
         </is>
       </c>
-      <c r="C14" s="60" t="inlineStr">
+      <c r="C14" s="61" t="inlineStr">
         <is>
           <t>Подставляется в заголовок и в назначение платежа</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="58" t="inlineStr">
+      <c r="A15" s="59" t="inlineStr">
         <is>
           <t>Дата начала периода</t>
         </is>
       </c>
-      <c r="B15" s="61" t="n">
+      <c r="B15" s="62" t="n">
         <v>46204</v>
       </c>
-      <c r="C15" s="60" t="inlineStr">
+      <c r="C15" s="61" t="inlineStr">
         <is>
           <t>Первое число расчётного месяца</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="58" t="inlineStr">
+      <c r="A16" s="59" t="inlineStr">
         <is>
           <t>Срок оплаты</t>
         </is>
       </c>
-      <c r="B16" s="61" t="n">
+      <c r="B16" s="62" t="n">
         <v>46244</v>
       </c>
-      <c r="C16" s="60" t="inlineStr">
+      <c r="C16" s="61" t="inlineStr">
         <is>
           <t>До какого числа вносится взнос</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="58" t="inlineStr">
+      <c r="A17" s="59" t="inlineStr">
         <is>
           <t>Текущая цветовая схема</t>
         </is>
       </c>
-      <c r="B17" s="59" t="inlineStr">
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t>ЧБ</t>
         </is>
       </c>
-      <c r="C17" s="60" t="inlineStr">
+      <c r="C17" s="61" t="inlineStr">
         <is>
           <t>ЧБ — для печати на А4; ЦВЕТ — для выгрузки в PDF. Переключается макросом</t>
         </is>
       </c>
     </row>
     <row r="20" ht="64" customHeight="1">
-      <c r="A20" s="62" t="inlineStr">
+      <c r="A20" s="63" t="inlineStr">
         <is>
           <t>Строка QR (ГОСТ Р 56042-2014)</t>
         </is>
       </c>
-      <c r="B20" s="63">
+      <c r="B20" s="64">
         <f>"ST00012|Name="&amp;НАСТРОЙКИ!$B$2&amp;"|PersonalAcc="&amp;НАСТРОЙКИ!$B$7&amp;"|BankName="&amp;НАСТРОЙКИ!$B$8&amp;"|BIC="&amp;НАСТРОЙКИ!$B$10&amp;"|CorrespAcc="&amp;НАСТРОЙКИ!$B$9&amp;"|PayeeINN="&amp;НАСТРОЙКИ!$B$4&amp;"|KPP="&amp;НАСТРОЙКИ!$B$5&amp;"|Sum="&amp;TEXT(ROUND(КВ_ИТОГО*100,0),"0")&amp;"|Purpose=Взнос на капитальный ремонт за "&amp;НАСТРОЙКИ!$B$14&amp;", л/с "&amp;КВ_ЛС&amp;"|PersAcc="&amp;КВ_ЛС&amp;"|PayerAddress="&amp;КВ_АДРЕС</f>
         <v/>
       </c>
-      <c r="C20" s="64" t="inlineStr">
+      <c r="C20" s="65" t="inlineStr">
         <is>
           <t>Сумма — в копейках, как требует стандарт. Значение читается макросом (функция СтрокаQR) и передаётся в генератор QR-кода.</t>
         </is>
@@ -1959,149 +1999,149 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="65" t="inlineStr">
+      <c r="A1" s="66" t="inlineStr">
         <is>
           <t>Лицевой счёт</t>
         </is>
       </c>
-      <c r="B1" s="65" t="inlineStr">
+      <c r="B1" s="66" t="inlineStr">
         <is>
           <t>Квартира</t>
         </is>
       </c>
-      <c r="C1" s="65" t="inlineStr">
+      <c r="C1" s="66" t="inlineStr">
         <is>
           <t>ФИО собственника</t>
         </is>
       </c>
-      <c r="D1" s="65" t="inlineStr">
+      <c r="D1" s="66" t="inlineStr">
         <is>
           <t>Адрес помещения</t>
         </is>
       </c>
-      <c r="E1" s="65" t="inlineStr">
+      <c r="E1" s="66" t="inlineStr">
         <is>
           <t>Площадь, м²</t>
         </is>
       </c>
-      <c r="F1" s="65" t="inlineStr">
+      <c r="F1" s="66" t="inlineStr">
         <is>
           <t>Размер взноса, руб./м²</t>
         </is>
       </c>
-      <c r="G1" s="65" t="inlineStr">
+      <c r="G1" s="66" t="inlineStr">
         <is>
           <t>Начислено за период, руб.</t>
         </is>
       </c>
-      <c r="H1" s="65" t="inlineStr">
+      <c r="H1" s="66" t="inlineStr">
         <is>
           <t>Задолженность на начало периода, руб.</t>
         </is>
       </c>
-      <c r="I1" s="65" t="inlineStr">
+      <c r="I1" s="66" t="inlineStr">
         <is>
           <t>Перерасчёт / переплата, руб.</t>
         </is>
       </c>
-      <c r="J1" s="65" t="inlineStr">
+      <c r="J1" s="66" t="inlineStr">
         <is>
           <t>ИТОГО к оплате, руб.</t>
         </is>
       </c>
-      <c r="K1" s="65" t="inlineStr">
+      <c r="K1" s="66" t="inlineStr">
         <is>
           <t>Оплачено с начала года, руб.</t>
         </is>
       </c>
-      <c r="L1" s="65" t="inlineStr">
+      <c r="L1" s="66" t="inlineStr">
         <is>
           <t>Остаток на спец. счёте МКД, руб.</t>
         </is>
       </c>
-      <c r="M1" s="65" t="inlineStr">
+      <c r="M1" s="66" t="inlineStr">
         <is>
           <t>Накоплено по лицевому счёту, руб.</t>
         </is>
       </c>
-      <c r="N1" s="65" t="inlineStr">
+      <c r="N1" s="66" t="inlineStr">
         <is>
           <t>Расчётный период (текст)</t>
         </is>
       </c>
-      <c r="O1" s="65" t="inlineStr">
+      <c r="O1" s="66" t="inlineStr">
         <is>
           <t>Дата начала периода</t>
         </is>
       </c>
-      <c r="P1" s="65" t="inlineStr">
+      <c r="P1" s="66" t="inlineStr">
         <is>
           <t>Срок оплаты</t>
         </is>
       </c>
-      <c r="Q1" s="65" t="inlineStr">
+      <c r="Q1" s="66" t="inlineStr">
         <is>
           <t>№ квитанции</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="66" t="n">
+      <c r="A2" s="67" t="n">
         <v>31202</v>
       </c>
-      <c r="B2" s="66" t="n">
+      <c r="B2" s="67" t="n">
         <v>49</v>
       </c>
-      <c r="C2" s="66" t="inlineStr">
+      <c r="C2" s="67" t="inlineStr">
         <is>
           <t>Иванов Иван Иванович</t>
         </is>
       </c>
-      <c r="D2" s="66" t="inlineStr">
+      <c r="D2" s="67" t="inlineStr">
         <is>
           <t>г. Омск, ул. Магистральная, 2, кв. 49</t>
         </is>
       </c>
-      <c r="E2" s="67" t="n">
+      <c r="E2" s="68" t="n">
         <v>63.1</v>
       </c>
-      <c r="F2" s="68" t="n"/>
-      <c r="G2" s="68" t="n">
+      <c r="F2" s="69" t="n"/>
+      <c r="G2" s="69" t="n">
         <v>674.99</v>
       </c>
-      <c r="H2" s="68" t="n">
+      <c r="H2" s="69" t="n">
         <v>19501.38</v>
       </c>
-      <c r="I2" s="68" t="n">
+      <c r="I2" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="68" t="n">
+      <c r="J2" s="69" t="n">
         <v>20176.37</v>
       </c>
-      <c r="K2" s="68" t="n">
+      <c r="K2" s="69" t="n">
         <v>13441.28</v>
       </c>
-      <c r="L2" s="68" t="n"/>
-      <c r="M2" s="68" t="n"/>
-      <c r="N2" s="66" t="inlineStr">
+      <c r="L2" s="69" t="n"/>
+      <c r="M2" s="69" t="n"/>
+      <c r="N2" s="67" t="inlineStr">
         <is>
           <t>Июль 2026</t>
         </is>
       </c>
-      <c r="O2" s="69" t="n">
+      <c r="O2" s="70" t="n">
         <v>46204</v>
       </c>
-      <c r="P2" s="69" t="n">
+      <c r="P2" s="70" t="n">
         <v>46244</v>
       </c>
-      <c r="Q2" s="66" t="inlineStr">
+      <c r="Q2" s="67" t="inlineStr">
         <is>
           <t>КР-2026-07-31202</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="70" t="inlineStr">
+      <c r="A4" s="71" t="inlineStr">
         <is>
           <t>Строка 2 — пример из образца. Ниже макрос разноски дописывает по одной строке на лицевой счёт за расчётный период. Ключ поиска — столбец A (лицевой счёт): по нему лист КВИТАНЦИЯ подтягивает все значения формулами ИНДЕКС/ПОИСКПОЗ. Столбцы F, J, L, M можно оставить пустыми — бланк рассчитает их сам либо поставит прочерк.</t>
         </is>
@@ -2136,423 +2176,423 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="65" t="inlineStr">
+      <c r="A1" s="66" t="inlineStr">
         <is>
           <t>Роль</t>
         </is>
       </c>
-      <c r="B1" s="65" t="inlineStr">
+      <c r="B1" s="66" t="inlineStr">
         <is>
           <t>Диапазоны (через запятую)</t>
         </is>
       </c>
-      <c r="C1" s="65" t="inlineStr">
+      <c r="C1" s="66" t="inlineStr">
         <is>
           <t>ЧБ: заливка</t>
         </is>
       </c>
-      <c r="D1" s="65" t="inlineStr">
+      <c r="D1" s="66" t="inlineStr">
         <is>
           <t>ЧБ: шрифт</t>
         </is>
       </c>
-      <c r="E1" s="65" t="inlineStr">
+      <c r="E1" s="66" t="inlineStr">
         <is>
           <t>ЦВЕТ: заливка</t>
         </is>
       </c>
-      <c r="F1" s="65" t="inlineStr">
+      <c r="F1" s="66" t="inlineStr">
         <is>
           <t>ЦВЕТ: шрифт</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="71" t="inlineStr">
+      <c r="A2" s="72" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B2" s="72" t="inlineStr">
+      <c r="B2" s="73" t="inlineStr">
         <is>
           <t>B2:H2</t>
         </is>
       </c>
-      <c r="C2" s="71" t="inlineStr">
+      <c r="C2" s="72" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="D2" s="71" t="inlineStr">
+      <c r="D2" s="72" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="E2" s="71" t="inlineStr">
+      <c r="E2" s="72" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
-      <c r="F2" s="71" t="inlineStr">
+      <c r="F2" s="72" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="71" t="inlineStr">
+      <c r="A3" s="72" t="inlineStr">
         <is>
           <t>subtitle</t>
         </is>
       </c>
-      <c r="B3" s="72" t="inlineStr">
+      <c r="B3" s="73" t="inlineStr">
         <is>
           <t>B3:E3,F3:H3</t>
         </is>
       </c>
-      <c r="C3" s="71" t="inlineStr">
+      <c r="C3" s="72" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D3" s="71" t="inlineStr">
+      <c r="D3" s="72" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E3" s="71" t="inlineStr">
+      <c r="E3" s="72" t="inlineStr">
         <is>
           <t>DDEFF0</t>
         </is>
       </c>
-      <c r="F3" s="71" t="inlineStr">
+      <c r="F3" s="72" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="71" t="inlineStr">
+      <c r="A4" s="72" t="inlineStr">
         <is>
           <t>section</t>
         </is>
       </c>
-      <c r="B4" s="72" t="inlineStr">
+      <c r="B4" s="73" t="inlineStr">
         <is>
           <t>B5:H5,B13:H13,B19:H19,B26:H26,B31:H31</t>
         </is>
       </c>
-      <c r="C4" s="71" t="inlineStr">
+      <c r="C4" s="72" t="inlineStr">
         <is>
           <t>D9D9D9</t>
         </is>
       </c>
-      <c r="D4" s="71" t="inlineStr">
+      <c r="D4" s="72" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E4" s="71" t="inlineStr">
+      <c r="E4" s="72" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
-      <c r="F4" s="71" t="inlineStr">
+      <c r="F4" s="72" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="71" t="inlineStr">
+      <c r="A5" s="72" t="inlineStr">
         <is>
           <t>thead</t>
         </is>
       </c>
-      <c r="B5" s="72" t="inlineStr">
+      <c r="B5" s="73" t="inlineStr">
         <is>
           <t>B20:E20,F20:G20,H20</t>
         </is>
       </c>
-      <c r="C5" s="71" t="inlineStr">
+      <c r="C5" s="72" t="inlineStr">
         <is>
           <t>BFBFBF</t>
         </is>
       </c>
-      <c r="D5" s="71" t="inlineStr">
+      <c r="D5" s="72" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E5" s="71" t="inlineStr">
+      <c r="E5" s="72" t="inlineStr">
         <is>
           <t>263238</t>
         </is>
       </c>
-      <c r="F5" s="71" t="inlineStr">
+      <c r="F5" s="72" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="71" t="inlineStr">
+      <c r="A6" s="72" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="B6" s="72" t="inlineStr">
+      <c r="B6" s="73" t="inlineStr">
         <is>
           <t>B6,B7,B8,E8,B9,B10,B11,E11,B14,D14,F14,B15,B16,B17,D17,F17,B35:F35</t>
         </is>
       </c>
-      <c r="C6" s="71" t="inlineStr">
+      <c r="C6" s="72" t="inlineStr">
         <is>
           <t>F2F2F2</t>
         </is>
       </c>
-      <c r="D6" s="71" t="inlineStr">
+      <c r="D6" s="72" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E6" s="71" t="inlineStr">
+      <c r="E6" s="72" t="inlineStr">
         <is>
           <t>F3F5F5</t>
         </is>
       </c>
-      <c r="F6" s="71" t="inlineStr">
+      <c r="F6" s="72" t="inlineStr">
         <is>
           <t>263238</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="71" t="inlineStr">
+      <c r="A7" s="72" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="B7" s="72" t="inlineStr">
-        <is>
-          <t>C6:H6,C7:H7,C8:D8,F8:H8,C9:H9,C10:H10,C11:D11,F11:H11,E14,G14:H14,C15:H15,C16:H16,C17,E17,G17:H17,B21:E21,F21:G21,H21,B22:E22,F22:G22,H22,B23:E23,F23:G23,H23,B27:F27,G27:H27,B28:F28,G28:H28,B29:F29,G29:H29,B32:F32,B33:F33,B34:F34,B36:F36,B41:H41</t>
-        </is>
-      </c>
-      <c r="C7" s="71" t="inlineStr">
+      <c r="B7" s="73" t="inlineStr">
+        <is>
+          <t>C6:H6,C7:H7,C8:D8,F8:H8,C9:H9,C10:H10,C11:D11,F11:H11,E14,G14:H14,C15:H15,C16:H16,C17,E17,G17:H17,B21:E21,F21:G21,H21,B22:E22,F22:G22,H22,B23:E23,F23:G23,H23,B27:F27,G27:H27,B28:F28,G28:H28,B29:F29,G29:H29,B32:F32,B33:F33,B34:F34,B36:F36,B43:H43</t>
+        </is>
+      </c>
+      <c r="C7" s="72" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D7" s="71" t="inlineStr">
+      <c r="D7" s="72" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E7" s="71" t="inlineStr">
+      <c r="E7" s="72" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="F7" s="71" t="inlineStr">
+      <c r="F7" s="72" t="inlineStr">
         <is>
           <t>263238</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="71" t="inlineStr">
+      <c r="A8" s="72" t="inlineStr">
         <is>
           <t>input</t>
         </is>
       </c>
-      <c r="B8" s="72" t="inlineStr">
+      <c r="B8" s="73" t="inlineStr">
         <is>
           <t>C14</t>
         </is>
       </c>
-      <c r="C8" s="71" t="inlineStr">
+      <c r="C8" s="72" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D8" s="71" t="inlineStr">
+      <c r="D8" s="72" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E8" s="71" t="inlineStr">
+      <c r="E8" s="72" t="inlineStr">
         <is>
           <t>E8F3F3</t>
         </is>
       </c>
-      <c r="F8" s="71" t="inlineStr">
+      <c r="F8" s="72" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="71" t="inlineStr">
+      <c r="A9" s="72" t="inlineStr">
         <is>
           <t>total</t>
         </is>
       </c>
-      <c r="B9" s="72" t="inlineStr">
-        <is>
-          <t>B24:G24</t>
-        </is>
-      </c>
-      <c r="C9" s="71" t="inlineStr">
+      <c r="B9" s="73" t="inlineStr">
+        <is>
+          <t>B24:G24,B39:H39</t>
+        </is>
+      </c>
+      <c r="C9" s="72" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="D9" s="71" t="inlineStr">
+      <c r="D9" s="72" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="E9" s="71" t="inlineStr">
+      <c r="E9" s="72" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
-      <c r="F9" s="71" t="inlineStr">
+      <c r="F9" s="72" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="71" t="inlineStr">
+      <c r="A10" s="72" t="inlineStr">
         <is>
           <t>totalsum</t>
         </is>
       </c>
-      <c r="B10" s="72" t="inlineStr">
+      <c r="B10" s="73" t="inlineStr">
         <is>
           <t>H24</t>
         </is>
       </c>
-      <c r="C10" s="71" t="inlineStr">
+      <c r="C10" s="72" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D10" s="71" t="inlineStr">
+      <c r="D10" s="72" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E10" s="71" t="inlineStr">
+      <c r="E10" s="72" t="inlineStr">
         <is>
           <t>E8F3F3</t>
         </is>
       </c>
-      <c r="F10" s="71" t="inlineStr">
+      <c r="F10" s="72" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="71" t="inlineStr">
+      <c r="A11" s="72" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B11" s="72" t="inlineStr">
+      <c r="B11" s="73" t="inlineStr">
         <is>
           <t>B37:F37,B40:H40</t>
         </is>
       </c>
-      <c r="C11" s="71" t="inlineStr">
+      <c r="C11" s="72" t="inlineStr">
         <is>
           <t>F2F2F2</t>
         </is>
       </c>
-      <c r="D11" s="71" t="inlineStr">
+      <c r="D11" s="72" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E11" s="71" t="inlineStr">
+      <c r="E11" s="72" t="inlineStr">
         <is>
           <t>E8F3F3</t>
         </is>
       </c>
-      <c r="F11" s="71" t="inlineStr">
+      <c r="F11" s="72" t="inlineStr">
         <is>
           <t>263238</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="71" t="inlineStr">
+      <c r="A12" s="72" t="inlineStr">
         <is>
           <t>qr</t>
         </is>
       </c>
-      <c r="B12" s="72" t="inlineStr">
+      <c r="B12" s="73" t="inlineStr">
         <is>
           <t>G32:H37</t>
         </is>
       </c>
-      <c r="C12" s="71" t="inlineStr">
+      <c r="C12" s="72" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D12" s="71" t="inlineStr">
+      <c r="D12" s="72" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E12" s="71" t="inlineStr">
+      <c r="E12" s="72" t="inlineStr">
         <is>
           <t>F3F5F5</t>
         </is>
       </c>
-      <c r="F12" s="71" t="inlineStr">
+      <c r="F12" s="72" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="71" t="inlineStr">
+      <c r="A13" s="72" t="inlineStr">
         <is>
           <t>plain</t>
         </is>
       </c>
-      <c r="B13" s="72" t="inlineStr">
-        <is>
-          <t>B39:D39,E39:F39,G39:H39</t>
-        </is>
-      </c>
-      <c r="C13" s="71" t="inlineStr">
+      <c r="B13" s="73" t="inlineStr">
+        <is>
+          <t>B42:D42,E42:F42,G42:H42</t>
+        </is>
+      </c>
+      <c r="C13" s="72" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D13" s="71" t="inlineStr">
+      <c r="D13" s="72" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E13" s="71" t="inlineStr">
+      <c r="E13" s="72" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="F13" s="71" t="inlineStr">
+      <c r="F13" s="72" t="inlineStr">
         <is>
           <t>263238</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="70" t="inlineStr">
+      <c r="A15" s="71" t="inlineStr">
         <is>
           <t>Служебная таблица. Макрос ПрименитьСхему читает её и перекрашивает лист КВИТАНЦИЯ. Цвета задаются шестью шестнадцатеричными знаками RRGGBB — правьте прямо здесь, код менять не нужно.</t>
         </is>
@@ -2585,186 +2625,186 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="73" t="inlineStr">
+      <c r="A1" s="74" t="inlineStr">
         <is>
           <t>КАК ВСТРОИТЬ ЭТОТ БЛАНК В СУЩЕСТВУЮЩУЮ ТАБЛИЦУ РАЗНОСКИ</t>
         </is>
       </c>
     </row>
     <row r="2" ht="8" customHeight="1">
-      <c r="A2" s="74" t="inlineStr"/>
+      <c r="A2" s="75" t="inlineStr"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="75" t="inlineStr">
+      <c r="A3" s="76" t="inlineStr">
         <is>
           <t>1. Перенос листов</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="76" t="inlineStr">
+      <c r="A4" s="77" t="inlineStr">
         <is>
           <t>Скопируйте в свою книгу (правый клик по ярлыку листа → Переместить/скопировать) листы КВИТАНЦИЯ, ДАННЫЕ, НАСТРОЙКИ и СХЕМА. Лист СХЕМА скрыт: чтобы увидеть его, нажмите правой кнопкой на любом ярлыке → Показать.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="76" t="inlineStr">
+      <c r="A5" s="77" t="inlineStr">
         <is>
           <t>Именованные диапазоны (КВ_ЛС, КВ_НАЧИСЛЕНО, КВ_ДОЛГ, КВ_ИТОГО и др.) переносятся вместе с листами. Проверьте их в Формулы → Диспетчер имён.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="76" t="inlineStr">
+      <c r="A6" s="77" t="inlineStr">
         <is>
           <t>Импортируйте модуль vba/modКвитанция.bas: Alt+F11 → File → Import File. Книгу сохраните как .xlsm.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="8" customHeight="1">
-      <c r="A7" s="74" t="inlineStr"/>
+      <c r="A7" s="75" t="inlineStr"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="75" t="inlineStr">
+      <c r="A8" s="76" t="inlineStr">
         <is>
           <t>2. Подключение разноски</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="76" t="inlineStr">
+      <c r="A9" s="77" t="inlineStr">
         <is>
           <t>Лист ДАННЫЕ — единственная точка стыковки. Ваш макрос разноски кладёт в него по одной строке на лицевой счёт за расчётный период. Ключ поиска — столбец A (лицевой счёт).</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="76" t="inlineStr">
+      <c r="A10" s="77" t="inlineStr">
         <is>
           <t>Если разноска уже лежит на другом листе, не копируйте её: пропишите в столбцах листа ДАННЫЕ обычные формулы-ссылки на этот лист (ВПР или ИНДЕКС+ПОИСКПОЗ). Бланк разницы не заметит.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="8" customHeight="1">
-      <c r="A11" s="74" t="inlineStr"/>
+      <c r="A11" s="75" t="inlineStr"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="75" t="inlineStr">
+      <c r="A12" s="76" t="inlineStr">
         <is>
           <t>3. Автоподстановка сумм</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="76" t="inlineStr">
+      <c r="A13" s="77" t="inlineStr">
         <is>
           <t>Достаточно записать лицевой счёт в ячейку КВИТАНЦИЯ!C14 (имя КВ_ЛС) — ФИО, адрес, площадь, начислено, долг и итог подтянутся формулами.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="76" t="inlineStr">
+      <c r="A14" s="77" t="inlineStr">
         <is>
           <t>Если суммы удобнее подавать напрямую из макроса, вызывайте процедуру ПодставитьСуммы: она пишет значения в лист ДАННЫЕ, а формулы бланка пересчитываются сами.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="76" t="inlineStr">
+      <c r="A15" s="77" t="inlineStr">
         <is>
           <t>ИТОГО К ОПЛАТЕ берётся из столбца J листа ДАННЫЕ. Если столбец пуст, бланк считает итог сам: начислено + долг + перерасчёт. Пени в этом доме не начисляются, поэтому строки под них в бланке нет.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="8" customHeight="1">
-      <c r="A16" s="74" t="inlineStr"/>
+      <c r="A16" s="75" t="inlineStr"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="75" t="inlineStr">
+      <c r="A17" s="76" t="inlineStr">
         <is>
           <t>4. Печать и PDF</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="76" t="inlineStr">
+      <c r="A18" s="77" t="inlineStr">
         <is>
           <t>Книга сохранена в чёрно-белой схеме — можно сразу печатать на А4: одна страница, поля 5 мм, вписано по ширине и высоте.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="76" t="inlineStr">
+      <c r="A19" s="77" t="inlineStr">
         <is>
           <t>Макрос ЭкспортКвитанцииВPDF временно переключает бланк в цветную схему, выгружает PDF и возвращает чёрно-белый вид. Файл для отправки жителю получается цветным, бумажная копия остаётся чёрно-белой.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="76" t="inlineStr">
+      <c r="A20" s="77" t="inlineStr">
         <is>
           <t>Макрос ПакетныйЭкспортPDF делает то же самое по всем лицевым счетам листа ДАННЫЕ и раскладывает файлы по выбранной папке.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="76" t="inlineStr">
+      <c r="A21" s="77" t="inlineStr">
         <is>
           <t>Макросы СхемаЧБ и СхемаЦвет переключают вид вручную — например, чтобы посмотреть, как квитанция будет выглядеть у жителя на экране.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="8" customHeight="1">
-      <c r="A22" s="74" t="inlineStr"/>
+      <c r="A22" s="75" t="inlineStr"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="75" t="inlineStr">
+      <c r="A23" s="76" t="inlineStr">
         <is>
           <t>5. QR-код</t>
         </is>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="76" t="inlineStr">
+      <c r="A24" s="77" t="inlineStr">
         <is>
           <t>Строка платежа по ГОСТ Р 56042-2014 собирается формулой на листе НАСТРОЙКИ (имя КВ_QR) и готова к передаче в любой генератор QR. Функция СтрокаQR возвращает её из VBA.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="76" t="inlineStr">
+      <c r="A25" s="77" t="inlineStr">
         <is>
           <t>Сама картинка QR в шаблон не встроена: вставьте изображение в область G32:H37 вручную либо подключите свой генератор в процедуре ВставитьQR (в модуле оставлена заготовка).</t>
         </is>
       </c>
     </row>
     <row r="26" ht="8" customHeight="1">
-      <c r="A26" s="74" t="inlineStr"/>
+      <c r="A26" s="75" t="inlineStr"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="75" t="inlineStr">
+      <c r="A27" s="76" t="inlineStr">
         <is>
           <t>6. Что проверить перед первой выдачей квитанций</t>
         </is>
       </c>
     </row>
     <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="76" t="inlineStr">
+      <c r="A28" s="77" t="inlineStr">
         <is>
           <t>• Размер взноса (руб./м²). В исходном файле он подтягивался из внешней книги, поэтому столбец F листа ДАННЫЕ оставлен пустым, а бланк восстанавливает тариф как начислено ÷ площадь. Впишите утверждённый тариф, чтобы в квитанции стояла точная величина.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="76" t="inlineStr">
+      <c r="A29" s="77" t="inlineStr">
         <is>
           <t>• Остаток средств на специальном счёте и накопления по лицевому счёту (столбцы L и M). Пока они пусты, в разделе 4 стоит прочерк.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="76" t="inlineStr">
+      <c r="A30" s="77" t="inlineStr">
         <is>
           <t>• Реквизиты специального счёта на листе НАСТРОЙКИ — они перенесены из вашего образца без изменений.</t>
         </is>

--- a/kapremont/output/Квитанция_КапРемонт_Омск_шаблон.xlsx
+++ b/kapremont/output/Квитанция_КапРемонт_Омск_шаблон.xlsx
@@ -47,7 +47,7 @@
     <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -90,7 +90,7 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="12"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -125,12 +125,6 @@
       <name val="Arial"/>
       <color rgb="00000000"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -390,7 +384,7 @@
   <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -503,13 +497,13 @@
     <xf numFmtId="4" fontId="11" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="14" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="4" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -557,7 +551,7 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -604,13 +598,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -996,10 +990,28 @@
   </cols>
   <sheetData>
     <row r="1" ht="6" customHeight="1"/>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="40" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>ВЗНОС НА КАПИТАЛЬНЫЙ РЕМОНТ ОБЩЕГО ИМУЩЕСТВА В МНОГОКВАРТИРНОМ ДОМЕ</t>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00FFFFFF"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">ПЛАТЁЖНЫЙ ДОКУМЕНТ (КВИТАНЦИЯ)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00FFFFFF"/>
+              <sz val="9"/>
+            </rPr>
+            <t>на внесение взноса на капитальный ремонт общего имущества в многоквартирном доме</t>
+          </r>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>

--- a/kapremont/output/Квитанция_КапРемонт_Омск_шаблон.xlsx
+++ b/kapremont/output/Квитанция_КапРемонт_Омск_шаблон.xlsx
@@ -47,7 +47,7 @@
     <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,7 +89,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00000000"/>
       <sz val="13"/>
     </font>
     <font>
@@ -102,18 +102,18 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
       <color rgb="00000000"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -134,6 +134,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00000000"/>
       <sz val="8"/>
@@ -151,7 +157,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -164,30 +170,12 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BFBFBF"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="14">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -266,13 +254,27 @@
       </bottom>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color rgb="00000000"/>
       </left>
       <right style="thin">
         <color rgb="00000000"/>
       </right>
-      <top style="medium">
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
         <color rgb="00000000"/>
       </top>
       <bottom style="thin">
@@ -283,13 +285,27 @@
       <left style="thin">
         <color rgb="00000000"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color rgb="00000000"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color rgb="00000000"/>
       </top>
       <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
         <color rgb="00000000"/>
       </bottom>
     </border>
@@ -300,24 +316,10 @@
       <right style="medium">
         <color rgb="00000000"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color rgb="00000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color rgb="00000000"/>
       </bottom>
     </border>
@@ -325,55 +327,13 @@
       <left style="thin">
         <color rgb="00000000"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color rgb="00000000"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="medium">
         <color rgb="00000000"/>
       </bottom>
     </border>
@@ -381,177 +341,171 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="11" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="9" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="11" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="9" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="14" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="15" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="11" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="9" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="11" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="9" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -598,13 +552,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -997,7 +951,7 @@
             <rPr>
               <rFont val="Arial"/>
               <b val="1"/>
-              <color rgb="00FFFFFF"/>
+              <color rgb="00000000"/>
               <sz val="13"/>
             </rPr>
             <t xml:space="preserve">ПЛАТЁЖНЫЙ ДОКУМЕНТ (КВИТАНЦИЯ)
@@ -1007,7 +961,7 @@
             <rPr>
               <rFont val="Arial"/>
               <b val="1"/>
-              <color rgb="00FFFFFF"/>
+              <color rgb="00000000"/>
               <sz val="9"/>
             </rPr>
             <t>на внесение взноса на капитальный ремонт общего имущества в многоквартирном доме</t>
@@ -1530,75 +1484,75 @@
       <c r="H36" s="49" t="n"/>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="B37" s="50">
+      <c r="B37" s="33">
         <f>"Срок оплаты: до "&amp;TEXT(DAY(IF(IFERROR(INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;TEXT(MONTH(IF(IFERROR(INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;YEAR(IF(IFERROR(INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))))&amp;" г."</f>
         <v/>
       </c>
-      <c r="C37" s="51" t="n"/>
-      <c r="D37" s="51" t="n"/>
-      <c r="E37" s="51" t="n"/>
-      <c r="F37" s="51" t="n"/>
-      <c r="G37" s="52" t="n"/>
-      <c r="H37" s="53" t="n"/>
+      <c r="C37" s="34" t="n"/>
+      <c r="D37" s="34" t="n"/>
+      <c r="E37" s="34" t="n"/>
+      <c r="F37" s="34" t="n"/>
+      <c r="G37" s="50" t="n"/>
+      <c r="H37" s="51" t="n"/>
     </row>
     <row r="38" ht="5" customHeight="1"/>
-    <row r="39" ht="30" customHeight="1">
-      <c r="B39" s="54">
+    <row r="39" ht="32" customHeight="1">
+      <c r="B39" s="52">
         <f>"ВНИМАНИЕ! ПЛАТИТЕ ТОЛЬКО ПО НОМЕРУ РАСЧЁТНОГО СЧЁТА "&amp;НАСТРОЙКИ!$B$7&amp;" — ЭТО СПЕЦИАЛЬНЫЙ СЧЁТ ВАШЕГО ДОМА"</f>
         <v/>
       </c>
-      <c r="C39" s="54" t="n"/>
-      <c r="D39" s="54" t="n"/>
-      <c r="E39" s="54" t="n"/>
-      <c r="F39" s="54" t="n"/>
-      <c r="G39" s="54" t="n"/>
-      <c r="H39" s="54" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+      <c r="E39" s="52" t="n"/>
+      <c r="F39" s="52" t="n"/>
+      <c r="G39" s="52" t="n"/>
+      <c r="H39" s="52" t="n"/>
     </row>
     <row r="40" ht="44" customHeight="1">
-      <c r="B40" s="55">
-        <f>"В отделении банка и в мобильном приложении выбирайте оплату по реквизитам — вкладку «Специальный счёт». Не платите через поиск «Капитальный ремонт»: такой платёж уходит на общий счёт Регионального фонда капитального ремонта и на счёт вашего дома не поступает."&amp;CHAR(10)&amp;"Лицевой счёт № "&amp;КВ_ЛС&amp;" при оплате НЕ вводится — он указан справочно, только для учёта начислений."</f>
-        <v/>
-      </c>
-      <c r="C40" s="55" t="n"/>
-      <c r="D40" s="55" t="n"/>
-      <c r="E40" s="55" t="n"/>
-      <c r="F40" s="55" t="n"/>
-      <c r="G40" s="55" t="n"/>
-      <c r="H40" s="55" t="n"/>
+      <c r="B40" s="53">
+        <f>"В отделении банка и в мобильном приложении во вкладках ищите "&amp;"«РФКР МКД_капремонт, оплата по расчётному счёту» и указывайте номер расчётного счёта, приведённый выше. Оплата через общий поиск «Капитальный ремонт» уходит на общий счёт Регионального фонда капитального ремонта и на счёт вашего дома не поступает."&amp;CHAR(10)&amp;"Лицевой счёт № "&amp;КВ_ЛС&amp;" при оплате НЕ вводится — он указан справочно, только для учёта начислений."</f>
+        <v/>
+      </c>
+      <c r="C40" s="53" t="n"/>
+      <c r="D40" s="53" t="n"/>
+      <c r="E40" s="53" t="n"/>
+      <c r="F40" s="53" t="n"/>
+      <c r="G40" s="53" t="n"/>
+      <c r="H40" s="53" t="n"/>
     </row>
     <row r="41" ht="6" customHeight="1"/>
     <row r="42" ht="24" customHeight="1">
-      <c r="B42" s="56" t="inlineStr">
+      <c r="B42" s="54" t="inlineStr">
         <is>
           <t>Подпись плательщика  ______________________</t>
         </is>
       </c>
-      <c r="C42" s="56" t="n"/>
-      <c r="D42" s="56" t="n"/>
-      <c r="E42" s="56" t="inlineStr">
+      <c r="C42" s="54" t="n"/>
+      <c r="D42" s="54" t="n"/>
+      <c r="E42" s="54" t="inlineStr">
         <is>
           <t>Кассир  ______________</t>
         </is>
       </c>
-      <c r="F42" s="56" t="n"/>
-      <c r="G42" s="56" t="inlineStr">
+      <c r="F42" s="54" t="n"/>
+      <c r="G42" s="54" t="inlineStr">
         <is>
           <t>Дата  ____________</t>
         </is>
       </c>
-      <c r="H42" s="56" t="n"/>
+      <c r="H42" s="54" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="B43" s="57">
+      <c r="B43" s="55">
         <f>"По вопросам начислений обращайтесь к председателю совета дома, тел. "&amp;НАСТРОЙКИ!$B$13&amp;".    Документ № "&amp;IF(IFERROR(INDEX(ДАННЫЕ!$Q:$Q,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="","—",INDEX(ДАННЫЕ!$Q:$Q,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="C43" s="57" t="n"/>
-      <c r="D43" s="57" t="n"/>
-      <c r="E43" s="57" t="n"/>
-      <c r="F43" s="57" t="n"/>
-      <c r="G43" s="57" t="n"/>
-      <c r="H43" s="57" t="n"/>
+      <c r="C43" s="55" t="n"/>
+      <c r="D43" s="55" t="n"/>
+      <c r="E43" s="55" t="n"/>
+      <c r="F43" s="55" t="n"/>
+      <c r="G43" s="55" t="n"/>
+      <c r="H43" s="55" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="48">
@@ -1677,301 +1631,301 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="56" t="inlineStr">
         <is>
           <t>Параметр</t>
         </is>
       </c>
-      <c r="B1" s="58" t="inlineStr">
+      <c r="B1" s="56" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C1" s="58" t="inlineStr">
+      <c r="C1" s="56" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="59" t="inlineStr">
+      <c r="A2" s="57" t="inlineStr">
         <is>
           <t>Получатель платежа</t>
         </is>
       </c>
-      <c r="B2" s="60" t="inlineStr">
+      <c r="B2" s="58" t="inlineStr">
         <is>
           <t>РЕГИОНАЛЬНЫЙ ФОНД КАПИТАЛЬНОГО РЕМОНТА МНОГОКВАРТИРНЫХ ДОМОВ ОМСКОЙ ОБЛАСТИ (СПЕЦ. СЧЕТ)</t>
         </is>
       </c>
-      <c r="C2" s="61" t="inlineStr">
+      <c r="C2" s="59" t="inlineStr">
         <is>
           <t>Владелец специального счёта МКД</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="59" t="inlineStr">
+      <c r="A3" s="57" t="inlineStr">
         <is>
           <t>Юридический адрес</t>
         </is>
       </c>
-      <c r="B3" s="60" t="inlineStr">
+      <c r="B3" s="58" t="inlineStr">
         <is>
           <t>644099, г. Омск, ул. Краснофлотская, 24</t>
         </is>
       </c>
-      <c r="C3" s="61" t="inlineStr">
+      <c r="C3" s="59" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="59" t="inlineStr">
+      <c r="A4" s="57" t="inlineStr">
         <is>
           <t>ИНН</t>
         </is>
       </c>
-      <c r="B4" s="60" t="inlineStr">
+      <c r="B4" s="58" t="inlineStr">
         <is>
           <t>5503239348</t>
         </is>
       </c>
-      <c r="C4" s="61" t="inlineStr">
+      <c r="C4" s="59" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="59" t="inlineStr">
+      <c r="A5" s="57" t="inlineStr">
         <is>
           <t>КПП</t>
         </is>
       </c>
-      <c r="B5" s="60" t="inlineStr">
+      <c r="B5" s="58" t="inlineStr">
         <is>
           <t>550301001</t>
         </is>
       </c>
-      <c r="C5" s="61" t="inlineStr">
+      <c r="C5" s="59" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr">
+      <c r="A6" s="57" t="inlineStr">
         <is>
           <t>ОГРН</t>
         </is>
       </c>
-      <c r="B6" s="60" t="inlineStr">
+      <c r="B6" s="58" t="inlineStr">
         <is>
           <t>1027700342890</t>
         </is>
       </c>
-      <c r="C6" s="61" t="inlineStr">
+      <c r="C6" s="59" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="59" t="inlineStr">
+      <c r="A7" s="57" t="inlineStr">
         <is>
           <t>Расчётный счёт (спец. счёт МКД)</t>
         </is>
       </c>
-      <c r="B7" s="60" t="inlineStr">
+      <c r="B7" s="58" t="inlineStr">
         <is>
           <t>40604810809000000154</t>
         </is>
       </c>
-      <c r="C7" s="61" t="inlineStr">
+      <c r="C7" s="59" t="inlineStr">
         <is>
           <t>Специальный счёт дома по ул. Магистральная, 2</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="59" t="inlineStr">
+      <c r="A8" s="57" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
       </c>
-      <c r="B8" s="60" t="inlineStr">
+      <c r="B8" s="58" t="inlineStr">
         <is>
           <t>Омский РФ АО «Россельхозбанк»</t>
         </is>
       </c>
-      <c r="C8" s="61" t="inlineStr">
+      <c r="C8" s="59" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="59" t="inlineStr">
+      <c r="A9" s="57" t="inlineStr">
         <is>
           <t>Корреспондентский счёт</t>
         </is>
       </c>
-      <c r="B9" s="60" t="inlineStr">
+      <c r="B9" s="58" t="inlineStr">
         <is>
           <t>30101810900000000822</t>
         </is>
       </c>
-      <c r="C9" s="61" t="inlineStr">
+      <c r="C9" s="59" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="59" t="inlineStr">
+      <c r="A10" s="57" t="inlineStr">
         <is>
           <t>БИК</t>
         </is>
       </c>
-      <c r="B10" s="60" t="inlineStr">
+      <c r="B10" s="58" t="inlineStr">
         <is>
           <t>045209822</t>
         </is>
       </c>
-      <c r="C10" s="61" t="inlineStr">
+      <c r="C10" s="59" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="59" t="inlineStr">
+      <c r="A11" s="57" t="inlineStr">
         <is>
           <t>ИНН/КПП банка</t>
         </is>
       </c>
-      <c r="B11" s="60" t="inlineStr">
+      <c r="B11" s="58" t="inlineStr">
         <is>
           <t>7725114488 / 550502001</t>
         </is>
       </c>
-      <c r="C11" s="61" t="inlineStr">
+      <c r="C11" s="59" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="59" t="inlineStr">
+      <c r="A12" s="57" t="inlineStr">
         <is>
           <t>Адрес МКД</t>
         </is>
       </c>
-      <c r="B12" s="60" t="inlineStr">
+      <c r="B12" s="58" t="inlineStr">
         <is>
           <t>г. Омск, ул. Магистральная, 2</t>
         </is>
       </c>
-      <c r="C12" s="61" t="inlineStr">
+      <c r="C12" s="59" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="59" t="inlineStr">
+      <c r="A13" s="57" t="inlineStr">
         <is>
           <t>Контактный телефон</t>
         </is>
       </c>
-      <c r="B13" s="60" t="inlineStr">
+      <c r="B13" s="58" t="inlineStr">
         <is>
           <t>8 908 108 02 00</t>
         </is>
       </c>
-      <c r="C13" s="61" t="inlineStr">
+      <c r="C13" s="59" t="inlineStr">
         <is>
           <t>Председатель совета дома</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="59" t="inlineStr">
+      <c r="A14" s="57" t="inlineStr">
         <is>
           <t>Расчётный период (текст)</t>
         </is>
       </c>
-      <c r="B14" s="60" t="inlineStr">
+      <c r="B14" s="58" t="inlineStr">
         <is>
           <t>Июль 2026</t>
         </is>
       </c>
-      <c r="C14" s="61" t="inlineStr">
+      <c r="C14" s="59" t="inlineStr">
         <is>
           <t>Подставляется в заголовок и в назначение платежа</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="59" t="inlineStr">
+      <c r="A15" s="57" t="inlineStr">
         <is>
           <t>Дата начала периода</t>
         </is>
       </c>
-      <c r="B15" s="62" t="n">
+      <c r="B15" s="60" t="n">
         <v>46204</v>
       </c>
-      <c r="C15" s="61" t="inlineStr">
+      <c r="C15" s="59" t="inlineStr">
         <is>
           <t>Первое число расчётного месяца</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="59" t="inlineStr">
+      <c r="A16" s="57" t="inlineStr">
         <is>
           <t>Срок оплаты</t>
         </is>
       </c>
-      <c r="B16" s="62" t="n">
+      <c r="B16" s="60" t="n">
         <v>46244</v>
       </c>
-      <c r="C16" s="61" t="inlineStr">
+      <c r="C16" s="59" t="inlineStr">
         <is>
           <t>До какого числа вносится взнос</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="59" t="inlineStr">
+      <c r="A17" s="57" t="inlineStr">
         <is>
           <t>Текущая цветовая схема</t>
         </is>
       </c>
-      <c r="B17" s="60" t="inlineStr">
+      <c r="B17" s="58" t="inlineStr">
         <is>
           <t>ЧБ</t>
         </is>
       </c>
-      <c r="C17" s="61" t="inlineStr">
+      <c r="C17" s="59" t="inlineStr">
         <is>
           <t>ЧБ — для печати на А4; ЦВЕТ — для выгрузки в PDF. Переключается макросом</t>
         </is>
       </c>
     </row>
     <row r="20" ht="64" customHeight="1">
-      <c r="A20" s="63" t="inlineStr">
+      <c r="A20" s="61" t="inlineStr">
         <is>
           <t>Строка QR (ГОСТ Р 56042-2014)</t>
         </is>
       </c>
-      <c r="B20" s="64">
+      <c r="B20" s="62">
         <f>"ST00012|Name="&amp;НАСТРОЙКИ!$B$2&amp;"|PersonalAcc="&amp;НАСТРОЙКИ!$B$7&amp;"|BankName="&amp;НАСТРОЙКИ!$B$8&amp;"|BIC="&amp;НАСТРОЙКИ!$B$10&amp;"|CorrespAcc="&amp;НАСТРОЙКИ!$B$9&amp;"|PayeeINN="&amp;НАСТРОЙКИ!$B$4&amp;"|KPP="&amp;НАСТРОЙКИ!$B$5&amp;"|Sum="&amp;TEXT(ROUND(КВ_ИТОГО*100,0),"0")&amp;"|Purpose=Взнос на капитальный ремонт за "&amp;НАСТРОЙКИ!$B$14&amp;", л/с "&amp;КВ_ЛС&amp;"|PersAcc="&amp;КВ_ЛС&amp;"|PayerAddress="&amp;КВ_АДРЕС</f>
         <v/>
       </c>
-      <c r="C20" s="65" t="inlineStr">
+      <c r="C20" s="63" t="inlineStr">
         <is>
           <t>Сумма — в копейках, как требует стандарт. Значение читается макросом (функция СтрокаQR) и передаётся в генератор QR-кода.</t>
         </is>
@@ -2011,149 +1965,149 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="66" t="inlineStr">
+      <c r="A1" s="64" t="inlineStr">
         <is>
           <t>Лицевой счёт</t>
         </is>
       </c>
-      <c r="B1" s="66" t="inlineStr">
+      <c r="B1" s="64" t="inlineStr">
         <is>
           <t>Квартира</t>
         </is>
       </c>
-      <c r="C1" s="66" t="inlineStr">
+      <c r="C1" s="64" t="inlineStr">
         <is>
           <t>ФИО собственника</t>
         </is>
       </c>
-      <c r="D1" s="66" t="inlineStr">
+      <c r="D1" s="64" t="inlineStr">
         <is>
           <t>Адрес помещения</t>
         </is>
       </c>
-      <c r="E1" s="66" t="inlineStr">
+      <c r="E1" s="64" t="inlineStr">
         <is>
           <t>Площадь, м²</t>
         </is>
       </c>
-      <c r="F1" s="66" t="inlineStr">
+      <c r="F1" s="64" t="inlineStr">
         <is>
           <t>Размер взноса, руб./м²</t>
         </is>
       </c>
-      <c r="G1" s="66" t="inlineStr">
+      <c r="G1" s="64" t="inlineStr">
         <is>
           <t>Начислено за период, руб.</t>
         </is>
       </c>
-      <c r="H1" s="66" t="inlineStr">
+      <c r="H1" s="64" t="inlineStr">
         <is>
           <t>Задолженность на начало периода, руб.</t>
         </is>
       </c>
-      <c r="I1" s="66" t="inlineStr">
+      <c r="I1" s="64" t="inlineStr">
         <is>
           <t>Перерасчёт / переплата, руб.</t>
         </is>
       </c>
-      <c r="J1" s="66" t="inlineStr">
+      <c r="J1" s="64" t="inlineStr">
         <is>
           <t>ИТОГО к оплате, руб.</t>
         </is>
       </c>
-      <c r="K1" s="66" t="inlineStr">
+      <c r="K1" s="64" t="inlineStr">
         <is>
           <t>Оплачено с начала года, руб.</t>
         </is>
       </c>
-      <c r="L1" s="66" t="inlineStr">
+      <c r="L1" s="64" t="inlineStr">
         <is>
           <t>Остаток на спец. счёте МКД, руб.</t>
         </is>
       </c>
-      <c r="M1" s="66" t="inlineStr">
+      <c r="M1" s="64" t="inlineStr">
         <is>
           <t>Накоплено по лицевому счёту, руб.</t>
         </is>
       </c>
-      <c r="N1" s="66" t="inlineStr">
+      <c r="N1" s="64" t="inlineStr">
         <is>
           <t>Расчётный период (текст)</t>
         </is>
       </c>
-      <c r="O1" s="66" t="inlineStr">
+      <c r="O1" s="64" t="inlineStr">
         <is>
           <t>Дата начала периода</t>
         </is>
       </c>
-      <c r="P1" s="66" t="inlineStr">
+      <c r="P1" s="64" t="inlineStr">
         <is>
           <t>Срок оплаты</t>
         </is>
       </c>
-      <c r="Q1" s="66" t="inlineStr">
+      <c r="Q1" s="64" t="inlineStr">
         <is>
           <t>№ квитанции</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n">
+      <c r="A2" s="65" t="n">
         <v>31202</v>
       </c>
-      <c r="B2" s="67" t="n">
+      <c r="B2" s="65" t="n">
         <v>49</v>
       </c>
-      <c r="C2" s="67" t="inlineStr">
+      <c r="C2" s="65" t="inlineStr">
         <is>
           <t>Иванов Иван Иванович</t>
         </is>
       </c>
-      <c r="D2" s="67" t="inlineStr">
+      <c r="D2" s="65" t="inlineStr">
         <is>
           <t>г. Омск, ул. Магистральная, 2, кв. 49</t>
         </is>
       </c>
-      <c r="E2" s="68" t="n">
+      <c r="E2" s="66" t="n">
         <v>63.1</v>
       </c>
-      <c r="F2" s="69" t="n"/>
-      <c r="G2" s="69" t="n">
+      <c r="F2" s="67" t="n"/>
+      <c r="G2" s="67" t="n">
         <v>674.99</v>
       </c>
-      <c r="H2" s="69" t="n">
+      <c r="H2" s="67" t="n">
         <v>19501.38</v>
       </c>
-      <c r="I2" s="69" t="n">
+      <c r="I2" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="69" t="n">
+      <c r="J2" s="67" t="n">
         <v>20176.37</v>
       </c>
-      <c r="K2" s="69" t="n">
+      <c r="K2" s="67" t="n">
         <v>13441.28</v>
       </c>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="67" t="inlineStr">
+      <c r="L2" s="67" t="n"/>
+      <c r="M2" s="67" t="n"/>
+      <c r="N2" s="65" t="inlineStr">
         <is>
           <t>Июль 2026</t>
         </is>
       </c>
-      <c r="O2" s="70" t="n">
+      <c r="O2" s="68" t="n">
         <v>46204</v>
       </c>
-      <c r="P2" s="70" t="n">
+      <c r="P2" s="68" t="n">
         <v>46244</v>
       </c>
-      <c r="Q2" s="67" t="inlineStr">
+      <c r="Q2" s="65" t="inlineStr">
         <is>
           <t>КР-2026-07-31202</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="71" t="inlineStr">
+      <c r="A4" s="69" t="inlineStr">
         <is>
           <t>Строка 2 — пример из образца. Ниже макрос разноски дописывает по одной строке на лицевой счёт за расчётный период. Ключ поиска — столбец A (лицевой счёт): по нему лист КВИТАНЦИЯ подтягивает все значения формулами ИНДЕКС/ПОИСКПОЗ. Столбцы F, J, L, M можно оставить пустыми — бланк рассчитает их сам либо поставит прочерк.</t>
         </is>
@@ -2188,423 +2142,423 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="66" t="inlineStr">
+      <c r="A1" s="64" t="inlineStr">
         <is>
           <t>Роль</t>
         </is>
       </c>
-      <c r="B1" s="66" t="inlineStr">
+      <c r="B1" s="64" t="inlineStr">
         <is>
           <t>Диапазоны (через запятую)</t>
         </is>
       </c>
-      <c r="C1" s="66" t="inlineStr">
+      <c r="C1" s="64" t="inlineStr">
         <is>
           <t>ЧБ: заливка</t>
         </is>
       </c>
-      <c r="D1" s="66" t="inlineStr">
+      <c r="D1" s="64" t="inlineStr">
         <is>
           <t>ЧБ: шрифт</t>
         </is>
       </c>
-      <c r="E1" s="66" t="inlineStr">
+      <c r="E1" s="64" t="inlineStr">
         <is>
           <t>ЦВЕТ: заливка</t>
         </is>
       </c>
-      <c r="F1" s="66" t="inlineStr">
+      <c r="F1" s="64" t="inlineStr">
         <is>
           <t>ЦВЕТ: шрифт</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="72" t="inlineStr">
+      <c r="A2" s="70" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B2" s="73" t="inlineStr">
+      <c r="B2" s="71" t="inlineStr">
         <is>
           <t>B2:H2</t>
         </is>
       </c>
-      <c r="C2" s="72" t="inlineStr">
+      <c r="C2" s="70" t="inlineStr">
+        <is>
+          <t>FFFFFF</t>
+        </is>
+      </c>
+      <c r="D2" s="70" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="D2" s="72" t="inlineStr">
+      <c r="E2" s="70" t="inlineStr">
+        <is>
+          <t>0F6B70</t>
+        </is>
+      </c>
+      <c r="F2" s="70" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="E2" s="72" t="inlineStr">
+    </row>
+    <row r="3">
+      <c r="A3" s="70" t="inlineStr">
+        <is>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="B3" s="71" t="inlineStr">
+        <is>
+          <t>B3:E3,F3:H3</t>
+        </is>
+      </c>
+      <c r="C3" s="70" t="inlineStr">
+        <is>
+          <t>FFFFFF</t>
+        </is>
+      </c>
+      <c r="D3" s="70" t="inlineStr">
+        <is>
+          <t>000000</t>
+        </is>
+      </c>
+      <c r="E3" s="70" t="inlineStr">
+        <is>
+          <t>DDEFF0</t>
+        </is>
+      </c>
+      <c r="F3" s="70" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
-      <c r="F2" s="72" t="inlineStr">
+    </row>
+    <row r="4">
+      <c r="A4" s="70" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="B4" s="71" t="inlineStr">
+        <is>
+          <t>B5:H5,B13:H13,B19:H19,B26:H26,B31:H31</t>
+        </is>
+      </c>
+      <c r="C4" s="70" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="72" t="inlineStr">
-        <is>
-          <t>subtitle</t>
-        </is>
-      </c>
-      <c r="B3" s="73" t="inlineStr">
-        <is>
-          <t>B3:E3,F3:H3</t>
-        </is>
-      </c>
-      <c r="C3" s="72" t="inlineStr">
+      <c r="D4" s="70" t="inlineStr">
+        <is>
+          <t>000000</t>
+        </is>
+      </c>
+      <c r="E4" s="70" t="inlineStr">
+        <is>
+          <t>0F6B70</t>
+        </is>
+      </c>
+      <c r="F4" s="70" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D3" s="72" t="inlineStr">
+    </row>
+    <row r="5">
+      <c r="A5" s="70" t="inlineStr">
+        <is>
+          <t>thead</t>
+        </is>
+      </c>
+      <c r="B5" s="71" t="inlineStr">
+        <is>
+          <t>B20:E20,F20:G20,H20</t>
+        </is>
+      </c>
+      <c r="C5" s="70" t="inlineStr">
+        <is>
+          <t>FFFFFF</t>
+        </is>
+      </c>
+      <c r="D5" s="70" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E3" s="72" t="inlineStr">
-        <is>
-          <t>DDEFF0</t>
-        </is>
-      </c>
-      <c r="F3" s="72" t="inlineStr">
+      <c r="E5" s="70" t="inlineStr">
+        <is>
+          <t>263238</t>
+        </is>
+      </c>
+      <c r="F5" s="70" t="inlineStr">
+        <is>
+          <t>FFFFFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="70" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="B6" s="71" t="inlineStr">
+        <is>
+          <t>B6,B7,B8,E8,B9,B10,B11,E11,B14,D14,F14,B15,B16,B17,D17,F17,B35:F35</t>
+        </is>
+      </c>
+      <c r="C6" s="70" t="inlineStr">
+        <is>
+          <t>FFFFFF</t>
+        </is>
+      </c>
+      <c r="D6" s="70" t="inlineStr">
+        <is>
+          <t>000000</t>
+        </is>
+      </c>
+      <c r="E6" s="70" t="inlineStr">
+        <is>
+          <t>F3F5F5</t>
+        </is>
+      </c>
+      <c r="F6" s="70" t="inlineStr">
+        <is>
+          <t>263238</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="70" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="B7" s="71" t="inlineStr">
+        <is>
+          <t>C6:H6,C7:H7,C8:D8,F8:H8,C9:H9,C10:H10,C11:D11,F11:H11,E14,G14:H14,C15:H15,C16:H16,C17,E17,G17:H17,B21:E21,F21:G21,H21,B22:E22,F22:G22,H22,B23:E23,F23:G23,H23,B27:F27,G27:H27,B28:F28,G28:H28,B29:F29,G29:H29,B32:F32,B33:F33,B34:F34,B36:F36,B43:H43</t>
+        </is>
+      </c>
+      <c r="C7" s="70" t="inlineStr">
+        <is>
+          <t>FFFFFF</t>
+        </is>
+      </c>
+      <c r="D7" s="70" t="inlineStr">
+        <is>
+          <t>000000</t>
+        </is>
+      </c>
+      <c r="E7" s="70" t="inlineStr">
+        <is>
+          <t>FFFFFF</t>
+        </is>
+      </c>
+      <c r="F7" s="70" t="inlineStr">
+        <is>
+          <t>263238</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="70" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="B8" s="71" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="C8" s="70" t="inlineStr">
+        <is>
+          <t>FFFFFF</t>
+        </is>
+      </c>
+      <c r="D8" s="70" t="inlineStr">
+        <is>
+          <t>000000</t>
+        </is>
+      </c>
+      <c r="E8" s="70" t="inlineStr">
+        <is>
+          <t>E8F3F3</t>
+        </is>
+      </c>
+      <c r="F8" s="70" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="72" t="inlineStr">
-        <is>
-          <t>section</t>
-        </is>
-      </c>
-      <c r="B4" s="73" t="inlineStr">
-        <is>
-          <t>B5:H5,B13:H13,B19:H19,B26:H26,B31:H31</t>
-        </is>
-      </c>
-      <c r="C4" s="72" t="inlineStr">
-        <is>
-          <t>D9D9D9</t>
-        </is>
-      </c>
-      <c r="D4" s="72" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="70" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="B9" s="71" t="inlineStr">
+        <is>
+          <t>B24:G24,B39:H39</t>
+        </is>
+      </c>
+      <c r="C9" s="70" t="inlineStr">
+        <is>
+          <t>FFFFFF</t>
+        </is>
+      </c>
+      <c r="D9" s="70" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E4" s="72" t="inlineStr">
+      <c r="E9" s="70" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
-      <c r="F4" s="72" t="inlineStr">
+      <c r="F9" s="70" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="72" t="inlineStr">
-        <is>
-          <t>thead</t>
-        </is>
-      </c>
-      <c r="B5" s="73" t="inlineStr">
-        <is>
-          <t>B20:E20,F20:G20,H20</t>
-        </is>
-      </c>
-      <c r="C5" s="72" t="inlineStr">
-        <is>
-          <t>BFBFBF</t>
-        </is>
-      </c>
-      <c r="D5" s="72" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="70" t="inlineStr">
+        <is>
+          <t>totalsum</t>
+        </is>
+      </c>
+      <c r="B10" s="71" t="inlineStr">
+        <is>
+          <t>H24</t>
+        </is>
+      </c>
+      <c r="C10" s="70" t="inlineStr">
+        <is>
+          <t>FFFFFF</t>
+        </is>
+      </c>
+      <c r="D10" s="70" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E5" s="72" t="inlineStr">
+      <c r="E10" s="70" t="inlineStr">
+        <is>
+          <t>E8F3F3</t>
+        </is>
+      </c>
+      <c r="F10" s="70" t="inlineStr">
+        <is>
+          <t>0F6B70</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="70" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B11" s="71" t="inlineStr">
+        <is>
+          <t>B37:F37,B40:H40</t>
+        </is>
+      </c>
+      <c r="C11" s="70" t="inlineStr">
+        <is>
+          <t>FFFFFF</t>
+        </is>
+      </c>
+      <c r="D11" s="70" t="inlineStr">
+        <is>
+          <t>000000</t>
+        </is>
+      </c>
+      <c r="E11" s="70" t="inlineStr">
+        <is>
+          <t>E8F3F3</t>
+        </is>
+      </c>
+      <c r="F11" s="70" t="inlineStr">
         <is>
           <t>263238</t>
         </is>
       </c>
-      <c r="F5" s="72" t="inlineStr">
+    </row>
+    <row r="12">
+      <c r="A12" s="70" t="inlineStr">
+        <is>
+          <t>qr</t>
+        </is>
+      </c>
+      <c r="B12" s="71" t="inlineStr">
+        <is>
+          <t>G32:H37</t>
+        </is>
+      </c>
+      <c r="C12" s="70" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="72" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-      <c r="B6" s="73" t="inlineStr">
-        <is>
-          <t>B6,B7,B8,E8,B9,B10,B11,E11,B14,D14,F14,B15,B16,B17,D17,F17,B35:F35</t>
-        </is>
-      </c>
-      <c r="C6" s="72" t="inlineStr">
-        <is>
-          <t>F2F2F2</t>
-        </is>
-      </c>
-      <c r="D6" s="72" t="inlineStr">
+      <c r="D12" s="70" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E6" s="72" t="inlineStr">
+      <c r="E12" s="70" t="inlineStr">
         <is>
           <t>F3F5F5</t>
         </is>
       </c>
-      <c r="F6" s="72" t="inlineStr">
+      <c r="F12" s="70" t="inlineStr">
+        <is>
+          <t>0F6B70</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="70" t="inlineStr">
+        <is>
+          <t>plain</t>
+        </is>
+      </c>
+      <c r="B13" s="71" t="inlineStr">
+        <is>
+          <t>B42:D42,E42:F42,G42:H42</t>
+        </is>
+      </c>
+      <c r="C13" s="70" t="inlineStr">
+        <is>
+          <t>FFFFFF</t>
+        </is>
+      </c>
+      <c r="D13" s="70" t="inlineStr">
+        <is>
+          <t>000000</t>
+        </is>
+      </c>
+      <c r="E13" s="70" t="inlineStr">
+        <is>
+          <t>FFFFFF</t>
+        </is>
+      </c>
+      <c r="F13" s="70" t="inlineStr">
         <is>
           <t>263238</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="72" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="B7" s="73" t="inlineStr">
-        <is>
-          <t>C6:H6,C7:H7,C8:D8,F8:H8,C9:H9,C10:H10,C11:D11,F11:H11,E14,G14:H14,C15:H15,C16:H16,C17,E17,G17:H17,B21:E21,F21:G21,H21,B22:E22,F22:G22,H22,B23:E23,F23:G23,H23,B27:F27,G27:H27,B28:F28,G28:H28,B29:F29,G29:H29,B32:F32,B33:F33,B34:F34,B36:F36,B43:H43</t>
-        </is>
-      </c>
-      <c r="C7" s="72" t="inlineStr">
-        <is>
-          <t>FFFFFF</t>
-        </is>
-      </c>
-      <c r="D7" s="72" t="inlineStr">
-        <is>
-          <t>000000</t>
-        </is>
-      </c>
-      <c r="E7" s="72" t="inlineStr">
-        <is>
-          <t>FFFFFF</t>
-        </is>
-      </c>
-      <c r="F7" s="72" t="inlineStr">
-        <is>
-          <t>263238</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="72" t="inlineStr">
-        <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="B8" s="73" t="inlineStr">
-        <is>
-          <t>C14</t>
-        </is>
-      </c>
-      <c r="C8" s="72" t="inlineStr">
-        <is>
-          <t>FFFFFF</t>
-        </is>
-      </c>
-      <c r="D8" s="72" t="inlineStr">
-        <is>
-          <t>000000</t>
-        </is>
-      </c>
-      <c r="E8" s="72" t="inlineStr">
-        <is>
-          <t>E8F3F3</t>
-        </is>
-      </c>
-      <c r="F8" s="72" t="inlineStr">
-        <is>
-          <t>0F6B70</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="72" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="B9" s="73" t="inlineStr">
-        <is>
-          <t>B24:G24,B39:H39</t>
-        </is>
-      </c>
-      <c r="C9" s="72" t="inlineStr">
-        <is>
-          <t>000000</t>
-        </is>
-      </c>
-      <c r="D9" s="72" t="inlineStr">
-        <is>
-          <t>FFFFFF</t>
-        </is>
-      </c>
-      <c r="E9" s="72" t="inlineStr">
-        <is>
-          <t>0F6B70</t>
-        </is>
-      </c>
-      <c r="F9" s="72" t="inlineStr">
-        <is>
-          <t>FFFFFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="72" t="inlineStr">
-        <is>
-          <t>totalsum</t>
-        </is>
-      </c>
-      <c r="B10" s="73" t="inlineStr">
-        <is>
-          <t>H24</t>
-        </is>
-      </c>
-      <c r="C10" s="72" t="inlineStr">
-        <is>
-          <t>FFFFFF</t>
-        </is>
-      </c>
-      <c r="D10" s="72" t="inlineStr">
-        <is>
-          <t>000000</t>
-        </is>
-      </c>
-      <c r="E10" s="72" t="inlineStr">
-        <is>
-          <t>E8F3F3</t>
-        </is>
-      </c>
-      <c r="F10" s="72" t="inlineStr">
-        <is>
-          <t>0F6B70</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="72" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B11" s="73" t="inlineStr">
-        <is>
-          <t>B37:F37,B40:H40</t>
-        </is>
-      </c>
-      <c r="C11" s="72" t="inlineStr">
-        <is>
-          <t>F2F2F2</t>
-        </is>
-      </c>
-      <c r="D11" s="72" t="inlineStr">
-        <is>
-          <t>000000</t>
-        </is>
-      </c>
-      <c r="E11" s="72" t="inlineStr">
-        <is>
-          <t>E8F3F3</t>
-        </is>
-      </c>
-      <c r="F11" s="72" t="inlineStr">
-        <is>
-          <t>263238</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="72" t="inlineStr">
-        <is>
-          <t>qr</t>
-        </is>
-      </c>
-      <c r="B12" s="73" t="inlineStr">
-        <is>
-          <t>G32:H37</t>
-        </is>
-      </c>
-      <c r="C12" s="72" t="inlineStr">
-        <is>
-          <t>FFFFFF</t>
-        </is>
-      </c>
-      <c r="D12" s="72" t="inlineStr">
-        <is>
-          <t>000000</t>
-        </is>
-      </c>
-      <c r="E12" s="72" t="inlineStr">
-        <is>
-          <t>F3F5F5</t>
-        </is>
-      </c>
-      <c r="F12" s="72" t="inlineStr">
-        <is>
-          <t>0F6B70</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="72" t="inlineStr">
-        <is>
-          <t>plain</t>
-        </is>
-      </c>
-      <c r="B13" s="73" t="inlineStr">
-        <is>
-          <t>B42:D42,E42:F42,G42:H42</t>
-        </is>
-      </c>
-      <c r="C13" s="72" t="inlineStr">
-        <is>
-          <t>FFFFFF</t>
-        </is>
-      </c>
-      <c r="D13" s="72" t="inlineStr">
-        <is>
-          <t>000000</t>
-        </is>
-      </c>
-      <c r="E13" s="72" t="inlineStr">
-        <is>
-          <t>FFFFFF</t>
-        </is>
-      </c>
-      <c r="F13" s="72" t="inlineStr">
-        <is>
-          <t>263238</t>
-        </is>
-      </c>
-    </row>
     <row r="15">
-      <c r="A15" s="71" t="inlineStr">
+      <c r="A15" s="69" t="inlineStr">
         <is>
           <t>Служебная таблица. Макрос ПрименитьСхему читает её и перекрашивает лист КВИТАНЦИЯ. Цвета задаются шестью шестнадцатеричными знаками RRGGBB — правьте прямо здесь, код менять не нужно.</t>
         </is>
@@ -2637,186 +2591,186 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="74" t="inlineStr">
+      <c r="A1" s="72" t="inlineStr">
         <is>
           <t>КАК ВСТРОИТЬ ЭТОТ БЛАНК В СУЩЕСТВУЮЩУЮ ТАБЛИЦУ РАЗНОСКИ</t>
         </is>
       </c>
     </row>
     <row r="2" ht="8" customHeight="1">
-      <c r="A2" s="75" t="inlineStr"/>
+      <c r="A2" s="73" t="inlineStr"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="76" t="inlineStr">
+      <c r="A3" s="74" t="inlineStr">
         <is>
           <t>1. Перенос листов</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="77" t="inlineStr">
+      <c r="A4" s="75" t="inlineStr">
         <is>
           <t>Скопируйте в свою книгу (правый клик по ярлыку листа → Переместить/скопировать) листы КВИТАНЦИЯ, ДАННЫЕ, НАСТРОЙКИ и СХЕМА. Лист СХЕМА скрыт: чтобы увидеть его, нажмите правой кнопкой на любом ярлыке → Показать.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="77" t="inlineStr">
+      <c r="A5" s="75" t="inlineStr">
         <is>
           <t>Именованные диапазоны (КВ_ЛС, КВ_НАЧИСЛЕНО, КВ_ДОЛГ, КВ_ИТОГО и др.) переносятся вместе с листами. Проверьте их в Формулы → Диспетчер имён.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="77" t="inlineStr">
+      <c r="A6" s="75" t="inlineStr">
         <is>
           <t>Импортируйте модуль vba/modКвитанция.bas: Alt+F11 → File → Import File. Книгу сохраните как .xlsm.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="8" customHeight="1">
-      <c r="A7" s="75" t="inlineStr"/>
+      <c r="A7" s="73" t="inlineStr"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="76" t="inlineStr">
+      <c r="A8" s="74" t="inlineStr">
         <is>
           <t>2. Подключение разноски</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="77" t="inlineStr">
+      <c r="A9" s="75" t="inlineStr">
         <is>
           <t>Лист ДАННЫЕ — единственная точка стыковки. Ваш макрос разноски кладёт в него по одной строке на лицевой счёт за расчётный период. Ключ поиска — столбец A (лицевой счёт).</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="77" t="inlineStr">
+      <c r="A10" s="75" t="inlineStr">
         <is>
           <t>Если разноска уже лежит на другом листе, не копируйте её: пропишите в столбцах листа ДАННЫЕ обычные формулы-ссылки на этот лист (ВПР или ИНДЕКС+ПОИСКПОЗ). Бланк разницы не заметит.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="8" customHeight="1">
-      <c r="A11" s="75" t="inlineStr"/>
+      <c r="A11" s="73" t="inlineStr"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="76" t="inlineStr">
+      <c r="A12" s="74" t="inlineStr">
         <is>
           <t>3. Автоподстановка сумм</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="77" t="inlineStr">
+      <c r="A13" s="75" t="inlineStr">
         <is>
           <t>Достаточно записать лицевой счёт в ячейку КВИТАНЦИЯ!C14 (имя КВ_ЛС) — ФИО, адрес, площадь, начислено, долг и итог подтянутся формулами.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="77" t="inlineStr">
+      <c r="A14" s="75" t="inlineStr">
         <is>
           <t>Если суммы удобнее подавать напрямую из макроса, вызывайте процедуру ПодставитьСуммы: она пишет значения в лист ДАННЫЕ, а формулы бланка пересчитываются сами.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="77" t="inlineStr">
+      <c r="A15" s="75" t="inlineStr">
         <is>
           <t>ИТОГО К ОПЛАТЕ берётся из столбца J листа ДАННЫЕ. Если столбец пуст, бланк считает итог сам: начислено + долг + перерасчёт. Пени в этом доме не начисляются, поэтому строки под них в бланке нет.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="8" customHeight="1">
-      <c r="A16" s="75" t="inlineStr"/>
+      <c r="A16" s="73" t="inlineStr"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="76" t="inlineStr">
+      <c r="A17" s="74" t="inlineStr">
         <is>
           <t>4. Печать и PDF</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="77" t="inlineStr">
+      <c r="A18" s="75" t="inlineStr">
         <is>
           <t>Книга сохранена в чёрно-белой схеме — можно сразу печатать на А4: одна страница, поля 5 мм, вписано по ширине и высоте.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="77" t="inlineStr">
+      <c r="A19" s="75" t="inlineStr">
         <is>
           <t>Макрос ЭкспортКвитанцииВPDF временно переключает бланк в цветную схему, выгружает PDF и возвращает чёрно-белый вид. Файл для отправки жителю получается цветным, бумажная копия остаётся чёрно-белой.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="77" t="inlineStr">
+      <c r="A20" s="75" t="inlineStr">
         <is>
           <t>Макрос ПакетныйЭкспортPDF делает то же самое по всем лицевым счетам листа ДАННЫЕ и раскладывает файлы по выбранной папке.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="77" t="inlineStr">
+      <c r="A21" s="75" t="inlineStr">
         <is>
           <t>Макросы СхемаЧБ и СхемаЦвет переключают вид вручную — например, чтобы посмотреть, как квитанция будет выглядеть у жителя на экране.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="8" customHeight="1">
-      <c r="A22" s="75" t="inlineStr"/>
+      <c r="A22" s="73" t="inlineStr"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="76" t="inlineStr">
+      <c r="A23" s="74" t="inlineStr">
         <is>
           <t>5. QR-код</t>
         </is>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="77" t="inlineStr">
+      <c r="A24" s="75" t="inlineStr">
         <is>
           <t>Строка платежа по ГОСТ Р 56042-2014 собирается формулой на листе НАСТРОЙКИ (имя КВ_QR) и готова к передаче в любой генератор QR. Функция СтрокаQR возвращает её из VBA.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="77" t="inlineStr">
+      <c r="A25" s="75" t="inlineStr">
         <is>
           <t>Сама картинка QR в шаблон не встроена: вставьте изображение в область G32:H37 вручную либо подключите свой генератор в процедуре ВставитьQR (в модуле оставлена заготовка).</t>
         </is>
       </c>
     </row>
     <row r="26" ht="8" customHeight="1">
-      <c r="A26" s="75" t="inlineStr"/>
+      <c r="A26" s="73" t="inlineStr"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="76" t="inlineStr">
+      <c r="A27" s="74" t="inlineStr">
         <is>
           <t>6. Что проверить перед первой выдачей квитанций</t>
         </is>
       </c>
     </row>
     <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="77" t="inlineStr">
+      <c r="A28" s="75" t="inlineStr">
         <is>
           <t>• Размер взноса (руб./м²). В исходном файле он подтягивался из внешней книги, поэтому столбец F листа ДАННЫЕ оставлен пустым, а бланк восстанавливает тариф как начислено ÷ площадь. Впишите утверждённый тариф, чтобы в квитанции стояла точная величина.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="77" t="inlineStr">
+      <c r="A29" s="75" t="inlineStr">
         <is>
           <t>• Остаток средств на специальном счёте и накопления по лицевому счёту (столбцы L и M). Пока они пусты, в разделе 4 стоит прочерк.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="77" t="inlineStr">
+      <c r="A30" s="75" t="inlineStr">
         <is>
           <t>• Реквизиты специального счёта на листе НАСТРОЙКИ — они перенесены из вашего образца без изменений.</t>
         </is>

--- a/kapremont/output/Квитанция_КапРемонт_Омск_шаблон.xlsx
+++ b/kapremont/output/Квитанция_КапРемонт_Омск_шаблон.xlsx
@@ -27,14 +27,13 @@
     <definedName name="КВ_ПЕРЕРАСЧЕТ">КВИТАНЦИЯ!$H$23</definedName>
     <definedName name="КВ_ИТОГО">КВИТАНЦИЯ!$H$24</definedName>
     <definedName name="КВ_ОПЛАЧЕНО">КВИТАНЦИЯ!$G$27</definedName>
-    <definedName name="КВ_НАКОПЛЕНО">КВИТАНЦИЯ!$G$28</definedName>
-    <definedName name="КВ_ОСТАТОК">КВИТАНЦИЯ!$G$29</definedName>
-    <definedName name="КВ_QR_МЕСТО">КВИТАНЦИЯ!$G$32</definedName>
+    <definedName name="КВ_ОСТАТОК">КВИТАНЦИЯ!$G$28</definedName>
+    <definedName name="КВ_QR_МЕСТО">КВИТАНЦИЯ!$G$31</definedName>
     <definedName name="КВ_QR">НАСТРОЙКИ!$B$20</definedName>
     <definedName name="КВ_СХЕМА">НАСТРОЙКИ!$B$17</definedName>
-    <definedName name="ДАННЫЕ_ТАБЛИЦА">ДАННЫЕ!$A$1:$Q$5000</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'КВИТАНЦИЯ'!$A$1:$I$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ДАННЫЕ'!$A$1:$Q$1</definedName>
+    <definedName name="ДАННЫЕ_ТАБЛИЦА">ДАННЫЕ!$A$1:$P$5000</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'КВИТАНЦИЯ'!$A$1:$I$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ДАННЫЕ'!$A$1:$P$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -929,7 +928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H43"/>
+  <dimension ref="B2:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.8" customWidth="1" min="1" max="1"/>
@@ -984,7 +983,7 @@
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="4">
-        <f>"Расчётный период: "&amp;IF(IFERROR(INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$14,INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
+        <f>"Расчётный период: "&amp;IF(IFERROR(INDEX(ДАННЫЕ!$M:$M,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$14,INDEX(ДАННЫЕ!$M:$M,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
         <v/>
       </c>
       <c r="G3" s="4" t="n"/>
@@ -1214,7 +1213,7 @@
         </is>
       </c>
       <c r="G17" s="31">
-        <f>IF(IFERROR(INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$14,INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
+        <f>IF(IFERROR(INDEX(ДАННЫЕ!$M:$M,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$14,INDEX(ДАННЫЕ!$M:$M,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
         <v/>
       </c>
       <c r="H17" s="32" t="n"/>
@@ -1264,7 +1263,7 @@
       <c r="D21" s="13" t="n"/>
       <c r="E21" s="13" t="n"/>
       <c r="F21" s="37">
-        <f>IF(IFERROR(INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$14,INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
+        <f>IF(IFERROR(INDEX(ДАННЫЕ!$M:$M,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$14,INDEX(ДАННЫЕ!$M:$M,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
         <v/>
       </c>
       <c r="G21" s="37" t="n"/>
@@ -1283,7 +1282,7 @@
       <c r="D22" s="13" t="n"/>
       <c r="E22" s="13" t="n"/>
       <c r="F22" s="37">
-        <f>"на "&amp;TEXT(DAY(IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;TEXT(MONTH(IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;YEAR(IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))))</f>
+        <f>"на "&amp;TEXT(DAY(IF(IFERROR(INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;TEXT(MONTH(IF(IFERROR(INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;YEAR(IF(IFERROR(INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))))</f>
         <v/>
       </c>
       <c r="G22" s="37" t="n"/>
@@ -1340,7 +1339,7 @@
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="B27" s="36">
-        <f>"Поступило оплат по лицевому счёту с начала "&amp;YEAR(IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))))&amp;" года, руб."</f>
+        <f>"Поступило оплат по лицевому счёту с начала "&amp;YEAR(IF(IFERROR(INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))))&amp;" года, руб."</f>
         <v/>
       </c>
       <c r="C27" s="13" t="n"/>
@@ -1354,66 +1353,50 @@
       <c r="H27" s="38" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="B28" s="36" t="inlineStr">
-        <is>
-          <t>Размер фонда капитального ремонта, накопленного по лицевому счёту, руб.</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="42">
-        <f>IF(IFERROR(INDEX(ДАННЫЕ!$M:$M,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="","—",INDEX(ДАННЫЕ!$M:$M,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
-        <v/>
-      </c>
-      <c r="H28" s="38" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="B29" s="43" t="inlineStr">
+      <c r="B28" s="43" t="inlineStr">
         <is>
           <t>Остаток средств на специальном счёте многоквартирного дома, руб.</t>
         </is>
       </c>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="19" t="n"/>
-      <c r="F29" s="19" t="n"/>
-      <c r="G29" s="44">
+      <c r="C28" s="19" t="n"/>
+      <c r="D28" s="19" t="n"/>
+      <c r="E28" s="19" t="n"/>
+      <c r="F28" s="19" t="n"/>
+      <c r="G28" s="44">
         <f>IF(IFERROR(INDEX(ДАННЫЕ!$L:$L,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="","—",INDEX(ДАННЫЕ!$L:$L,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="H29" s="45" t="n"/>
-    </row>
-    <row r="30" ht="5" customHeight="1"/>
-    <row r="31" ht="16" customHeight="1">
-      <c r="B31" s="6" t="inlineStr">
+      <c r="H28" s="45" t="n"/>
+    </row>
+    <row r="29" ht="5" customHeight="1"/>
+    <row r="30" ht="16" customHeight="1">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>5. ПОРЯДОК ОПЛАТЫ</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="8" t="n"/>
-    </row>
-    <row r="32" ht="14" customHeight="1">
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="8" t="n"/>
+    </row>
+    <row r="31" ht="14" customHeight="1">
+      <c r="B31" s="46" t="inlineStr">
+        <is>
+          <t>1) без комиссии — в отделениях АО «Россельхозбанк» (банк, в котором открыт специальный счёт дома);</t>
+        </is>
+      </c>
+      <c r="C31" s="47" t="n"/>
+      <c r="D31" s="47" t="n"/>
+      <c r="E31" s="47" t="n"/>
+      <c r="F31" s="47" t="n"/>
+      <c r="G31" s="48" t="n"/>
+      <c r="H31" s="49" t="n"/>
+    </row>
+    <row r="32" ht="26" customHeight="1">
       <c r="B32" s="46" t="inlineStr">
-        <is>
-          <t>1) без комиссии — в отделениях АО «Россельхозбанк» (банк, в котором открыт специальный счёт дома);</t>
-        </is>
-      </c>
-      <c r="C32" s="47" t="n"/>
-      <c r="D32" s="47" t="n"/>
-      <c r="E32" s="47" t="n"/>
-      <c r="F32" s="47" t="n"/>
-      <c r="G32" s="48" t="n"/>
-      <c r="H32" s="49" t="n"/>
-    </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="B33" s="46" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1442,6 +1425,15 @@
           </r>
         </is>
       </c>
+      <c r="C32" s="47" t="n"/>
+      <c r="D32" s="47" t="n"/>
+      <c r="E32" s="47" t="n"/>
+      <c r="F32" s="47" t="n"/>
+      <c r="G32" s="48" t="n"/>
+      <c r="H32" s="49" t="n"/>
+    </row>
+    <row r="33" ht="14" customHeight="1">
+      <c r="B33" s="46" t="n"/>
       <c r="C33" s="47" t="n"/>
       <c r="D33" s="47" t="n"/>
       <c r="E33" s="47" t="n"/>
@@ -1450,121 +1442,110 @@
       <c r="H33" s="49" t="n"/>
     </row>
     <row r="34" ht="14" customHeight="1">
-      <c r="B34" s="46" t="n"/>
-      <c r="C34" s="47" t="n"/>
-      <c r="D34" s="47" t="n"/>
-      <c r="E34" s="47" t="n"/>
-      <c r="F34" s="47" t="n"/>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>Назначение платежа:</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="15" t="n"/>
+      <c r="E34" s="15" t="n"/>
+      <c r="F34" s="15" t="n"/>
       <c r="G34" s="48" t="n"/>
       <c r="H34" s="49" t="n"/>
     </row>
-    <row r="35" ht="14" customHeight="1">
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>Назначение платежа:</t>
-        </is>
-      </c>
-      <c r="C35" s="15" t="n"/>
-      <c r="D35" s="15" t="n"/>
-      <c r="E35" s="15" t="n"/>
-      <c r="F35" s="15" t="n"/>
+    <row r="35" ht="30" customHeight="1">
+      <c r="B35" s="46">
+        <f>"Взнос на капитальный ремонт, л/с № "&amp;КВ_ЛС&amp;", кв. № "&amp;IFERROR(INDEX(ДАННЫЕ!$B:$B,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")&amp;", за "&amp;IF(IFERROR(INDEX(ДАННЫЕ!$M:$M,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$14,INDEX(ДАННЫЕ!$M:$M,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))&amp;"."</f>
+        <v/>
+      </c>
+      <c r="C35" s="47" t="n"/>
+      <c r="D35" s="47" t="n"/>
+      <c r="E35" s="47" t="n"/>
+      <c r="F35" s="47" t="n"/>
       <c r="G35" s="48" t="n"/>
       <c r="H35" s="49" t="n"/>
     </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="B36" s="46">
-        <f>"Взнос на капитальный ремонт, л/с № "&amp;КВ_ЛС&amp;", кв. № "&amp;IFERROR(INDEX(ДАННЫЕ!$B:$B,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")&amp;", за "&amp;IF(IFERROR(INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$14,INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))&amp;"."</f>
-        <v/>
-      </c>
-      <c r="C36" s="47" t="n"/>
-      <c r="D36" s="47" t="n"/>
-      <c r="E36" s="47" t="n"/>
-      <c r="F36" s="47" t="n"/>
-      <c r="G36" s="48" t="n"/>
-      <c r="H36" s="49" t="n"/>
-    </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="B37" s="33">
-        <f>"Срок оплаты: до "&amp;TEXT(DAY(IF(IFERROR(INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;TEXT(MONTH(IF(IFERROR(INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;YEAR(IF(IFERROR(INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))))&amp;" г."</f>
-        <v/>
-      </c>
-      <c r="C37" s="34" t="n"/>
-      <c r="D37" s="34" t="n"/>
-      <c r="E37" s="34" t="n"/>
-      <c r="F37" s="34" t="n"/>
-      <c r="G37" s="50" t="n"/>
-      <c r="H37" s="51" t="n"/>
-    </row>
-    <row r="38" ht="5" customHeight="1"/>
-    <row r="39" ht="32" customHeight="1">
-      <c r="B39" s="52">
+    <row r="36" ht="17" customHeight="1">
+      <c r="B36" s="33">
+        <f>"Срок оплаты: до "&amp;TEXT(DAY(IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;TEXT(MONTH(IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;YEAR(IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))))&amp;" г."</f>
+        <v/>
+      </c>
+      <c r="C36" s="34" t="n"/>
+      <c r="D36" s="34" t="n"/>
+      <c r="E36" s="34" t="n"/>
+      <c r="F36" s="34" t="n"/>
+      <c r="G36" s="50" t="n"/>
+      <c r="H36" s="51" t="n"/>
+    </row>
+    <row r="37" ht="5" customHeight="1"/>
+    <row r="38" ht="32" customHeight="1">
+      <c r="B38" s="52">
         <f>"ВНИМАНИЕ! ПЛАТИТЕ ТОЛЬКО ПО НОМЕРУ РАСЧЁТНОГО СЧЁТА "&amp;НАСТРОЙКИ!$B$7&amp;" — ЭТО СПЕЦИАЛЬНЫЙ СЧЁТ ВАШЕГО ДОМА"</f>
         <v/>
       </c>
-      <c r="C39" s="52" t="n"/>
-      <c r="D39" s="52" t="n"/>
-      <c r="E39" s="52" t="n"/>
-      <c r="F39" s="52" t="n"/>
-      <c r="G39" s="52" t="n"/>
-      <c r="H39" s="52" t="n"/>
-    </row>
-    <row r="40" ht="44" customHeight="1">
-      <c r="B40" s="53">
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+      <c r="E38" s="52" t="n"/>
+      <c r="F38" s="52" t="n"/>
+      <c r="G38" s="52" t="n"/>
+      <c r="H38" s="52" t="n"/>
+    </row>
+    <row r="39" ht="44" customHeight="1">
+      <c r="B39" s="53">
         <f>"В отделении банка и в мобильном приложении во вкладках ищите "&amp;"«РФКР МКД_капремонт, оплата по расчётному счёту» и указывайте номер расчётного счёта, приведённый выше. Оплата через общий поиск «Капитальный ремонт» уходит на общий счёт Регионального фонда капитального ремонта и на счёт вашего дома не поступает."&amp;CHAR(10)&amp;"Лицевой счёт № "&amp;КВ_ЛС&amp;" при оплате НЕ вводится — он указан справочно, только для учёта начислений."</f>
         <v/>
       </c>
-      <c r="C40" s="53" t="n"/>
-      <c r="D40" s="53" t="n"/>
-      <c r="E40" s="53" t="n"/>
-      <c r="F40" s="53" t="n"/>
-      <c r="G40" s="53" t="n"/>
-      <c r="H40" s="53" t="n"/>
-    </row>
-    <row r="41" ht="6" customHeight="1"/>
-    <row r="42" ht="24" customHeight="1">
-      <c r="B42" s="54" t="inlineStr">
+      <c r="C39" s="53" t="n"/>
+      <c r="D39" s="53" t="n"/>
+      <c r="E39" s="53" t="n"/>
+      <c r="F39" s="53" t="n"/>
+      <c r="G39" s="53" t="n"/>
+      <c r="H39" s="53" t="n"/>
+    </row>
+    <row r="40" ht="6" customHeight="1"/>
+    <row r="41" ht="24" customHeight="1">
+      <c r="B41" s="54" t="inlineStr">
         <is>
           <t>Подпись плательщика  ______________________</t>
         </is>
       </c>
-      <c r="C42" s="54" t="n"/>
-      <c r="D42" s="54" t="n"/>
-      <c r="E42" s="54" t="inlineStr">
+      <c r="C41" s="54" t="n"/>
+      <c r="D41" s="54" t="n"/>
+      <c r="E41" s="54" t="inlineStr">
         <is>
           <t>Кассир  ______________</t>
         </is>
       </c>
-      <c r="F42" s="54" t="n"/>
-      <c r="G42" s="54" t="inlineStr">
+      <c r="F41" s="54" t="n"/>
+      <c r="G41" s="54" t="inlineStr">
         <is>
           <t>Дата  ____________</t>
         </is>
       </c>
-      <c r="H42" s="54" t="n"/>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="B43" s="55">
-        <f>"По вопросам начислений обращайтесь к председателю совета дома, тел. "&amp;НАСТРОЙКИ!$B$13&amp;".    Документ № "&amp;IF(IFERROR(INDEX(ДАННЫЕ!$Q:$Q,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="","—",INDEX(ДАННЫЕ!$Q:$Q,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
-        <v/>
-      </c>
-      <c r="C43" s="55" t="n"/>
-      <c r="D43" s="55" t="n"/>
-      <c r="E43" s="55" t="n"/>
-      <c r="F43" s="55" t="n"/>
-      <c r="G43" s="55" t="n"/>
-      <c r="H43" s="55" t="n"/>
+      <c r="H41" s="54" t="n"/>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="B42" s="55">
+        <f>"По вопросам начислений обращайтесь к председателю совета дома, тел. "&amp;НАСТРОЙКИ!$B$13&amp;".    Документ № "&amp;IF(IFERROR(INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="","—",INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
+        <v/>
+      </c>
+      <c r="C42" s="55" t="n"/>
+      <c r="D42" s="55" t="n"/>
+      <c r="E42" s="55" t="n"/>
+      <c r="F42" s="55" t="n"/>
+      <c r="G42" s="55" t="n"/>
+      <c r="H42" s="55" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="48">
-    <mergeCell ref="B42:D42"/>
+  <mergeCells count="46">
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
-    <mergeCell ref="B40:H40"/>
     <mergeCell ref="C9:H9"/>
-    <mergeCell ref="G42:H42"/>
     <mergeCell ref="G27:H27"/>
     <mergeCell ref="F8:H8"/>
-    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="B31:F31"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="G17:H17"/>
@@ -1576,29 +1557,29 @@
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="C7:H7"/>
     <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B31:H31"/>
     <mergeCell ref="B24:G24"/>
-    <mergeCell ref="B29:F29"/>
     <mergeCell ref="B34:F34"/>
-    <mergeCell ref="G32:H37"/>
+    <mergeCell ref="B41:D41"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B43:H43"/>
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="F23:G23"/>
-    <mergeCell ref="B37:F37"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="F22:G22"/>
+    <mergeCell ref="G31:H36"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="F11:H11"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C15:H15"/>
-    <mergeCell ref="G29:H29"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="B33:F33"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="B38:H38"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="F3:H3"/>
@@ -1942,7 +1923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1957,11 +1938,10 @@
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -2027,25 +2007,20 @@
       </c>
       <c r="M1" s="64" t="inlineStr">
         <is>
-          <t>Накоплено по лицевому счёту, руб.</t>
+          <t>Расчётный период (текст)</t>
         </is>
       </c>
       <c r="N1" s="64" t="inlineStr">
         <is>
-          <t>Расчётный период (текст)</t>
+          <t>Дата начала периода</t>
         </is>
       </c>
       <c r="O1" s="64" t="inlineStr">
         <is>
-          <t>Дата начала периода</t>
+          <t>Срок оплаты</t>
         </is>
       </c>
       <c r="P1" s="64" t="inlineStr">
-        <is>
-          <t>Срок оплаты</t>
-        </is>
-      </c>
-      <c r="Q1" s="64" t="inlineStr">
         <is>
           <t>№ квитанции</t>
         </is>
@@ -2088,19 +2063,18 @@
         <v>13441.28</v>
       </c>
       <c r="L2" s="67" t="n"/>
-      <c r="M2" s="67" t="n"/>
-      <c r="N2" s="65" t="inlineStr">
+      <c r="M2" s="65" t="inlineStr">
         <is>
           <t>Июль 2026</t>
         </is>
       </c>
+      <c r="N2" s="68" t="n">
+        <v>46204</v>
+      </c>
       <c r="O2" s="68" t="n">
-        <v>46204</v>
-      </c>
-      <c r="P2" s="68" t="n">
         <v>46244</v>
       </c>
-      <c r="Q2" s="65" t="inlineStr">
+      <c r="P2" s="65" t="inlineStr">
         <is>
           <t>КР-2026-07-31202</t>
         </is>
@@ -2109,14 +2083,14 @@
     <row r="4">
       <c r="A4" s="69" t="inlineStr">
         <is>
-          <t>Строка 2 — пример из образца. Ниже макрос разноски дописывает по одной строке на лицевой счёт за расчётный период. Ключ поиска — столбец A (лицевой счёт): по нему лист КВИТАНЦИЯ подтягивает все значения формулами ИНДЕКС/ПОИСКПОЗ. Столбцы F, J, L, M можно оставить пустыми — бланк рассчитает их сам либо поставит прочерк.</t>
+          <t>Строка 2 — пример из образца. Ниже макрос разноски дописывает по одной строке на лицевой счёт за расчётный период. Ключ поиска — столбец A (лицевой счёт): по нему лист КВИТАНЦИЯ подтягивает все значения формулами ИНДЕКС/ПОИСКПОЗ. Столбцы F, J и L можно оставить пустыми — бланк рассчитает их сам либо поставит прочерк.</t>
         </is>
       </c>
     </row>
     <row r="5"/>
     <row r="6"/>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:P1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H6"/>
   </mergeCells>
@@ -2245,7 +2219,7 @@
       </c>
       <c r="B4" s="71" t="inlineStr">
         <is>
-          <t>B5:H5,B13:H13,B19:H19,B26:H26,B31:H31</t>
+          <t>B5:H5,B13:H13,B19:H19,B26:H26,B30:H30</t>
         </is>
       </c>
       <c r="C4" s="70" t="inlineStr">
@@ -2309,7 +2283,7 @@
       </c>
       <c r="B6" s="71" t="inlineStr">
         <is>
-          <t>B6,B7,B8,E8,B9,B10,B11,E11,B14,D14,F14,B15,B16,B17,D17,F17,B35:F35</t>
+          <t>B6,B7,B8,E8,B9,B10,B11,E11,B14,D14,F14,B15,B16,B17,D17,F17,B34:F34</t>
         </is>
       </c>
       <c r="C6" s="70" t="inlineStr">
@@ -2341,7 +2315,7 @@
       </c>
       <c r="B7" s="71" t="inlineStr">
         <is>
-          <t>C6:H6,C7:H7,C8:D8,F8:H8,C9:H9,C10:H10,C11:D11,F11:H11,E14,G14:H14,C15:H15,C16:H16,C17,E17,G17:H17,B21:E21,F21:G21,H21,B22:E22,F22:G22,H22,B23:E23,F23:G23,H23,B27:F27,G27:H27,B28:F28,G28:H28,B29:F29,G29:H29,B32:F32,B33:F33,B34:F34,B36:F36,B43:H43</t>
+          <t>C6:H6,C7:H7,C8:D8,F8:H8,C9:H9,C10:H10,C11:D11,F11:H11,E14,G14:H14,C15:H15,C16:H16,C17,E17,G17:H17,B21:E21,F21:G21,H21,B22:E22,F22:G22,H22,B23:E23,F23:G23,H23,B27:F27,G27:H27,B28:F28,G28:H28,B31:F31,B32:F32,B33:F33,B35:F35,B42:H42</t>
         </is>
       </c>
       <c r="C7" s="70" t="inlineStr">
@@ -2405,7 +2379,7 @@
       </c>
       <c r="B9" s="71" t="inlineStr">
         <is>
-          <t>B24:G24,B39:H39</t>
+          <t>B24:G24,B38:H38</t>
         </is>
       </c>
       <c r="C9" s="70" t="inlineStr">
@@ -2469,7 +2443,7 @@
       </c>
       <c r="B11" s="71" t="inlineStr">
         <is>
-          <t>B37:F37,B40:H40</t>
+          <t>B36:F36,B39:H39</t>
         </is>
       </c>
       <c r="C11" s="70" t="inlineStr">
@@ -2501,7 +2475,7 @@
       </c>
       <c r="B12" s="71" t="inlineStr">
         <is>
-          <t>G32:H37</t>
+          <t>G31:H36</t>
         </is>
       </c>
       <c r="C12" s="70" t="inlineStr">
@@ -2533,7 +2507,7 @@
       </c>
       <c r="B13" s="71" t="inlineStr">
         <is>
-          <t>B42:D42,E42:F42,G42:H42</t>
+          <t>B41:D41,E41:F41,G41:H41</t>
         </is>
       </c>
       <c r="C13" s="70" t="inlineStr">
@@ -2741,7 +2715,7 @@
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="75" t="inlineStr">
         <is>
-          <t>Сама картинка QR в шаблон не встроена: вставьте изображение в область G32:H37 вручную либо подключите свой генератор в процедуре ВставитьQR (в модуле оставлена заготовка).</t>
+          <t>Сама картинка QR в шаблон не встроена: вставьте изображение в область G31:H36 вручную либо подключите свой генератор в процедуре ВставитьQR (в модуле оставлена заготовка).</t>
         </is>
       </c>
     </row>
@@ -2765,7 +2739,7 @@
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="75" t="inlineStr">
         <is>
-          <t>• Остаток средств на специальном счёте и накопления по лицевому счёту (столбцы L и M). Пока они пусты, в разделе 4 стоит прочерк.</t>
+          <t>• Остаток средств на специальном счёте многоквартирного дома (столбец L). Пока он пуст, в разделе 4 стоит прочерк.</t>
         </is>
       </c>
     </row>

--- a/kapremont/output/Квитанция_КапРемонт_Омск_шаблон.xlsx
+++ b/kapremont/output/Квитанция_КапРемонт_Омск_шаблон.xlsx
@@ -340,7 +340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -487,6 +487,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1466,76 +1469,76 @@
       <c r="G35" s="48" t="n"/>
       <c r="H35" s="49" t="n"/>
     </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="B36" s="33">
-        <f>"Срок оплаты: до "&amp;TEXT(DAY(IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;TEXT(MONTH(IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;YEAR(IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))))&amp;" г."</f>
-        <v/>
-      </c>
-      <c r="C36" s="34" t="n"/>
-      <c r="D36" s="34" t="n"/>
-      <c r="E36" s="34" t="n"/>
-      <c r="F36" s="34" t="n"/>
-      <c r="G36" s="50" t="n"/>
-      <c r="H36" s="51" t="n"/>
+    <row r="36" ht="20" customHeight="1">
+      <c r="B36" s="50">
+        <f>"Срок оплаты: до "&amp;НАСТРОЙКИ!$B$16&amp;" числа каждого месяца (за "&amp;IF(IFERROR(INDEX(ДАННЫЕ!$M:$M,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$14,INDEX(ДАННЫЕ!$M:$M,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))&amp;" — до "&amp;TEXT(DAY(IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",EOMONTH(IF(IFERROR(INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))),0)+НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;TEXT(MONTH(IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",EOMONTH(IF(IFERROR(INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))),0)+НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;YEAR(IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",EOMONTH(IF(IFERROR(INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))),0)+НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))))&amp;")"</f>
+        <v/>
+      </c>
+      <c r="C36" s="51" t="n"/>
+      <c r="D36" s="51" t="n"/>
+      <c r="E36" s="51" t="n"/>
+      <c r="F36" s="51" t="n"/>
+      <c r="G36" s="51" t="n"/>
+      <c r="H36" s="52" t="n"/>
     </row>
     <row r="37" ht="5" customHeight="1"/>
     <row r="38" ht="32" customHeight="1">
-      <c r="B38" s="52">
+      <c r="B38" s="53">
         <f>"ВНИМАНИЕ! ПЛАТИТЕ ТОЛЬКО ПО НОМЕРУ РАСЧЁТНОГО СЧЁТА "&amp;НАСТРОЙКИ!$B$7&amp;" — ЭТО СПЕЦИАЛЬНЫЙ СЧЁТ ВАШЕГО ДОМА"</f>
         <v/>
       </c>
-      <c r="C38" s="52" t="n"/>
-      <c r="D38" s="52" t="n"/>
-      <c r="E38" s="52" t="n"/>
-      <c r="F38" s="52" t="n"/>
-      <c r="G38" s="52" t="n"/>
-      <c r="H38" s="52" t="n"/>
+      <c r="C38" s="53" t="n"/>
+      <c r="D38" s="53" t="n"/>
+      <c r="E38" s="53" t="n"/>
+      <c r="F38" s="53" t="n"/>
+      <c r="G38" s="53" t="n"/>
+      <c r="H38" s="53" t="n"/>
     </row>
     <row r="39" ht="44" customHeight="1">
-      <c r="B39" s="53">
+      <c r="B39" s="54">
         <f>"В отделении банка и в мобильном приложении во вкладках ищите "&amp;"«РФКР МКД_капремонт, оплата по расчётному счёту» и указывайте номер расчётного счёта, приведённый выше. Оплата через общий поиск «Капитальный ремонт» уходит на общий счёт Регионального фонда капитального ремонта и на счёт вашего дома не поступает."&amp;CHAR(10)&amp;"Лицевой счёт № "&amp;КВ_ЛС&amp;" при оплате НЕ вводится — он указан справочно, только для учёта начислений."</f>
         <v/>
       </c>
-      <c r="C39" s="53" t="n"/>
-      <c r="D39" s="53" t="n"/>
-      <c r="E39" s="53" t="n"/>
-      <c r="F39" s="53" t="n"/>
-      <c r="G39" s="53" t="n"/>
-      <c r="H39" s="53" t="n"/>
+      <c r="C39" s="54" t="n"/>
+      <c r="D39" s="54" t="n"/>
+      <c r="E39" s="54" t="n"/>
+      <c r="F39" s="54" t="n"/>
+      <c r="G39" s="54" t="n"/>
+      <c r="H39" s="54" t="n"/>
     </row>
     <row r="40" ht="6" customHeight="1"/>
     <row r="41" ht="24" customHeight="1">
-      <c r="B41" s="54" t="inlineStr">
+      <c r="B41" s="55" t="inlineStr">
         <is>
           <t>Подпись плательщика  ______________________</t>
         </is>
       </c>
-      <c r="C41" s="54" t="n"/>
-      <c r="D41" s="54" t="n"/>
-      <c r="E41" s="54" t="inlineStr">
+      <c r="C41" s="55" t="n"/>
+      <c r="D41" s="55" t="n"/>
+      <c r="E41" s="55" t="inlineStr">
         <is>
           <t>Кассир  ______________</t>
         </is>
       </c>
-      <c r="F41" s="54" t="n"/>
-      <c r="G41" s="54" t="inlineStr">
+      <c r="F41" s="55" t="n"/>
+      <c r="G41" s="55" t="inlineStr">
         <is>
           <t>Дата  ____________</t>
         </is>
       </c>
-      <c r="H41" s="54" t="n"/>
+      <c r="H41" s="55" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
-      <c r="B42" s="55">
+      <c r="B42" s="56">
         <f>"По вопросам начислений обращайтесь к председателю совета дома, тел. "&amp;НАСТРОЙКИ!$B$13&amp;".    Документ № "&amp;IF(IFERROR(INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="","—",INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
         <v/>
       </c>
-      <c r="C42" s="55" t="n"/>
-      <c r="D42" s="55" t="n"/>
-      <c r="E42" s="55" t="n"/>
-      <c r="F42" s="55" t="n"/>
-      <c r="G42" s="55" t="n"/>
-      <c r="H42" s="55" t="n"/>
+      <c r="C42" s="56" t="n"/>
+      <c r="D42" s="56" t="n"/>
+      <c r="E42" s="56" t="n"/>
+      <c r="F42" s="56" t="n"/>
+      <c r="G42" s="56" t="n"/>
+      <c r="H42" s="56" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="46">
@@ -1612,301 +1615,301 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="56" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>Параметр</t>
         </is>
       </c>
-      <c r="B1" s="56" t="inlineStr">
+      <c r="B1" s="57" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C1" s="56" t="inlineStr">
+      <c r="C1" s="57" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="57" t="inlineStr">
+      <c r="A2" s="58" t="inlineStr">
         <is>
           <t>Получатель платежа</t>
         </is>
       </c>
-      <c r="B2" s="58" t="inlineStr">
+      <c r="B2" s="59" t="inlineStr">
         <is>
           <t>РЕГИОНАЛЬНЫЙ ФОНД КАПИТАЛЬНОГО РЕМОНТА МНОГОКВАРТИРНЫХ ДОМОВ ОМСКОЙ ОБЛАСТИ (СПЕЦ. СЧЕТ)</t>
         </is>
       </c>
-      <c r="C2" s="59" t="inlineStr">
+      <c r="C2" s="60" t="inlineStr">
         <is>
           <t>Владелец специального счёта МКД</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="57" t="inlineStr">
+      <c r="A3" s="58" t="inlineStr">
         <is>
           <t>Юридический адрес</t>
         </is>
       </c>
-      <c r="B3" s="58" t="inlineStr">
+      <c r="B3" s="59" t="inlineStr">
         <is>
           <t>644099, г. Омск, ул. Краснофлотская, 24</t>
         </is>
       </c>
-      <c r="C3" s="59" t="inlineStr">
+      <c r="C3" s="60" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="57" t="inlineStr">
+      <c r="A4" s="58" t="inlineStr">
         <is>
           <t>ИНН</t>
         </is>
       </c>
-      <c r="B4" s="58" t="inlineStr">
+      <c r="B4" s="59" t="inlineStr">
         <is>
           <t>5503239348</t>
         </is>
       </c>
-      <c r="C4" s="59" t="inlineStr">
+      <c r="C4" s="60" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="57" t="inlineStr">
+      <c r="A5" s="58" t="inlineStr">
         <is>
           <t>КПП</t>
         </is>
       </c>
-      <c r="B5" s="58" t="inlineStr">
+      <c r="B5" s="59" t="inlineStr">
         <is>
           <t>550301001</t>
         </is>
       </c>
-      <c r="C5" s="59" t="inlineStr">
+      <c r="C5" s="60" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="57" t="inlineStr">
+      <c r="A6" s="58" t="inlineStr">
         <is>
           <t>ОГРН</t>
         </is>
       </c>
-      <c r="B6" s="58" t="inlineStr">
+      <c r="B6" s="59" t="inlineStr">
         <is>
           <t>1027700342890</t>
         </is>
       </c>
-      <c r="C6" s="59" t="inlineStr">
+      <c r="C6" s="60" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="57" t="inlineStr">
+      <c r="A7" s="58" t="inlineStr">
         <is>
           <t>Расчётный счёт (спец. счёт МКД)</t>
         </is>
       </c>
-      <c r="B7" s="58" t="inlineStr">
+      <c r="B7" s="59" t="inlineStr">
         <is>
           <t>40604810809000000154</t>
         </is>
       </c>
-      <c r="C7" s="59" t="inlineStr">
+      <c r="C7" s="60" t="inlineStr">
         <is>
           <t>Специальный счёт дома по ул. Магистральная, 2</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="57" t="inlineStr">
+      <c r="A8" s="58" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
       </c>
-      <c r="B8" s="58" t="inlineStr">
+      <c r="B8" s="59" t="inlineStr">
         <is>
           <t>Омский РФ АО «Россельхозбанк»</t>
         </is>
       </c>
-      <c r="C8" s="59" t="inlineStr">
+      <c r="C8" s="60" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="57" t="inlineStr">
+      <c r="A9" s="58" t="inlineStr">
         <is>
           <t>Корреспондентский счёт</t>
         </is>
       </c>
-      <c r="B9" s="58" t="inlineStr">
+      <c r="B9" s="59" t="inlineStr">
         <is>
           <t>30101810900000000822</t>
         </is>
       </c>
-      <c r="C9" s="59" t="inlineStr">
+      <c r="C9" s="60" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="57" t="inlineStr">
+      <c r="A10" s="58" t="inlineStr">
         <is>
           <t>БИК</t>
         </is>
       </c>
-      <c r="B10" s="58" t="inlineStr">
+      <c r="B10" s="59" t="inlineStr">
         <is>
           <t>045209822</t>
         </is>
       </c>
-      <c r="C10" s="59" t="inlineStr">
+      <c r="C10" s="60" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="57" t="inlineStr">
+      <c r="A11" s="58" t="inlineStr">
         <is>
           <t>ИНН/КПП банка</t>
         </is>
       </c>
-      <c r="B11" s="58" t="inlineStr">
+      <c r="B11" s="59" t="inlineStr">
         <is>
           <t>7725114488 / 550502001</t>
         </is>
       </c>
-      <c r="C11" s="59" t="inlineStr">
+      <c r="C11" s="60" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="57" t="inlineStr">
+      <c r="A12" s="58" t="inlineStr">
         <is>
           <t>Адрес МКД</t>
         </is>
       </c>
-      <c r="B12" s="58" t="inlineStr">
+      <c r="B12" s="59" t="inlineStr">
         <is>
           <t>г. Омск, ул. Магистральная, 2</t>
         </is>
       </c>
-      <c r="C12" s="59" t="inlineStr">
+      <c r="C12" s="60" t="inlineStr">
         <is>
           <t>Из образца</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="57" t="inlineStr">
+      <c r="A13" s="58" t="inlineStr">
         <is>
           <t>Контактный телефон</t>
         </is>
       </c>
-      <c r="B13" s="58" t="inlineStr">
+      <c r="B13" s="59" t="inlineStr">
         <is>
           <t>8 908 108 02 00</t>
         </is>
       </c>
-      <c r="C13" s="59" t="inlineStr">
+      <c r="C13" s="60" t="inlineStr">
         <is>
           <t>Председатель совета дома</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="57" t="inlineStr">
+      <c r="A14" s="58" t="inlineStr">
         <is>
           <t>Расчётный период (текст)</t>
         </is>
       </c>
-      <c r="B14" s="58" t="inlineStr">
+      <c r="B14" s="59" t="inlineStr">
         <is>
           <t>Июль 2026</t>
         </is>
       </c>
-      <c r="C14" s="59" t="inlineStr">
+      <c r="C14" s="60" t="inlineStr">
         <is>
           <t>Подставляется в заголовок и в назначение платежа</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="57" t="inlineStr">
+      <c r="A15" s="58" t="inlineStr">
         <is>
           <t>Дата начала периода</t>
         </is>
       </c>
-      <c r="B15" s="60" t="n">
+      <c r="B15" s="61" t="n">
         <v>46204</v>
       </c>
-      <c r="C15" s="59" t="inlineStr">
+      <c r="C15" s="60" t="inlineStr">
         <is>
           <t>Первое число расчётного месяца</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="57" t="inlineStr">
-        <is>
-          <t>Срок оплаты</t>
-        </is>
-      </c>
-      <c r="B16" s="60" t="n">
-        <v>46244</v>
-      </c>
-      <c r="C16" s="59" t="inlineStr">
-        <is>
-          <t>До какого числа вносится взнос</t>
+      <c r="A16" s="58" t="inlineStr">
+        <is>
+          <t>День срока оплаты</t>
+        </is>
+      </c>
+      <c r="B16" s="59" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" s="60" t="inlineStr">
+        <is>
+          <t>Взнос вносится до этого числа месяца, следующего за расчётным</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="57" t="inlineStr">
+      <c r="A17" s="58" t="inlineStr">
         <is>
           <t>Текущая цветовая схема</t>
         </is>
       </c>
-      <c r="B17" s="58" t="inlineStr">
+      <c r="B17" s="59" t="inlineStr">
         <is>
           <t>ЧБ</t>
         </is>
       </c>
-      <c r="C17" s="59" t="inlineStr">
+      <c r="C17" s="60" t="inlineStr">
         <is>
           <t>ЧБ — для печати на А4; ЦВЕТ — для выгрузки в PDF. Переключается макросом</t>
         </is>
       </c>
     </row>
     <row r="20" ht="64" customHeight="1">
-      <c r="A20" s="61" t="inlineStr">
+      <c r="A20" s="62" t="inlineStr">
         <is>
           <t>Строка QR (ГОСТ Р 56042-2014)</t>
         </is>
       </c>
-      <c r="B20" s="62">
+      <c r="B20" s="63">
         <f>"ST00012|Name="&amp;НАСТРОЙКИ!$B$2&amp;"|PersonalAcc="&amp;НАСТРОЙКИ!$B$7&amp;"|BankName="&amp;НАСТРОЙКИ!$B$8&amp;"|BIC="&amp;НАСТРОЙКИ!$B$10&amp;"|CorrespAcc="&amp;НАСТРОЙКИ!$B$9&amp;"|PayeeINN="&amp;НАСТРОЙКИ!$B$4&amp;"|KPP="&amp;НАСТРОЙКИ!$B$5&amp;"|Sum="&amp;TEXT(ROUND(КВ_ИТОГО*100,0),"0")&amp;"|Purpose=Взнос на капитальный ремонт за "&amp;НАСТРОЙКИ!$B$14&amp;", л/с "&amp;КВ_ЛС&amp;"|PersAcc="&amp;КВ_ЛС&amp;"|PayerAddress="&amp;КВ_АДРЕС</f>
         <v/>
       </c>
-      <c r="C20" s="63" t="inlineStr">
+      <c r="C20" s="64" t="inlineStr">
         <is>
           <t>Сумма — в копейках, как требует стандарт. Значение читается макросом (функция СтрокаQR) и передаётся в генератор QR-кода.</t>
         </is>
@@ -1940,150 +1943,148 @@
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="64" t="inlineStr">
+      <c r="A1" s="65" t="inlineStr">
         <is>
           <t>Лицевой счёт</t>
         </is>
       </c>
-      <c r="B1" s="64" t="inlineStr">
+      <c r="B1" s="65" t="inlineStr">
         <is>
           <t>Квартира</t>
         </is>
       </c>
-      <c r="C1" s="64" t="inlineStr">
+      <c r="C1" s="65" t="inlineStr">
         <is>
           <t>ФИО собственника</t>
         </is>
       </c>
-      <c r="D1" s="64" t="inlineStr">
+      <c r="D1" s="65" t="inlineStr">
         <is>
           <t>Адрес помещения</t>
         </is>
       </c>
-      <c r="E1" s="64" t="inlineStr">
+      <c r="E1" s="65" t="inlineStr">
         <is>
           <t>Площадь, м²</t>
         </is>
       </c>
-      <c r="F1" s="64" t="inlineStr">
+      <c r="F1" s="65" t="inlineStr">
         <is>
           <t>Размер взноса, руб./м²</t>
         </is>
       </c>
-      <c r="G1" s="64" t="inlineStr">
+      <c r="G1" s="65" t="inlineStr">
         <is>
           <t>Начислено за период, руб.</t>
         </is>
       </c>
-      <c r="H1" s="64" t="inlineStr">
+      <c r="H1" s="65" t="inlineStr">
         <is>
           <t>Задолженность на начало периода, руб.</t>
         </is>
       </c>
-      <c r="I1" s="64" t="inlineStr">
+      <c r="I1" s="65" t="inlineStr">
         <is>
           <t>Перерасчёт / переплата, руб.</t>
         </is>
       </c>
-      <c r="J1" s="64" t="inlineStr">
+      <c r="J1" s="65" t="inlineStr">
         <is>
           <t>ИТОГО к оплате, руб.</t>
         </is>
       </c>
-      <c r="K1" s="64" t="inlineStr">
+      <c r="K1" s="65" t="inlineStr">
         <is>
           <t>Оплачено с начала года, руб.</t>
         </is>
       </c>
-      <c r="L1" s="64" t="inlineStr">
+      <c r="L1" s="65" t="inlineStr">
         <is>
           <t>Остаток на спец. счёте МКД, руб.</t>
         </is>
       </c>
-      <c r="M1" s="64" t="inlineStr">
+      <c r="M1" s="65" t="inlineStr">
         <is>
           <t>Расчётный период (текст)</t>
         </is>
       </c>
-      <c r="N1" s="64" t="inlineStr">
+      <c r="N1" s="65" t="inlineStr">
         <is>
           <t>Дата начала периода</t>
         </is>
       </c>
-      <c r="O1" s="64" t="inlineStr">
-        <is>
-          <t>Срок оплаты</t>
-        </is>
-      </c>
-      <c r="P1" s="64" t="inlineStr">
+      <c r="O1" s="65" t="inlineStr">
+        <is>
+          <t>Срок оплаты (если отличается)</t>
+        </is>
+      </c>
+      <c r="P1" s="65" t="inlineStr">
         <is>
           <t>№ квитанции</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="65" t="n">
+      <c r="A2" s="66" t="n">
         <v>31202</v>
       </c>
-      <c r="B2" s="65" t="n">
+      <c r="B2" s="66" t="n">
         <v>49</v>
       </c>
-      <c r="C2" s="65" t="inlineStr">
+      <c r="C2" s="66" t="inlineStr">
         <is>
           <t>Иванов Иван Иванович</t>
         </is>
       </c>
-      <c r="D2" s="65" t="inlineStr">
+      <c r="D2" s="66" t="inlineStr">
         <is>
           <t>г. Омск, ул. Магистральная, 2, кв. 49</t>
         </is>
       </c>
-      <c r="E2" s="66" t="n">
+      <c r="E2" s="67" t="n">
         <v>63.1</v>
       </c>
-      <c r="F2" s="67" t="n"/>
-      <c r="G2" s="67" t="n">
+      <c r="F2" s="68" t="n"/>
+      <c r="G2" s="68" t="n">
         <v>674.99</v>
       </c>
-      <c r="H2" s="67" t="n">
+      <c r="H2" s="68" t="n">
         <v>19501.38</v>
       </c>
-      <c r="I2" s="67" t="n">
+      <c r="I2" s="68" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="67" t="n">
+      <c r="J2" s="68" t="n">
         <v>20176.37</v>
       </c>
-      <c r="K2" s="67" t="n">
+      <c r="K2" s="68" t="n">
         <v>13441.28</v>
       </c>
-      <c r="L2" s="67" t="n"/>
-      <c r="M2" s="65" t="inlineStr">
+      <c r="L2" s="68" t="n"/>
+      <c r="M2" s="66" t="inlineStr">
         <is>
           <t>Июль 2026</t>
         </is>
       </c>
-      <c r="N2" s="68" t="n">
+      <c r="N2" s="69" t="n">
         <v>46204</v>
       </c>
-      <c r="O2" s="68" t="n">
-        <v>46244</v>
-      </c>
-      <c r="P2" s="65" t="inlineStr">
+      <c r="O2" s="69" t="n"/>
+      <c r="P2" s="66" t="inlineStr">
         <is>
           <t>КР-2026-07-31202</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="69" t="inlineStr">
-        <is>
-          <t>Строка 2 — пример из образца. Ниже макрос разноски дописывает по одной строке на лицевой счёт за расчётный период. Ключ поиска — столбец A (лицевой счёт): по нему лист КВИТАНЦИЯ подтягивает все значения формулами ИНДЕКС/ПОИСКПОЗ. Столбцы F, J и L можно оставить пустыми — бланк рассчитает их сам либо поставит прочерк.</t>
+      <c r="A4" s="70" t="inlineStr">
+        <is>
+          <t>Строка 2 — пример из образца. Ниже макрос разноски дописывает по одной строке на лицевой счёт за расчётный период. Ключ поиска — столбец A (лицевой счёт): по нему лист КВИТАНЦИЯ подтягивает все значения формулами ИНДЕКС/ПОИСКПОЗ. Столбцы F, J, L и P можно оставить пустыми — бланк рассчитает их сам либо поставит прочерк.</t>
         </is>
       </c>
     </row>
@@ -2116,423 +2117,423 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="64" t="inlineStr">
+      <c r="A1" s="65" t="inlineStr">
         <is>
           <t>Роль</t>
         </is>
       </c>
-      <c r="B1" s="64" t="inlineStr">
+      <c r="B1" s="65" t="inlineStr">
         <is>
           <t>Диапазоны (через запятую)</t>
         </is>
       </c>
-      <c r="C1" s="64" t="inlineStr">
+      <c r="C1" s="65" t="inlineStr">
         <is>
           <t>ЧБ: заливка</t>
         </is>
       </c>
-      <c r="D1" s="64" t="inlineStr">
+      <c r="D1" s="65" t="inlineStr">
         <is>
           <t>ЧБ: шрифт</t>
         </is>
       </c>
-      <c r="E1" s="64" t="inlineStr">
+      <c r="E1" s="65" t="inlineStr">
         <is>
           <t>ЦВЕТ: заливка</t>
         </is>
       </c>
-      <c r="F1" s="64" t="inlineStr">
+      <c r="F1" s="65" t="inlineStr">
         <is>
           <t>ЦВЕТ: шрифт</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="70" t="inlineStr">
+      <c r="A2" s="71" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B2" s="71" t="inlineStr">
+      <c r="B2" s="72" t="inlineStr">
         <is>
           <t>B2:H2</t>
         </is>
       </c>
-      <c r="C2" s="70" t="inlineStr">
+      <c r="C2" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D2" s="70" t="inlineStr">
+      <c r="D2" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E2" s="70" t="inlineStr">
+      <c r="E2" s="71" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
-      <c r="F2" s="70" t="inlineStr">
+      <c r="F2" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="70" t="inlineStr">
+      <c r="A3" s="71" t="inlineStr">
         <is>
           <t>subtitle</t>
         </is>
       </c>
-      <c r="B3" s="71" t="inlineStr">
+      <c r="B3" s="72" t="inlineStr">
         <is>
           <t>B3:E3,F3:H3</t>
         </is>
       </c>
-      <c r="C3" s="70" t="inlineStr">
+      <c r="C3" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D3" s="70" t="inlineStr">
+      <c r="D3" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E3" s="70" t="inlineStr">
+      <c r="E3" s="71" t="inlineStr">
         <is>
           <t>DDEFF0</t>
         </is>
       </c>
-      <c r="F3" s="70" t="inlineStr">
+      <c r="F3" s="71" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="70" t="inlineStr">
+      <c r="A4" s="71" t="inlineStr">
         <is>
           <t>section</t>
         </is>
       </c>
-      <c r="B4" s="71" t="inlineStr">
+      <c r="B4" s="72" t="inlineStr">
         <is>
           <t>B5:H5,B13:H13,B19:H19,B26:H26,B30:H30</t>
         </is>
       </c>
-      <c r="C4" s="70" t="inlineStr">
+      <c r="C4" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D4" s="70" t="inlineStr">
+      <c r="D4" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E4" s="70" t="inlineStr">
+      <c r="E4" s="71" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
-      <c r="F4" s="70" t="inlineStr">
+      <c r="F4" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="70" t="inlineStr">
+      <c r="A5" s="71" t="inlineStr">
         <is>
           <t>thead</t>
         </is>
       </c>
-      <c r="B5" s="71" t="inlineStr">
+      <c r="B5" s="72" t="inlineStr">
         <is>
           <t>B20:E20,F20:G20,H20</t>
         </is>
       </c>
-      <c r="C5" s="70" t="inlineStr">
+      <c r="C5" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D5" s="70" t="inlineStr">
+      <c r="D5" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E5" s="70" t="inlineStr">
+      <c r="E5" s="71" t="inlineStr">
         <is>
           <t>263238</t>
         </is>
       </c>
-      <c r="F5" s="70" t="inlineStr">
+      <c r="F5" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="70" t="inlineStr">
+      <c r="A6" s="71" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="B6" s="71" t="inlineStr">
+      <c r="B6" s="72" t="inlineStr">
         <is>
           <t>B6,B7,B8,E8,B9,B10,B11,E11,B14,D14,F14,B15,B16,B17,D17,F17,B34:F34</t>
         </is>
       </c>
-      <c r="C6" s="70" t="inlineStr">
+      <c r="C6" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D6" s="70" t="inlineStr">
+      <c r="D6" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E6" s="70" t="inlineStr">
+      <c r="E6" s="71" t="inlineStr">
         <is>
           <t>F3F5F5</t>
         </is>
       </c>
-      <c r="F6" s="70" t="inlineStr">
+      <c r="F6" s="71" t="inlineStr">
         <is>
           <t>263238</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="70" t="inlineStr">
+      <c r="A7" s="71" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="B7" s="71" t="inlineStr">
+      <c r="B7" s="72" t="inlineStr">
         <is>
           <t>C6:H6,C7:H7,C8:D8,F8:H8,C9:H9,C10:H10,C11:D11,F11:H11,E14,G14:H14,C15:H15,C16:H16,C17,E17,G17:H17,B21:E21,F21:G21,H21,B22:E22,F22:G22,H22,B23:E23,F23:G23,H23,B27:F27,G27:H27,B28:F28,G28:H28,B31:F31,B32:F32,B33:F33,B35:F35,B42:H42</t>
         </is>
       </c>
-      <c r="C7" s="70" t="inlineStr">
+      <c r="C7" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D7" s="70" t="inlineStr">
+      <c r="D7" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E7" s="70" t="inlineStr">
+      <c r="E7" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="F7" s="70" t="inlineStr">
+      <c r="F7" s="71" t="inlineStr">
         <is>
           <t>263238</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="70" t="inlineStr">
+      <c r="A8" s="71" t="inlineStr">
         <is>
           <t>input</t>
         </is>
       </c>
-      <c r="B8" s="71" t="inlineStr">
+      <c r="B8" s="72" t="inlineStr">
         <is>
           <t>C14</t>
         </is>
       </c>
-      <c r="C8" s="70" t="inlineStr">
+      <c r="C8" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D8" s="70" t="inlineStr">
+      <c r="D8" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E8" s="70" t="inlineStr">
+      <c r="E8" s="71" t="inlineStr">
         <is>
           <t>E8F3F3</t>
         </is>
       </c>
-      <c r="F8" s="70" t="inlineStr">
+      <c r="F8" s="71" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="70" t="inlineStr">
+      <c r="A9" s="71" t="inlineStr">
         <is>
           <t>total</t>
         </is>
       </c>
-      <c r="B9" s="71" t="inlineStr">
+      <c r="B9" s="72" t="inlineStr">
         <is>
           <t>B24:G24,B38:H38</t>
         </is>
       </c>
-      <c r="C9" s="70" t="inlineStr">
+      <c r="C9" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D9" s="70" t="inlineStr">
+      <c r="D9" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E9" s="70" t="inlineStr">
+      <c r="E9" s="71" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
-      <c r="F9" s="70" t="inlineStr">
+      <c r="F9" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="70" t="inlineStr">
+      <c r="A10" s="71" t="inlineStr">
         <is>
           <t>totalsum</t>
         </is>
       </c>
-      <c r="B10" s="71" t="inlineStr">
+      <c r="B10" s="72" t="inlineStr">
         <is>
           <t>H24</t>
         </is>
       </c>
-      <c r="C10" s="70" t="inlineStr">
+      <c r="C10" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D10" s="70" t="inlineStr">
+      <c r="D10" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E10" s="70" t="inlineStr">
+      <c r="E10" s="71" t="inlineStr">
         <is>
           <t>E8F3F3</t>
         </is>
       </c>
-      <c r="F10" s="70" t="inlineStr">
+      <c r="F10" s="71" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="70" t="inlineStr">
+      <c r="A11" s="71" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B11" s="71" t="inlineStr">
+      <c r="B11" s="72" t="inlineStr">
         <is>
           <t>B36:F36,B39:H39</t>
         </is>
       </c>
-      <c r="C11" s="70" t="inlineStr">
+      <c r="C11" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D11" s="70" t="inlineStr">
+      <c r="D11" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E11" s="70" t="inlineStr">
+      <c r="E11" s="71" t="inlineStr">
         <is>
           <t>E8F3F3</t>
         </is>
       </c>
-      <c r="F11" s="70" t="inlineStr">
+      <c r="F11" s="71" t="inlineStr">
         <is>
           <t>263238</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="70" t="inlineStr">
+      <c r="A12" s="71" t="inlineStr">
         <is>
           <t>qr</t>
         </is>
       </c>
-      <c r="B12" s="71" t="inlineStr">
+      <c r="B12" s="72" t="inlineStr">
         <is>
           <t>G31:H36</t>
         </is>
       </c>
-      <c r="C12" s="70" t="inlineStr">
+      <c r="C12" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D12" s="70" t="inlineStr">
+      <c r="D12" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E12" s="70" t="inlineStr">
+      <c r="E12" s="71" t="inlineStr">
         <is>
           <t>F3F5F5</t>
         </is>
       </c>
-      <c r="F12" s="70" t="inlineStr">
+      <c r="F12" s="71" t="inlineStr">
         <is>
           <t>0F6B70</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="70" t="inlineStr">
+      <c r="A13" s="71" t="inlineStr">
         <is>
           <t>plain</t>
         </is>
       </c>
-      <c r="B13" s="71" t="inlineStr">
+      <c r="B13" s="72" t="inlineStr">
         <is>
           <t>B41:D41,E41:F41,G41:H41</t>
         </is>
       </c>
-      <c r="C13" s="70" t="inlineStr">
+      <c r="C13" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="D13" s="70" t="inlineStr">
+      <c r="D13" s="71" t="inlineStr">
         <is>
           <t>000000</t>
         </is>
       </c>
-      <c r="E13" s="70" t="inlineStr">
+      <c r="E13" s="71" t="inlineStr">
         <is>
           <t>FFFFFF</t>
         </is>
       </c>
-      <c r="F13" s="70" t="inlineStr">
+      <c r="F13" s="71" t="inlineStr">
         <is>
           <t>263238</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="69" t="inlineStr">
+      <c r="A15" s="70" t="inlineStr">
         <is>
           <t>Служебная таблица. Макрос ПрименитьСхему читает её и перекрашивает лист КВИТАНЦИЯ. Цвета задаются шестью шестнадцатеричными знаками RRGGBB — правьте прямо здесь, код менять не нужно.</t>
         </is>
@@ -2565,186 +2566,186 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="72" t="inlineStr">
+      <c r="A1" s="73" t="inlineStr">
         <is>
           <t>КАК ВСТРОИТЬ ЭТОТ БЛАНК В СУЩЕСТВУЮЩУЮ ТАБЛИЦУ РАЗНОСКИ</t>
         </is>
       </c>
     </row>
     <row r="2" ht="8" customHeight="1">
-      <c r="A2" s="73" t="inlineStr"/>
+      <c r="A2" s="74" t="inlineStr"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="74" t="inlineStr">
+      <c r="A3" s="75" t="inlineStr">
         <is>
           <t>1. Перенос листов</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="75" t="inlineStr">
+      <c r="A4" s="76" t="inlineStr">
         <is>
           <t>Скопируйте в свою книгу (правый клик по ярлыку листа → Переместить/скопировать) листы КВИТАНЦИЯ, ДАННЫЕ, НАСТРОЙКИ и СХЕМА. Лист СХЕМА скрыт: чтобы увидеть его, нажмите правой кнопкой на любом ярлыке → Показать.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="75" t="inlineStr">
+      <c r="A5" s="76" t="inlineStr">
         <is>
           <t>Именованные диапазоны (КВ_ЛС, КВ_НАЧИСЛЕНО, КВ_ДОЛГ, КВ_ИТОГО и др.) переносятся вместе с листами. Проверьте их в Формулы → Диспетчер имён.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="75" t="inlineStr">
+      <c r="A6" s="76" t="inlineStr">
         <is>
           <t>Импортируйте модуль vba/modКвитанция.bas: Alt+F11 → File → Import File. Книгу сохраните как .xlsm.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="8" customHeight="1">
-      <c r="A7" s="73" t="inlineStr"/>
+      <c r="A7" s="74" t="inlineStr"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="74" t="inlineStr">
+      <c r="A8" s="75" t="inlineStr">
         <is>
           <t>2. Подключение разноски</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="75" t="inlineStr">
+      <c r="A9" s="76" t="inlineStr">
         <is>
           <t>Лист ДАННЫЕ — единственная точка стыковки. Ваш макрос разноски кладёт в него по одной строке на лицевой счёт за расчётный период. Ключ поиска — столбец A (лицевой счёт).</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="75" t="inlineStr">
+      <c r="A10" s="76" t="inlineStr">
         <is>
           <t>Если разноска уже лежит на другом листе, не копируйте её: пропишите в столбцах листа ДАННЫЕ обычные формулы-ссылки на этот лист (ВПР или ИНДЕКС+ПОИСКПОЗ). Бланк разницы не заметит.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="8" customHeight="1">
-      <c r="A11" s="73" t="inlineStr"/>
+      <c r="A11" s="74" t="inlineStr"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="74" t="inlineStr">
+      <c r="A12" s="75" t="inlineStr">
         <is>
           <t>3. Автоподстановка сумм</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="75" t="inlineStr">
+      <c r="A13" s="76" t="inlineStr">
         <is>
           <t>Достаточно записать лицевой счёт в ячейку КВИТАНЦИЯ!C14 (имя КВ_ЛС) — ФИО, адрес, площадь, начислено, долг и итог подтянутся формулами.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="75" t="inlineStr">
+      <c r="A14" s="76" t="inlineStr">
         <is>
           <t>Если суммы удобнее подавать напрямую из макроса, вызывайте процедуру ПодставитьСуммы: она пишет значения в лист ДАННЫЕ, а формулы бланка пересчитываются сами.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="75" t="inlineStr">
+      <c r="A15" s="76" t="inlineStr">
         <is>
           <t>ИТОГО К ОПЛАТЕ берётся из столбца J листа ДАННЫЕ. Если столбец пуст, бланк считает итог сам: начислено + долг + перерасчёт. Пени в этом доме не начисляются, поэтому строки под них в бланке нет.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="8" customHeight="1">
-      <c r="A16" s="73" t="inlineStr"/>
+      <c r="A16" s="74" t="inlineStr"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="74" t="inlineStr">
+      <c r="A17" s="75" t="inlineStr">
         <is>
           <t>4. Печать и PDF</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="75" t="inlineStr">
+      <c r="A18" s="76" t="inlineStr">
         <is>
           <t>Книга сохранена в чёрно-белой схеме — можно сразу печатать на А4: одна страница, поля 5 мм, вписано по ширине и высоте.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="75" t="inlineStr">
+      <c r="A19" s="76" t="inlineStr">
         <is>
           <t>Макрос ЭкспортКвитанцииВPDF временно переключает бланк в цветную схему, выгружает PDF и возвращает чёрно-белый вид. Файл для отправки жителю получается цветным, бумажная копия остаётся чёрно-белой.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="75" t="inlineStr">
+      <c r="A20" s="76" t="inlineStr">
         <is>
           <t>Макрос ПакетныйЭкспортPDF делает то же самое по всем лицевым счетам листа ДАННЫЕ и раскладывает файлы по выбранной папке.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="75" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>Макросы СхемаЧБ и СхемаЦвет переключают вид вручную — например, чтобы посмотреть, как квитанция будет выглядеть у жителя на экране.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="8" customHeight="1">
-      <c r="A22" s="73" t="inlineStr"/>
+      <c r="A22" s="74" t="inlineStr"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="74" t="inlineStr">
+      <c r="A23" s="75" t="inlineStr">
         <is>
           <t>5. QR-код</t>
         </is>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="75" t="inlineStr">
+      <c r="A24" s="76" t="inlineStr">
         <is>
           <t>Строка платежа по ГОСТ Р 56042-2014 собирается формулой на листе НАСТРОЙКИ (имя КВ_QR) и готова к передаче в любой генератор QR. Функция СтрокаQR возвращает её из VBA.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="75" t="inlineStr">
+      <c r="A25" s="76" t="inlineStr">
         <is>
           <t>Сама картинка QR в шаблон не встроена: вставьте изображение в область G31:H36 вручную либо подключите свой генератор в процедуре ВставитьQR (в модуле оставлена заготовка).</t>
         </is>
       </c>
     </row>
     <row r="26" ht="8" customHeight="1">
-      <c r="A26" s="73" t="inlineStr"/>
+      <c r="A26" s="74" t="inlineStr"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="74" t="inlineStr">
+      <c r="A27" s="75" t="inlineStr">
         <is>
           <t>6. Что проверить перед первой выдачей квитанций</t>
         </is>
       </c>
     </row>
     <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="75" t="inlineStr">
+      <c r="A28" s="76" t="inlineStr">
         <is>
           <t>• Размер взноса (руб./м²). В исходном файле он подтягивался из внешней книги, поэтому столбец F листа ДАННЫЕ оставлен пустым, а бланк восстанавливает тариф как начислено ÷ площадь. Впишите утверждённый тариф, чтобы в квитанции стояла точная величина.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="75" t="inlineStr">
+      <c r="A29" s="76" t="inlineStr">
         <is>
           <t>• Остаток средств на специальном счёте многоквартирного дома (столбец L). Пока он пуст, в разделе 4 стоит прочерк.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="75" t="inlineStr">
+      <c r="A30" s="76" t="inlineStr">
         <is>
           <t>• Реквизиты специального счёта на листе НАСТРОЙКИ — они перенесены из вашего образца без изменений.</t>
         </is>

--- a/kapremont/output/Квитанция_КапРемонт_Омск_шаблон.xlsx
+++ b/kapremont/output/Квитанция_КапРемонт_Омск_шаблон.xlsx
@@ -1469,9 +1469,9 @@
       <c r="G35" s="48" t="n"/>
       <c r="H35" s="49" t="n"/>
     </row>
-    <row r="36" ht="20" customHeight="1">
+    <row r="36" ht="26" customHeight="1">
       <c r="B36" s="50">
-        <f>"Срок оплаты: до "&amp;НАСТРОЙКИ!$B$16&amp;" числа каждого месяца (за "&amp;IF(IFERROR(INDEX(ДАННЫЕ!$M:$M,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$14,INDEX(ДАННЫЕ!$M:$M,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))&amp;" — до "&amp;TEXT(DAY(IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",EOMONTH(IF(IFERROR(INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))),0)+НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;TEXT(MONTH(IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",EOMONTH(IF(IFERROR(INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))),0)+НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;YEAR(IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",EOMONTH(IF(IFERROR(INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))),0)+НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))))&amp;")"</f>
+        <f>"Срок оплаты: до "&amp;НАСТРОЙКИ!$B$16&amp;" числа каждого месяца (за "&amp;IF(IFERROR(INDEX(ДАННЫЕ!$M:$M,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$14,INDEX(ДАННЫЕ!$M:$M,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))&amp;" — до "&amp;TEXT(DAY(IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",EOMONTH(IF(IFERROR(INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))),0)+НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;TEXT(MONTH(IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",EOMONTH(IF(IFERROR(INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))),0)+НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))),"00")&amp;"."&amp;YEAR(IF(IFERROR(INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",EOMONTH(IF(IFERROR(INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$15,INDEX(ДАННЫЕ!$N:$N,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))),0)+НАСТРОЙКИ!$B$16,INDEX(ДАННЫЕ!$O:$O,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0))))&amp;")."&amp;CHAR(10)&amp;"Основание: ч. 1 ст. 155, ч. 2 ст. 171 ЖК РФ."</f>
         <v/>
       </c>
       <c r="C36" s="51" t="n"/>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C16" s="60" t="inlineStr">
         <is>
-          <t>Взнос вносится до этого числа месяца, следующего за расчётным</t>
+          <t>Единый срок по ч. 1 ст. 155 и ч. 2 ст. 171 ЖК РФ (ФЗ от 24.06.2025 № 177-ФЗ, действует с 01.03.2026). Решением общего собрания не меняется</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2726,33 +2726,57 @@
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="75" t="inlineStr">
         <is>
-          <t>6. Что проверить перед первой выдачей квитанций</t>
+          <t>6. Сроки</t>
         </is>
       </c>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="76" t="inlineStr">
         <is>
-          <t>• Размер взноса (руб./м²). В исходном файле он подтягивался из внешней книги, поэтому столбец F листа ДАННЫЕ оставлен пустым, а бланк восстанавливает тариф как начислено ÷ площадь. Впишите утверждённый тариф, чтобы в квитанции стояла точная величина.</t>
+          <t>Взнос вносится до 15 числа месяца, следующего за расчётным — единый срок по ч. 1 ст. 155 и ч. 2 ст. 171 ЖК РФ в редакции Федерального закона от 24.06.2025 № 177-ФЗ (действует с 01.03.2026). Он распространяется и на взносы на капитальный ремонт по специальному счёту; решением общего собрания его изменить нельзя.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="76" t="inlineStr">
         <is>
+          <t>Тем же законом сдвинут срок вручения платёжного документа: его нужно представить собственнику не позднее 5 числа месяца, следующего за расчётным (раньше было не позднее 1 числа). Планируйте разноску и рассылку квитанций с запасом до этой даты.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="8" customHeight="1">
+      <c r="A30" s="74" t="inlineStr"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="75" t="inlineStr">
+        <is>
+          <t>7. Что проверить перед первой выдачей квитанций</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="76" t="inlineStr">
+        <is>
+          <t>• Размер взноса (руб./м²). В исходном файле он подтягивался из внешней книги, поэтому столбец F листа ДАННЫЕ оставлен пустым, а бланк восстанавливает тариф как начислено ÷ площадь. Впишите утверждённый тариф, чтобы в квитанции стояла точная величина.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="76" t="inlineStr">
+        <is>
           <t>• Остаток средств на специальном счёте многоквартирного дома (столбец L). Пока он пуст, в разделе 4 стоит прочерк.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="76" t="inlineStr">
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="76" t="inlineStr">
         <is>
           <t>• Реквизиты специального счёта на листе НАСТРОЙКИ — они перенесены из вашего образца без изменений.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="34">
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A12:F12"/>
@@ -2761,9 +2785,11 @@
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A32:F32"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A17:F17"/>
@@ -2775,6 +2801,8 @@
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A34:F34"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A24:F24"/>

--- a/kapremont/output/Квитанция_КапРемонт_Омск_шаблон.xlsx
+++ b/kapremont/output/Квитанция_КапРемонт_Омск_шаблон.xlsx
@@ -31,9 +31,9 @@
     <definedName name="КВ_QR_МЕСТО">КВИТАНЦИЯ!$G$31</definedName>
     <definedName name="КВ_QR">НАСТРОЙКИ!$B$20</definedName>
     <definedName name="КВ_СХЕМА">НАСТРОЙКИ!$B$17</definedName>
-    <definedName name="ДАННЫЕ_ТАБЛИЦА">ДАННЫЕ!$A$1:$P$5000</definedName>
+    <definedName name="ДАННЫЕ_ТАБЛИЦА">ДАННЫЕ!$A$1:$O$5000</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'КВИТАНЦИЯ'!$A$1:$I$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ДАННЫЕ'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ДАННЫЕ'!$A$1:$O$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="B42" s="56">
-        <f>"По вопросам начислений обращайтесь к председателю совета дома, тел. "&amp;НАСТРОЙКИ!$B$13&amp;".    Документ № "&amp;IF(IFERROR(INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="","—",INDEX(ДАННЫЕ!$P:$P,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))</f>
+        <f>"Начисление за "&amp;IF(IFERROR(INDEX(ДАННЫЕ!$M:$M,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)),"")="",НАСТРОЙКИ!$B$14,INDEX(ДАННЫЕ!$M:$M,MATCH(КВ_ЛС,ДАННЫЕ!$A:$A,0)))&amp;".    По вопросам начислений обращайтесь к председателю совета дома, тел. "&amp;НАСТРОЙКИ!$B$13&amp;"."</f>
         <v/>
       </c>
       <c r="C42" s="56" t="n"/>
@@ -1926,7 +1926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1944,7 +1944,6 @@
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -2023,11 +2022,6 @@
           <t>Срок оплаты (если отличается)</t>
         </is>
       </c>
-      <c r="P1" s="65" t="inlineStr">
-        <is>
-          <t>№ квитанции</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="66" t="n">
@@ -2075,23 +2069,18 @@
         <v>46204</v>
       </c>
       <c r="O2" s="69" t="n"/>
-      <c r="P2" s="66" t="inlineStr">
-        <is>
-          <t>КР-2026-07-31202</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="70" t="inlineStr">
         <is>
-          <t>Строка 2 — пример из образца. Ниже макрос разноски дописывает по одной строке на лицевой счёт за расчётный период. Ключ поиска — столбец A (лицевой счёт): по нему лист КВИТАНЦИЯ подтягивает все значения формулами ИНДЕКС/ПОИСКПОЗ. Столбцы F, J, L и P можно оставить пустыми — бланк рассчитает их сам либо поставит прочерк.</t>
+          <t>Строка 2 — пример из образца. Ниже макрос разноски дописывает по одной строке на лицевой счёт за расчётный период. Ключ поиска — столбец A (лицевой счёт): по нему лист КВИТАНЦИЯ подтягивает все значения формулами ИНДЕКС/ПОИСКПОЗ. Столбцы F, J, L и O можно оставить пустыми — бланк рассчитает их сам либо поставит прочерк.</t>
         </is>
       </c>
     </row>
     <row r="5"/>
     <row r="6"/>
   </sheetData>
-  <autoFilter ref="A1:P1"/>
+  <autoFilter ref="A1:O1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H6"/>
   </mergeCells>

--- a/kapremont/output/Квитанция_КапРемонт_Омск_шаблон.xlsx
+++ b/kapremont/output/Квитанция_КапРемонт_Омск_шаблон.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="КВИТАНЦИЯ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="НАСТРОЙКИ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ДАННЫЕ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="СХЕМА" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet name="ИНСТРУКЦИЯ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="КВИТАНЦИЯ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="НАСТРОЙКИ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ДАННЫЕ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="СХЕМА" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ИНСТРУКЦИЯ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="КВ_ЛС">КВИТАНЦИЯ!$C$14</definedName>
@@ -33,7 +33,10 @@
     <definedName name="КВ_СХЕМА">НАСТРОЙКИ!$B$17</definedName>
     <definedName name="ДАННЫЕ_ТАБЛИЦА">ДАННЫЕ!$A$1:$O$5000</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'КВИТАНЦИЯ'!$A$1:$I$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'НАСТРОЙКИ'!$A$1:$C$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ДАННЫЕ'!$A$1:$O$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'ДАННЫЕ'!$A$1:$P$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'ИНСТРУКЦИЯ'!$A$1:$F$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1604,7 +1607,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1916,7 +1919,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1924,7 +1928,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2084,7 +2088,8 @@
   <mergeCells count="1">
     <mergeCell ref="A4:H6"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2541,7 +2546,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2801,6 +2806,7 @@
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/kapremont/output/Квитанция_КапРемонт_Омск_шаблон.xlsx
+++ b/kapremont/output/Квитанция_КапРемонт_Омск_шаблон.xlsx
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="C14" s="22" t="n">
-        <v>31202</v>
+        <v>3120249</v>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
     </row>
     <row r="2">
       <c r="A2" s="66" t="n">
-        <v>31202</v>
+        <v>3120249</v>
       </c>
       <c r="B2" s="66" t="n">
         <v>49</v>
@@ -2077,7 +2077,7 @@
     <row r="4">
       <c r="A4" s="70" t="inlineStr">
         <is>
-          <t>Строка 2 — пример из образца. Ниже макрос разноски дописывает по одной строке на лицевой счёт за расчётный период. Ключ поиска — столбец A (лицевой счёт): по нему лист КВИТАНЦИЯ подтягивает все значения формулами ИНДЕКС/ПОИСКПОЗ. Столбцы F, J, L и O можно оставить пустыми — бланк рассчитает их сам либо поставит прочерк.</t>
+          <t>Строка 2 — пример из образца. Ниже макрос разноски дописывает по одной строке на лицевой счёт за расчётный период. Ключ поиска — столбец A (лицевой счёт): по нему лист КВИТАНЦИЯ подтягивает все значения формулами ИНДЕКС/ПОИСКПОЗ. Лицевой счёт складывается из номера дома и номера квартиры: 31202 + 49 = 3120249. Столбцы F, J, L и O можно оставить пустыми — бланк рассчитает их сам либо поставит прочерк.</t>
         </is>
       </c>
     </row>
